--- a/Datasets_all.xlsx
+++ b/Datasets_all.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="626">
   <si>
     <t>Author</t>
   </si>
@@ -367,49 +367,49 @@
     <t>https://www.10xgenomics.com/datasets/fixed-frozen-visium-on-cytassist-mouse-brain-probe-based-whole-transcriptome-profiling-2-standard</t>
   </si>
   <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-08050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjM2In0.EArwM5nWmFpOFMYtl4-EWPSqqE3f9BR_JCgtJtduNUyI-lbq3gvB7Z_S7qDQKuyFFaEQen_qJm37fPei1yRMqIJ-0WfEr67YD5SGouncXEQ_Q7m9YKQLFRSxZzNMOkFLc8d7V0G414gNOSbw8meKXrXmfLYqNSUNGNf82KQhimM_wtb7xokpwZ4ILc4CtrdTqB1WS8h0_f_9fwC38hWgfmCvslD7KBjpzG3N_-0lVuwyax8xurfH3X_saLfVSo-snJXFsDk_EXpkWQgsND_szRioNQa1KpFvi056dplpOkXtc3hhzVMxmsgJmn3SMsHalHdUn8i9oZJXUI_O1IAXOrE8j_Zjf5swmRhB9LFElJz2HIhvqS7edohthWwCufReTzwyvPP59RvGyLIStLMfNfkc_JLpZCPGoiLc5cF1nY3zroLdp9u9EyXlZunDRMa3qB2tIxBWnIl2P8nwg73-fqEt7PGYn8u-HmPusJukIjf1QtYv5lJEYpXPoJtl4gZfR8NEyYd-4sHJPhJrqzuJ6Q.HUb-4324pi3j6M9CoEbLZeCCCKdZMi25GnywzNzUfUc&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-5b040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjM4In0.9bpDbKSST0Ap8IJtCAJasARrVPAMe3E5Bqih1DSXRNFHIjhVvjosGbtaUJ-Kdw6sM8zQeb455l13f7zV5uRcu2E53-ODgg-swZx9KtTYpdTcd97bH_ZtIkxaPy6zYPhQTSLwlvaMabZCIv0ua-h-Nzf8tcA4PT1y0o84jMecF0zxzusqaj0e2dkX4awChF1Ya3BVKTx62UMitOiOMkboXf1QnSQUK6soxpqF4DHisJ5RwNB3TQL7yzKIXP03xuhC9PipEkf2p9htPCW0Z3-QywtomOlUdfPB3v8JadIk3bq-gl91XDV3XCUfR0g3FxvTqmS3UTqQkXXlwbG-sCbvq20GwfiNmbLxHtbbQcp3_qFOtSd8EDZyXaW44fZnhP1B0hmkYW8ay95cjeeBaDtCnGw6zc9D0CYGYqlJEm0wH5AsCJ7qB1S-e6rV1CTYSNUNmq3BWx_1c1Bs8b1pPZ7Z7_x4mKw1eJWM2N8QaIdtiTzKaDLUDAwBlJjegDQ136VNu1LoXHZyUk19Ow_Xbt4esg.4bGjM-ytOe2vJa6QRWT5_-XrHEmMhAXtEiaLmkvAYqM&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-07050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjQwIn0.pdc8sR5K2gxvn4R1zVeiZlh7URAutTJ4PuukjiSs9vZYOCrwW944BQQdfvRPDeCqUMW5gIrWP9_NHEIXl6xuP1SmhL7eo-7yraZjMV_YOfPX07ycDZvYlH9hkcSFEBWYllLRay4TxYyixweXaOyizlEtW5hwdcXCqRGCKe9pHTvBiPYXTujTVFKX5vosyk-eZMYQ77jDKUV3JXpjIEpTs4vOmu1teAyju2gPeI4E5s9kSOz8A8apu8trFPKt1u7xLxTKkDRGu-rj2XJL0cxRLQ4fomdszMdNmatDsT3Xk6oNwDGcUGv0FvnpaGzWx0eK8qw0YDP9oHkhyglJVTPJYF9dhZM7LJnM5oVLKy_G_3buJa6A7HMgjJCkHcT7630pfuiaIZXrlkTbFqeRErO462qzl4fbdk7RU8dSSdlsoZanwDJPPx1VSld3Z21U-1wpASuqfqkEFVIA62q6SDlB9_pZsGEks3WPRiPd3mexZ-aFSGYq01zH5tgqb87jv0Ok-dc2frNfFe_VdlvnBVo7OQ.4bLJV4MmK_cXJmgYh5B8NmrS0n8BN7Ar5EnvalRZ_dI&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-31060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjQzIn0.F6y1yqF7YbWNTo_OYj-PQBQ6JPrBUNFa5_JSvZZaIecRBK761LpSMSr8ARYEGcTcv3uedYyM8dvEtVrskdr6pT-F6MtXnzrV4ORu2YvvY4w6Fy8ipmeaq7xojel3RRvN9kp6J2FdMH8XxFW5UPzNOnWd_v9pmp2zfOfIee5SJqd0FoSVmsCJj5kDPWtmhLJmj6gM0u719-55ca5Px4Kiw-BaUrknIQs9xe_Fv_ziOPa87HKYzVXmR-rnybaQjT0wYtNDe6U79y2m8Nv6xC1noua06LDtrX6vRygpxwkGauRScDHfgs2YH0fcjmUHQaK8oAqk33U5jmblTO1XKPTQDtpn6pSp4VkBGT8RWeKHADSa8GV6dIYiAWQl0aCU-hV0g03U01bivUglYZl3PcVP8XONDsmjXsn3wFNK7pO_noCuqB1-tmraO3V6fMT-prbHTeDmo2kzsW_jDlpvy8fwFtjIMZrnKLpS1FCYPlGq6lgvxU4DNHPbwBUvKKvvu-u2bqz32Xg1XM2jnxECHDrIAA.nWCM967MqF-qNWyYD2FPXhvdu9KyBvuQX3ERNN30ypw&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-30060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjQ1In0.vPYKJmZxjyN-Nf_fu3qcZcnph2PqFlsSEYM_EP_F_U4k_0_URaHvdSTkL3YfcUiGvIfWYHePJJAw1hL17EEIx9vMwWcEkM31H7tDxAvPQMF-7vvehIoqwqkN-pcXXFjb156m4J9Gw4ONbr8bPuSCbvuqA_GVV9Mdl8yFoshLWNt85XBlPQOEgB40netJAwHxacgrYhi39W_B6m5g_yc19MSpr2OftP9QkOWHOMvjEUaAO8UYyevnkF7uQo-SCGJNLL2ju8-Q-ANV4f_ODNagQmLWWlphBxA7__DheSuDREM5QdWUVc5ztRVM-EddPvOj5yHU1i9OgdS5KgKvh2tisj9pVCLhf8ZJthPCPo2esXXB2xer01HERFg4bUJXWYoicxH7_fmuY-sIY089cwUbtNJKcjBIfOMm704lxy9N-2RTxUSq7JNlTGV1EIoUvUV-DgGUx5nS3bDnJ84Vb1fKQB6i8EU-p3G1eoQYNnQIDo2qeKDMJ202ijMdK9gunnXJU44EnPG-pn-wqz_MuBnPqw.0H1rbHW5_s5VFhUsoMdnlkHfic8oiVu49TMqLSkyNYU&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-2f060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjQ3In0.9Md2zBNpbxk4W-g61H8QL8dgb7dqjGthmtFTYJQJdVznoc1v4AqS1BFTbtbfVZrGbCp2-1htE8N0kpoaoqNvgu8CzZSt9BP4yIO7Y0dwH2FFXKIxIlih8PcJglCveGxOwozYyaUsEyl9O-yBSL9F4_xmjpWF2konO5SKn6mJ7ZEEDBEpf2cVkRnG74xz60w_CSRIvjuKm38AKYL6STEGcAEUB7KYHSCzMOIxBpng-u_wqjg0jODMnY9TEeTW1WaUcJhCEVCu0SzADxBvRreQqf9SN0q2TZU0vtCzJFacp_xx1Z6peE-DMeT5SOzHvDsoRCVFOSk_8gvaPtCCFWLTiezkhJmTq22e89MtTmzU_P7PjefM1JnuHyMBJiuEFaKPXqfMAuSoje15pPwu3TZTMNBWgg4eGpkUws3sSojPbnb4aDxK-w-s1tvsq7bG2Q7lHPT4vQL4VwG5ujzgTfISyagDT4I0Y6Vd12CnRI_zJrQmoxq0LDKSAgsWFk4QgpGi9EaxWEEVz0E-SgvxOO3Opw.7XfjNVf1P347gOaZVuFb7GKiES1CLyaIxdXrG7xpE-Q&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-33060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjUwIn0.MeNcunRESCJP5fjmS2YgZA5o2yT8iQkNrZaDi96e-10FLmb_dicYAlS9DwzdccebihHkpi0MKpp3weMKrNlW9ApeNfdgde_UidYolMLyPwrFvxvhY7Jy2qs6gg8ke6cfGdfpaYynT-rWNRt2femY55cX7obu2I3rsCthZLMGJ_9yr8Gl6oeUbTXdapSwfIBs74usiF0-At2KPbDu_nLaD34cb_2QJb6JSZSsEXXx8sSGddjfc1VRnAWUOmYXbGOLfKvBvvU1bNTpVruNAD_u6n98c3K1tciwi1fOHKVQ0_p2QhWxooZcIAMkg9YXzCxOR8NBNwgL_5IXayglXGskY7UU5rudrbHZUCrfx12R-bfloOa-jQgLBqh9YCjRqO6KaWbgTyXf6kQucBUz8T7E93uU1NKyS7GqV8pRX3os6bWE-i9wOargj_kGuvlAYnhTvfYVx6NzxiRCUp47Gma2CRuLME6nq9y4Jw_Vj9-WdSqIWG5fp4wsIY9gObUZ5eUyvQIDe7D8LQD58j93YymBzA.NHA2QJ9aJP1a461WA9DgLMycqzvTf-PXWE5ySYKMckE&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-2d060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjUyIn0.dBEYTuynwsmxEbeiED2Br79Vpl4fmj6gg0V_qOuIgGyLNTYQTO20olqLGbl3iKWAbblUKKtlJpEu3K97nm7969vOmGEy2Tbp-2dWKEsKojkDd_rN0tPEYqsrCWHg0lhyzTp6mnmOts6_CZir-7tF0LjEUmRPvsAYqmclGGlnCE43NU1S22h6LR0MZSaGI-h1wEeSI6Cmt3enzjyCUE-juoao_JbEhRuivYzIZCERjrLN-Lt9RWhTteLAO-5dMUwWQNNp9DMD5EQLFqofNX0NWmAdD45s8C4v45XnNLCBuNTPfvvgzaqOE3oUecSjgVXLfjhzvxFYl_MzopOsy_6hOOBFr7wPjR-l0zoFAqBkZ_uSzfHwjD0RKcDNvmAEct4lB-R9YY2FZK4Qf-0D-OXmDYoEJkCqaeu2HSaBQDRJu8J0nj-6gu86mpP77nojLD9pVlfCuCXeY6zksUSvVbehzSww007tE2EP1lxOrOrXonjC2FVEhgP9UMa1QImtultITZQ3DHPwMrmzVUueYJZr7g.__DbPb9CTQK1obco39oQ9jYR5gbo35vRzw76QGWxGRU&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-32060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjU0In0.f3Jm86AQJ_dzDpcss8_TNl4vVlXqUKjStjIGLxgYOZlZVoS0_2lPutd00tCktwu-aOzAALnSSHVJWkBRxjkIfRgTCJlwyyftUo94bCNbNYkQmpUnnkH3EW0_v0qmz9ZnvDC-x3W08rKF-3EWo8NsPZRdvFGrPkz6gRJshCVshl6ZlVuWLJzHdERJOpLWfsMmhGBAFczb8mD3eD0wy8uvBt-FgxEiFtBIXLam-YezZRLlMpyup6ahhDX2wHEZyqGLr54kUKjEUmnz6jfSnNlr748OHImAs6nVE05ugWbfbDUY6BUl57L0IrwnXRfTlRElh_ZYqy_eShqUSB-XugrksvHxWFktUAVe2PjA75c9oBGXqDvzBu6zUtZqqTFbZ_x62FpadE7u_ZcE5qgnnj5pGLPiTDrVsT251k_8--1MlYxWkxvZ2bcZt1Z_AtZVwVfOrlXbHEC9hEuqMyDYqcmHCbraj8BVgmAgrvx80N6yWhI5SjBrmci5Uk0cV2kh-eK7k15-YYUNCZ4483sp6Cin2A.PiwDGYmexpYIThkrJNWROEtCB80Q0DGTgOD5Mves6e0&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-34060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjU3In0.FmAmbqcjeYKNcTKkja_wR1KXK-OH0Tawn6BnFe6aO-sgyakrGqEso-cy0-IavT4jXuHFCyeLot6zZVV_wFtkq77AXu7ulCugIhn8LhSAXOFgXos_5LI5chUDsOhXgxrKBFnHkhs1fbJ50PZ9OXTQyvbQ0LG10IRP49_6XSz6lmOecepgXh1Xpoq11oOClonJF91Gp4grjSd2EI2iTo0-xW-sdcMnSeFL3-buCMrNzhXdnfxvRAkse2-c-ol-0kBLjPs00_DzPdZz5OYPSpl6MY900WJVL_AVeDIfYvKrw5QNke9HsiKtZ7VaPHYsKI3j6aJLzphOQ6e6k5JJe4LiR-YY5fNDaFtkZRO5V6JHl4D0T56NiYjRkAqFGcSTYFeCVIpK_3R8EMaqidgFYEjwaFRGt3Zm0V5lHaRFO5yDqyGs2LrBihprIFlMj9oks8ePQUs38DhS0dg-vOrdvf7wj5UC_xbdYAUBAeFm9_ovGwbTK37R1sZGdjgxzmMSwhrB5QloNEQH13MnLYqAMkqR9A.p03XiKswfRR6zWj3fMZLEDERs8mV_yJjtaQhIJQgVaA&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-2e060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjU5In0.BqSFjS7dUai5VJFCsZkVkEIVK6faDBGZaiAuC3dxTyKC6o1EnKOquDksby8Pogkoaep_gZN3MRvaIBUyU3f-89rEemqqaihYy5dONafOgWhUpxWYOTeC4uQTjHZivBfI9PVzIJmeC5xDDEQtzPtqh6tSRzJ-3GnP7D-623JApQ1vRGwmLZ6-mzjWCWCsA-dD4p43_sWxtw0Vr6DgN72pxMOh31Ags0HGnQYqK8YXSuD1vXFm5THBNdklQJBeH3g6QZdsiJb6rAbJ-yC6QqctGA_UBQIgSe2B5AHn2ec09RzZ8fOM1wNZ2MjLQ8qy6JzQ1YEWxYnNYfUxwQyLHYeJONz8eA2_5tf7OhKyRpsN3U1y_nTBA9JDJ0p13HUEufvh5Z0fj0A-DacToGddenk5ftPtitE2M0rm3ZQdGWywKQepJ4MEW_tiIylMS9s-5Ri_DJqts0b7oVl70FRcck2kOjYyqPj14RcWczv_GeUspKmG4wnjgWvIyZ2pdMqJDXRBtkdObfdymoyPVSsbg8FoqQ.kzUDafcoiZ86TjH5OQBYkcuIXhbzb-UEdpHv9qx3O-M&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-a4040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjYyIn0.dLAH9ZKFaCfqufr8gUpz2HxmUI1NdacNRT_fbrCB-PwPmiz4cGAvgegOMIg80HWSLxtcjr9dji8b5mhSMROxyy0BRjvJHENdxWXnFbQsATyFnzheqei4xqNyTa0yQXvunK7x1_-eYEB1aLgJsnsgG9MYnhMxF8RmZo4yvUAJt9WNttbZa1cbAFFJ1cgk0QYpE09D27ORxQlPKKll-kXBedtMwPbjbg_vyhje9dDznGTdZWsB20NB5hozJjM5tVnj7_eaAYVCySvejQGNMlqs7evIPOxEwqm9NUt7s6W5NtjLJrtc67-OPSrP6i2TvQb-WUK1ZsN_AOGUkGTRN-4_gmevH0QsLXN843u9U9srNH0hSED73M8GChBjgQb6fEpiH4B5fGunrCf3IbykXbJuKDkQhaqaWvdbCWCd095-p6IOZm36HR44Ql2qLLhoarOQ3oA8eL5O1i7b6ATZFelOrR2PpcXu0SQoOHbSkTZbPpLnbdt6Wv7VWyDSjHBBd59eGzOlS1w7KRKGX3hQ-DdXfw.JLOzUCRD7eavlL-tyAX8hhIZWgJ7zYuE9ylNdGkbi3I&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d0050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjY0In0.FgJcfPgt6BViq-89PuHtkUPNd8HBiwwhwq610G5EIsuwpbn_25nxd3BOV0BRAg20VxhWCoHTMCPQw30eZwOOTmVJrkM2y2Of0uyOEMKgJY7TXf0810ztYfhLAKVx4hAQgneE09qhNcRv4DlaG28GFyDDkqEZRaRc_3wAimTKscWc56lLg5R8cG5Y738e2sff8HvSuUkRJUmGmkXHgWgTqZMDF1NqA0pKFq0D-hJcxg6yTjEPx-uWyb6vks1yr3o5YIzqjmtpxmGEZ9gxh64BdPbh_xhio7Dlud1AnkpD6xXXUZ22VPwMxx4j4VvIDj6TflTOEQj7HzVtO-SwC2MvPOWtOBYtClIOpYyevRJhZ2QRyaOqeEesz4np5HgWZamE68REdY_Ck8qf3nvU75fCVffnvZBUsdCIa4162SxbycjQ3xD4rO-7reJCLfonXvmCWipnxFRb1u6W7uNLaat5kA4ZLLVTh-v8HsRT4ClP4RMK58kNM38-e9BQEC_JE-lvhWlVo5VlacJJ9qCjVdxbrw.Ta-UPqQwm7-mrUj1Ot7oR-nj0mR7que3sBqzcEM7eco&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-3f070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjY2In0.9u3PhtvjYyQlXxaMVtlzhwMJ9w3WXk7SLlfWuqeEX55wRU7QKt5g_liKI4onT1Fvu9-L1YHHxmRXv-vV1qowN2h4y-nfogYoEgBgskMs-HV8skS1ST9IAw7L3dxYvuDrtapIJ-d443mx7qjFHcD_F098XhirG1W0mp1eF7dWHSx-PG4DDMYObFo-NnVfBNwN-uFP4kAKdsa_uQd5GndaADPT2oSLddOCI1qZVF8KiS405xpqDJN-8YehaQRaVnsBbSZPgBCoH-D6ei4Hw4lUlV2YQSBtINbVxKKwj8ocmjXfr04_Yt_ijCTLaLRlK6FGf23MxP0Dro8asQeSaobSfmUtNKb9H-zA6jRJ_eITfNzMJz8HdXwTZl8AzbQ6d34Nj5dgF9kkgqKGLjM5QE591GUwSdYImnjxJOH6-r7DynSZp5FC58dUKkNpRnEJLWyBVYg4XOoadbVR1SyRoouR5QcfTJ6AXKhbxvOAt17KQcj4VYH3c8agATrLHaGtnqJT3L8Z2FSqoKMaYUgI1HPONw.GlMDleRMpAP6WeTepTnr_KREp3HyLOkuRVbxT_3Z1CU&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-40070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjY5In0.J8z0yh5U7MkkJVkqBxAaE7wV0Y-y1X0SQrizSzK-iYMA6H4ecADVvYKScDQf_zA8BTDxSxnVGhWvde-P7fpMDHwa5ogbiaAjABPABjP9sY6P1TKUDgSDCdxvhyK0MwIBdOG8-Iwig49BvXf15l2VQMNpidC3Ghucp27WyHqL32ynQC2diUD-_jqLRvZtL1RnqjEMnUNamx5f7s1beB2l-PI7R0HdaFf0eU08BJSGwCyjZ3qcTuDxysVW5PRdiss-v6RJJek1FwANOI3dOh636Bv7JS_PcLXsoQYuQLjZgYW00qZceXWguw66r9qAddzmWQEb6EvA1vkYnPgrjqwqK-990A-nKZmqlqu7NKF4tDRO0TTdihpR6BN0xCbJ-55OdR-j0meKn0BgCOxzKWxyQLW0GN1HYoY3o_uPLMOVca72ZDbtOp86vT2Nc3zAejsVjusYNqFfzElZHZdKHRxEt-EVZDWb6VvYp29iSDmIHChza0AZlBgn_RSMZVIMPufx2n77ls3hVo19Q-9g8abdkA.T88T7avkUWMRV3fWyoH7zhrY5tQZOkryi7htayDXtQA&amp;ApiVersion=2.0</t>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-08050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTIwIn0.J_xUlRNE0mWPUdkKE3HbWGCERP6PqUKSEuBRhEfzM5YQnih0aIReyFd8EDWOySy2LArE1EeOp_yMArVqwhDXzcms6E5EuPpBRnUs-y2WkoByrycvNqN1AmUY4E1WGP8GsFT1xEdf0ZQn8jzktOEFnvEFs9qSL3S4CyNxnYkPc9OYksBqkqswzcyqagsvFAlWoi4Ai5Y1RSo3Qc2PyLPmW6g8cT_L2RONchguI4slgd3IWF2Gn_H8y8jkExLtIWBKprseeSpfChz5BAN4VMdoMVUtRjmy4FHsQ7JIz1Khg_1PIxxlVRSmWIxUaXXt7MLxGNYU5cqV4gWa-6-hiaz5qLI2OW5-M-Oz2oDa5VJ0StV8zOrd-H37SzPzFnCfvma1Gl-q7Xd8s2ppzqGitZGp4__q0ijUlNPiy-GgXhqU0qvbjFb9iDvsxJRqTbl8_-Bim0Mfr13b8UwKYDzmvP0BJGUN_Az07zPaYHwNWULS3rh_mCHeb_osu8I840DdwEVCssUV811zYkRrbIkpt2qo0w.kHxT4J6aHjByslhmdjkvsBKQ9QkqE1xUZk_3Y79CK-o&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-5b040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTIyIn0.XOQiPS56CUOTYuT76N_qa_12Xi9ypq1ooRX291sjQXwjS7wv-8b_P2FLHjoFvssNDh0tv0w_RR80L0WUtiUf7weu-1FD77Yh-JzPKDQKz4iPLAzpBiby2_P5pPx0a6XFllqv7lvss3OOWolniNonOjkBWGoGj2Q85HFIqgvS4Xmw7MXuTeaekjN42Ohslt5TygOWWlLwICoZz8I5KcyYm8Ujo_FC3W8zaKu_xDDVdM6x89xSFI7egMEN7TpBi5qz7aqyeuF1yl17v43BkTBlkFsH2KdOth3_-obD_prLUJghvWfoZGXLWg0lcoRyt_j6NvAzTKI2Ck5w8rJ4j8TdHjnbhctRa8Tq89RjaLemFYVKvkaDt2pb0ene08Yk9fDE7TLJJG-VEyCDN3NjWmIen_lrgtJrhWfK7FkYpkptfuOL_TRhZ39XjhBriawzOtHXEqQzxcIcsmjBk1d3muCcXdo9YPnJiPXRLhf8Lmr372mhXpUvY44cN76Ig_OIqBNb4WIzgZayT7QN2ZuElWvCTA.BoPQkz7ENoR1IwqjTeOerED4uTUenbcWjzE-MkQQVEA&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-07050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTI0In0.T08n6gbfoWepw6IlXCZ20VK4pY2eO47iWax7NB3YwsPhs_JfyXdojCqNHkXMbdSMhINtpjCAiuRP10xZ6dM-W3NAH6k4yqXj8o-UUBCiOj-Y60VCb5IoRnjpKLNV4BPNLm8eCOIAd0k7FpZvTOrvcnSWPyQd8ZTZrGtK443xGNxvbVq2nMsY2Rdt8h-9reBqSP_wvaCp_X3sPihjA-dVR-T5Os9O7GIHMptJuMw-FpN629BUDbtaK9ZN4aHq0wEQdN2xPmLYXR0SoHgAiX3XsWVCdgqcaPDY6crhXh0LkxFZeFi5GQkX90hrE8OXiGdn3tFkdm82G06EnQASOIhB8xaq0jfZA2fD-4X8eeHp2oc0SOrp2tkdlxn8rfzN8BSbBD-mWDJwpP6eLvwtDbtl9wLjXWn47FQ_p9bxQbZMc3MPVVbktWbPco5B71hJJ4ZjZD7GxO5y9b2kH1qbbhc6MIQH5MqrsyqvRhpLcj7GWPBZeXAhkxsaQnEpR9-BzcI4Dc9PmSI3SXA7LSZSxfgnMg.Rc-rW5zJWtIdzJ8YgTjtewFsSPrYwhPQfLrUkE15uCM&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-31060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTI3In0.xe0XFX6wGQ5sbHhB65OaG9gQIhDbQWygms5LJRGF6Lv3WC0-xIi6mljMNJyrxhbkW7sjvOVzGQGg_6XriVuSGCBQ1WAXB8NFVt6eW0Yba4Ds5Xf7HSM6AvCghmj_spoZbYf6Kur4rpimX8zrti1a2QdD2W4jJIlCO7QnO7AxTcJA0cg3LMsYz4t8YcItgO7loMsek5KVYXxb_3xfSvWZF5Yvty6Nnd3M5YOP0_7aY0h5QlGbag99MR0Kb_oFe4jZVORckH8UTbSyrmLTMESTKP9jxbi11VeoQH-WiY2UBm6jXxCrcWGzB5kwtK8Leq5XCj7ixYWIyWPlgrs6cVmgf4m5gtXyB4SDcbNnM1BG596M1PcWANif_5TWtl6w1R038fXlt9dAh3hBTHooq8FY6uIWXlGqZu8Y2_paUqn4_DwWaxGFuR_yb2ndphTFznpxiVUWuX58b1j38dTNWNQXfmccUmRgwvN_zWfE-vdeRtl14v7A_VixFYVCjyu2h0KYXE9g_soTlEinlyvAkDR73Q.xvk4OpPI9-ctExP_TRGpdOrazb-wahagJy-E_kV_ufI&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-30060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTI5In0.HobqdkzTtO30YFB-ULsyJOxbOTL6McJdaG4uBujg1phe_Yje0K_BaxrFDU16XUz1CVJIyZDWDfbbvPy0f9m3y0WS2nM3poGJYkeOmoUoeeMBGT-IXnIpVnLs1bzaJny5yekcPnkEaXxJCknx1YyoWY0aNLIX3T40YK0Isha1bPIIz8f_AAh89zTTGN0Dkef9l8_6Z97iYwo7CnSA6IzccvsIjL68XXQaT_PTKgf93yV9OH8_pQPkCV5xGaoL3St6K_oys-6orJWojwoaNX4iTCX22JG4Lhfea3cNQFUC0D0eiD_pJMWWzIp4AFnGRaCRXc8Y68YrBnG_h-ztCcUamSZvoWIQELxEY5B6ixNSR3pcHGnng8ODlee4EsfhuGC56MyZim539QgJIi1KGko3B_620M_-N55A8vQOx5eDBCLb0w78--CXR-AP5SgbWqM50PLRcUY5d5Nj_MfHv5wQ2TiV4gKrI_0Cfe_I2l2G4v0BBg4UyFygT7YP9GBiFvs0bPwSgdnnxy9m3KxE-ypCJQ.F56rO5whWSODd5F8nJ9V_wBLnxkOVNk48ciWpT0SnyI&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-2f060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTMxIn0.TcpaH1lib7RIOyQZqs5jhxD9v8z0QVCSWrPKncyG0Gg2zrMLA2lNXP-tb7_2iZ8x4HMdLvy-Ct5GLSNNPeRvR1Q6oeP_C_DAEzO5vwShNi7VvrxyIO66F8OAkEn_wros6AjU710XwYJzjuuDSpLID4R-cb-JfahYt6x5boqmrWDoI6mi9J-f1LCKEiZcOy8oZ3X2Np_Pl5Gi8XbQ3tmGOloc3NbxXdQWy-IuAaXLJ5QAVibcY-axVH9uTAQY2Q7o2G7YN50bDu0KJHehGygc4Pu-FkRSE7qw0jo4ZWZvKnMdO1QXPtWY0WSDNj2OQplJxVscKVlms-6G4wwtAagp8X6YXlOxpYKsoVaiZhnS9DyMZ6vjXsFrNAq30sfLyrYq3NBB6b9M-kILa3QG_pfJkaWuwBh6ruxkRTstNKBWpPCQ-p59lNIIPP96MuUPMxyCNgBgnDgzy-_lR2EKZ_4BnOW3EtZnmuFckS9g10POpDGqqHwFnRXu8nHd6nGEQidF80ksjxjTAqfcP_j5S1OUiQ.315kLdAQPNWqmH-zg-Et6xNBphKm13it66AaIc5B-aU&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-33060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTMzIn0.bkmwnBg5CsaX3nN24lRyM1cmVTp9xO7vog0trtHMvsmTv4Tb0UOnGoVgQWsB3BhRl-3eX_ADRJm8sXCPvnC4ujZ86dq-wFoBdjVpPc6vNP8-51cODcTqUIRhIkINKEzEcoF-z-d2EhI2U7f8DZpjb2FfW4vUhtkwIzhoFWGep3Tbe2AFEzs_A3607IrF2-q4HUs22OQUPC-JduQNL07BA4CkgBEvZ6fYdgq0Moey066HG251MKiChjeOHMySGpxlazx0oiY23--nQdQ4D8Bu0ysiyrNmtVzSaMO-50lyxthSKG3mAgNcwqsSAF2NG38BquAVqtxIcl4wDmqZYXDbvoJ9v3ZvR6woVLyO3GrlEhvRQmRsNUwc-Tvg_m5TDQL3pX5RYTPRvq-JXQw1xduoPwdat6v5gzY_519jD-kE-F4OZ9DNbIzI0eJOEvQto08DBSVZdwh2l1xu1RpUkpwkWJ6kkTND2CiBhQeJ2zSwKgvCKozYgVslT7u7CcYSa3zVmbxTh2YPyZwSZNVowJa74Q.tsLNckk1V7CMEvy7xBUtg9JjHI_kCGxsthujGwUMhfA&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-2d060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTM2In0.C_j7DyIfb1lB_18NGFJ5S6Tze8ezjiTKW8Jky53L22pujdJ5mWooBPFZTNEmxqlkVFr9-Nc3y-LQNXhq7aIn8ieoMPVGnnEwyiMiKYoIc0o7pjX_RbUgKksIPtTUQaKGFRJNtgcQo2sNz4XXmCgo7Su65290ZO9H62z3CMpePf72u1Bg4ZtmIg9S86NmU7wTu1GQIYJtJgwZU_2Ee5j2tAOvE43QMlqTxvczo8KzNFwn0HAk0HdRNSfw5sn13opAIbeNgKx6gJBevVFpmZ0O1wOKeamLKiaEq6eIuHVkEIWFXo4h_9BMZKO7pj5SBboX7h1LhIhJPWG38LeHCtIPvz4BN3agwKBGNMNZ3Oc9BZHvhWGHVEcgDbGxYqq7tYq_MWDRAY2zl4c_MKO42KkOP0knTJDUB9iHBATJozsd0j2X5j2oUBKrrFy3oUa9cX9fBW8vVkEvjtJQW92FzQb9yD_BxvJ7i0MdXfgwQxItHQmVkzDUs0Pb6aE7kjDoSuPFdgUvb0jjXwyTxzBa_7h6Jg.MCU4FNT-g8eZHWC8TZyJEpdRejSAFUabgXKH5WAyufI&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-32060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTM4In0.h5ksVsuawobZLamre5WQSuC5rw8vnNMfjril-s_cg-egqleegnC7YIMT5TDlYvkjyU4n4dKG3gwHm3owTh-_WbY_mBTO97cS5iTS8M-9w-tvOCObzgAmKT07gyeiio-wj9bnzhMzkMtnclB9lneKp1G540tkDj64OihwU2bbzpxB8QcwjwsjL74AJEqZj9NsXSzWH2sHF4PgTAhGhaUzZSfZOuYFDqaJcYsXh3G_LGIl91u--XDKho41fbmdLvPyLpzZA-qah_Hcckj-HW1IJt2T18G0k_vftJCJ0tneeCYmN9LvsytJHnL6d1fUMzBrtecxOFw6iijJ4MpwgVUFix9ontAhiwy8_Elo3N1eCz28HjB4bUfU9B1NrLUtfuSuzuoBRjMJnEP_Wrj0xyNCdTl8iDgQeA6Vnwp9FfpY9RQ-JniFoEPhxk3xk0jY2DpgSBuKPUXlzUD8lMRgnf5EudTZmoOBXmNmoIUBmj0HkWFzNVRUeh3mVttyw51DyNxCpvd0sXBYjQ-XZ2iLXvCtEw.dA0GU2wUP7Oc6p_bDilXiwxLOrkUT1TShvbsgKPIJrQ&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-34060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTQwIn0.C4PBLkhyi5iCrIhW57zBrNp-ylpav_dYOg-rFfy-NG5ZMGXmODnIdn95AWHDcHTMiVldyPV8BnpPa4jXgD1yir48mSF_Jot_AO0sArw1gQtMtTWvWr9JT8gDmisJgWf2Trt-t63GIToAoQDbFN6A8xLaQbLzDHVt54SsIAa_I5AO8HGsE12jW49cVy2Zo5xw6IxpD6s42mYaR7UaQeyZzmI-O0_gAaimSxV2ZZTaEdBESHjR9qelHA1EIM_LHTdqeFEWt_jOl5xWYKvTpsoh3jrjY8rovEEymXFIWZXLrSSsmEhseN62GGvLc2EBIFYFHMVoT22HaAfKgLzKhAWgpnbElKl9jyd5tyjLyMYnbqzbg4vWY3QO9bQ-n75AOh8MfVsxmVmhGeGmavRRKoQYzdEGKf9wpvQIwl8YlQRQg2yYDSBQYn1UCmqAjrTQnT1J4fbFWgT8LgknBwYlzPNi1whRzGTA_6dT0qDwxztnc1mciZ5eR1LLMlN-Fm5926guCvYvdRGtkq3bzHB-o9T2Iw.eFfeBXpHDY1diMWCos6kxLihsOW301EKxZc3LGGm4fs&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-2e060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTQyIn0.m8HwVYAEKJT9Q-1qNOA8UOqj8koxp9xbFlXKWyCQb9a50iMPQZ7C1nyO7oC6W8StK1ztXlurMCyEqU4vplDhMJTnpphl9kjk8BjWf3OT3wC2Pri7yzTi_8c50ITNDHeaUHJyMCdEY0XhgUD1hxo_lDgT8jUQar7Kr1pk-BWS4QRlHLkAVm5tyBEUvFed-T73QLHch-_wzsZIlvBciCEwyPn7mF8yqaRJ3Rwjx6MxLKFtFV2-1vkN8FytXxatntjas2OKUI-RGwNKH2z2bl3nJWSA4heidbiDYkg4Z2vXbg6M4Wr0rrUcdVkETPDRsM8QwQjaT4xGFHMOMah3JdRB32cPnYBntTcI_vskWjeI2qhwV57Nf3LCOzcrf7XCOC4EA7xd4_pwS0QnobgAhmyEa8oaE1K2-VxBXm4W-gHyO_meT3NQ5gqQnF09iSEq5w71X2kZfnDrLw-a1bk2cLUA3rP3BqqKjJv52Y5OgznFFwxe9n0L1cPpNfAHShkBVqS3ku0dQ-hiEyDyOCP4dtEFhA.5fHmlYAcPuAzO6B_zftaw8mjXDvUfeHpxXPlnsNDvlg&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-a4040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTQ0In0.aZd7DnkiFTNNJpBmPaBdJzTYZlsTm_bqDdtn47w2lhY4FqLDmQSpejElhmRE4oQE_Akl5MyfTisI4j5-ibP6l-Nyi5sdAB9r0TFof92xDUW4qg92Um1MbD1ohGgIxDhiHV9_X6vTctXl1UQJd7PlKI6PA7twLYUOVlSey9ZR2M9okifnsR7DlPFzEAa3DL8-6gCI9jnwOa8OLfc__y4KUN7vmmCkSXfbP8vlcBOCjMV_Vw_uASrLcHj4-5YBYsNAd-RqkbfDkfrZXl8DkagSsTWMnyxqQsWb6pIeSn1LsgGcK1EiHXSxHiQuUlqyEs3kIsXAUaaAjPVAI1VjTcEzy5UUGXGdWB4VIA5I-y4zYmVi7c_uW083Oy2WcJj1WL6s6Qllq6YNhJ937I5HsPBzsbu7UMTUub8e9dZnZ3C73kUc5g9qsHbnb-M23eqzhbYdSDxxtiQ1dmp7T3kaemqk-eMntpXPigxdUlIaa_1DgHDyF4Pzx5qiobR6Ox2hnP1a_S_JFV0QtsnoGORtmNgmgw.Cw-kTlC8VX9GNvTxsl6nL-QN0jU0mPPVEZxGua67Jm8&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d0050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTQ2In0.ZSAy_P3LcAohWNsY6NyXEMTRBJhr2Gn3QUH6Dn8pX_1eg4wonboy9zO52lnvhMT46gsfkf1uZ4GeWkAk3Sl0tN4CRCfSrkB9YLV-0iotlzurEW3EriIGmxHeHyTFwcdLL5pY6NwRwoWWYdFjB8N6knaQ8uwtXet2_qDBXphvOAJ2sJmzsLN8VHw0GDuTrNdYvicvuMoMJXfIvoEiuwjfTDCQMZoRaqtlMMe-TwBqCHN7q4nWLF0zkxM9LTP8jBnZO54w_HXnuVqql-Z0FXfJ9Gdlsxa5ev-qfeueIgkNEf8S1drDvOLpJj-7XLFeYSKpXQyPq6fLX7mtehoDJRRB2r9dZLkuqDam6_Hz9jCmrSBhwBLGWIlUdI4BExqls2MnRtpcrnbnfyPwIxDAOdj2rjNWy0NqoXLQTAsXJmbOQGMr2sYhRiX2dyu6yHLleseJXNGvP-PLRU-ayVMyLEB9XZqrtp49UcRDUjHLxOfhIAQXDaOl-rCELm2vvg0t2A-7Dnco_Zk69LPYJYO3sG20fw.s-piO0r6CHSAfMia2eYjWBRliJcKckSqjByX_003n-A&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-3f070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTQ4In0.oa8r0gFBaSZzzZkV8Eux8e0EEJqT6iYgdETZExAkg5tUCWErTz1CCzxYLWIFGzCiDxWQbozEVNzsjKOu4Og4w6mnyEgTTm-YphthBfgc6K5-OXxKZeUwH5tJdo__CEKWI0Rzbs_Tfvuap4d13O60yKOZJLA1DHltwyBo2eWkkg5t6qGTw8M0ucVtGYvPqDzCGspGr2ityq1ifVbF16hiDT7ZijhDIrE6r02iib109aQheXzZZI4LGWX-uDfSUAXjxpM6oszp1T48LaokAWTHe7gYol5t9UGoBgqMGxMLOryXvzAyOQZOp1XPIT4ErYyLOxXHkRXvdBNuZW4yWK5anb1FJOx5n51uOUe7PY6X52HxBU404L35PlxziMVTvkYGLSWJnBaewMKAuWAM-m_DgH5NXNeGUka63ZUk4Mb37GNtFMZuKEpHsz17Wsn7tILEI8AWUBRFffnp9s8A1Z1iDgexCA70xtU9hFxVyG3284lsQ7_61S1nkLAwsxsmi8whvUKLhQJwPq9C88tJbeM3nQ.E1VWxChSzYHgR-jrI_V_daSvI-UqJr3sqzHbvgUPSak&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-40070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTUxIn0.PXWLwzyfViXhEviTUjMoo4vrNPlxCjDondGDjiPPvriX62A-WW9FcVvtFNwp6SXaWGnrqCg9vZZGk6RAnS4DwemJ4-838UejczcHkMuolR4oFb73HXXx8xw99PH-7qmwROc-odUK2Ti0yzj3nrD5J5eQ_qJ-m6KZ5MYDrUzfHlTntsB9GNwV3kShbfQWIIkW1vrN4Qh7BSJ6CgfHOmRtVEnxBBz6bEdjBDzroWYo-yP8VLmgO96FWcpJIDbWLKV_JcHptx0MGKq1Kj4xBGeJUShnyKJIqhB70KTzgqj2vpj3XDNFScmgwZiOtkrLeb6FAoVK20mCwo5ON-NnqTJBw6v7GxjGJwfJI17DQH06EoiGyNWQVoWysfeTIrONGDWD9kEl7oEjBrTQw_cCHKRkQU5OxNDzcEmWuMSQsaRYvPgftsJqmr-nVl6mACEGmsWvaqrqarYVev-2c5Dcx_4kfryz4TGh_iA9USuV31tUumeVrq0GsGsLHULrFdgXsbnJDJ2dq9e30zu-5FEVCKBk8Q.tcWDlRysmA19rYyOq7w9Nu3zCVYuJ4_cNr1w_jKRv2M&amp;ApiVersion=2.0</t>
   </si>
   <si>
     <t>https://s3-us-west-2.amazonaws.com/10x.files/samples/xenium/1.9.0/Xenium_V1_hTonsil_reactive_follicular_hyperplasia_section_FFPE/Xenium_V1_hTonsil_reactive_follicular_hyperplasia_section_FFPE_outs.zip</t>
@@ -430,7 +430,7 @@
     <t>https://s3-us-west-2.amazonaws.com/10x.files/samples/xenium/2.0.0/Xenium_V1_Human_Brain_GBM_FFPE/Xenium_V1_Human_Brain_GBM_FFPE_outs.zip</t>
   </si>
   <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-da050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MjcxIn0.yen9attXNuMYEnqXkoyPYTvn3msMagmAA4LBqL698iWIklMK_G6ooTShtNynvdGbkPQBNEBa_zCecxykDGZx3ItiN3He3oXCMwC9od2OrRFNj_xlD5hbaOZMKLobSQ23tQS3jlxXhkywBYGgVSfRb8LX6592kBlAf1vxpOiW73zeqFrGDXMesY9UnHUM28Nsv2fG01oJcqE4N6bI04HIAtVroshx77QdI-kRTPS261dFIjLhXBpwsHqliXPYRPFxHs7hxmlHw2NBjHDMop_nLhpXNBwCi4JU4M7r55ZjbDO8ixLMrcvYRUUtBEXUAzmo7bUtcdHUCB_lFJNODsKmNdDI9d1WMMqS8puFhsRMWdqeDKQk71ht118pSXQTAln5YBk4KlTnCL2pPiQuiA113TkJfiIcueK4Fmrym-S3SX6ETYNb3tnrn31ChJIZM8D3hz57K0m9eAf097Ux5FPpjntviwTd9o6vLpLrA_iFgSlZAU7Puga7qB2gg_ZdnPkU-gvzBaOXT3qt5-VI5MOgtw.uOjrU6Gi51t-NF8ur5wtbROwUa1vSmLrjGksfU0cdA4&amp;ApiVersion=2.0</t>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-da050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTUzIn0.T7XVb_dCPsES3fjHVRzw2gOh8O1Nnq1N0Sn2YaE-9qxAOjpuSYuyjLn2QqOoE2SmO1BwdcvAHqp_ZG4lmsarXuiJHmzRT7jaBYONksXxvXCUoyKaNV-a5PItiJsRf7kLTcpUvmw1U7e5R5Dci0AbcD2ECkPVJWTrIvAjpMGL94pE7i0K8liW5CN4DiGLtxitE3Vtie8fL5DaahC3F7tzzDfwy3FMdenBYUNwhB9uz0N1HZSUI3JdXP_2oGLDQU1I16mDsOlzK93GpLoDOHDbhtsH4ZNLctUNIMdnjqcH3M_N-jjg7djgATQPC9aUIft9NdiiRSFuBZWRs_MNRxVTHcPeIjC9LNQuEx7TmB2r66xzS_wE4JrW_iyzedUUVOdnA4v-iMJAVWQ2vIqN0Y3PFRq-IUAJLpPHW7INM-NNTp6xwL4boSB6Cr0hCDtR2LQKptwXyhgkktPsBSsYOuFFulsiQoUOsc4fN7PDVmi_mMLJ10Pg_m-ywGvRRJpsJZYvOeF-s5c1ZzlCkLiH30z2tw.kaxGgVNJmTkkjROWkUJrVMQ58HgC3xm-cRfH82B59cY&amp;ApiVersion=2.0</t>
   </si>
   <si>
     <t>https://s3-us-west-2.amazonaws.com/10x.files/samples/xenium/3.0.0/Xenium_Prime_Human_Lymph_Node_Reactive_FFPE/Xenium_Prime_Human_Lymph_Node_Reactive_FFPE_outs.zip</t>
@@ -445,100 +445,100 @@
     <t>https://cf.10xgenomics.com/samples/xenium/1.9.0/Xenium_V1_hSkin_nondiseased_section_2_FFPE/Xenium_V1_hSkin_nondiseased_section_2_FFPE_outs.zip</t>
   </si>
   <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-85030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2Mjc0In0.c4PPbkYIT7N4NXJHiOyfkjK39IGH9q2Nk_Hm-PKrELhodeYG9VA1Oyuv_tPZ3NN1nS6b0_kDlgCXBvofxw1wyZC4vt3VDDbWljD-_wCc1of27p27KiCWqIJIRJhWCviKKSTnELXU8REAbL9A_4oMbTWO-Suc10OV_1CJVQQl4UCXhzjlU7H-gIzMisPM6CgzXkprwmSK5jVk7uGx94wrdrZibx5_49y_-bxKR5hvCbckFCSXsISSgykNI_agpsB86dIG9Zr5r-fGoiOD-gfl63nW2ZXL2Lz2GTic1fVymUeFF2KbzRF70TOrFAWuNXa178T__7A0dLd-bf8Peoy-Ju2MI2_-54v2MI2kl36V7xgOfCUfx4vxH0XQXJxSFGoxvsDhvDBbEKnVdRNY2vdI2-mZ22fA1VQzVC9T6KQlW6JsSGE-DRl1sVWA1suJBr1SK1Gjo6gBqoWQwrI8dV_HYhUdrbs-8VWgN2LuTm2iu-zkxZnTf7yg2I8AwUj68EvG1hBclUm1vFnURGF1P2lViQ.8nXE-1HaVTSbRriskewHtgxs1f-ZncqlvR5UAJlrREc&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-86030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzA1In0.Rwr_eRkuGvXwHxKkr6nG36eyBQWDR9Ltk15wPxETIxloFlOVFTLecXmzb2aUktbP-mJD4n6ELwsy7G9ukZQQ0Dn0aaXiyMwTb-g1g9z4_i832zGcDiiNmJI_LBmXtOmPsywJcHeRKTJCeojDIdDBB4ATNwk-reagZIju49EB_3_DWWaKwJhVB__bZtQmJZWlmxAjiM9wELqQ66Q1A-iUUPs_9kduSaOs94m0AG8GO8kPEE904chelULH_jyHTlYmfd_JM53O8_fTdMc-S4zwM6_Zd6fyzQdT2UkY4ngQ60fOPkv4Fqe3Jt6Ft-YUyWbsc1KsKZtBFhvkKXfO2uS-1hCV62tsjCKYyw4JFl1ZgxHMGrkyj4zIQMyFqzzDBmxFLk5Aydfc2wX6URWbSs-OR8MwcRK_Km-kWHN5FiL2oVyVqaAu-y1DnAI2cSJkLzbNyB81zwzckDKsoU8upyJEO80SvbMmuNH9cPQq1Gc9TIlynC5mJ5BKkVXZzJFQNNwvkx8SMyQ1t3Ashpjbunia7w.yMG1Xx-kgW8mZ48M_na7E0uZre-rRkqGeiQq3J9uC4s&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-87030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzA4In0.g-M3pKo1vPTFdYn93AGsvM4WLykD9NZTQ_buGrgLz04YBhwSTgYU4GEqkETl727Ki_NTQvHGuT_ySOUzQ8pp_N8WoBsjZycjwHPq5UocAB_yt9o9JFnVo2_J0tacsk4oB1O5EOqmo-4xoL_bfEOTcETfNn3uYNlsHE4-6BBi2wDwGP9dQ2RUVW1wlyQZCsWajHlXIDKgK8ttLLz82DPCMo-s9bJ8YvKMZpZF6mR8yHTcA9szYvfZZFxUktM9mUMtmMyIICEWswbQ1vjhPYoom0AZMiEj132HXTKlH1_R3hwhq_EZcsbp25O8-dz5r5bLii55FdrxvXHg6fCp-Du562rmMqZ8sBZYBJv2G8ZSn9I6MmM0v7P4znMG-5MomJgYj_NEzd8ETYvhBRjEjYacRa8UHP-z2i9wFCYTxR5jgiiBLASdTSjbmGS98mhpXtT2uXR9s0VutoqhmRGcgi6CUJ8djvHDCEivShbwsf3vDAh-4ulGNPstNQlocWLo5fF4BiRS3vF5ejoz3R3Wt8ZNlA.qg36PMeWroPsVPmrC0sgVbabgouKa66Ft2LDYDvYxI8&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-79030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzEwIn0.jy5QLvti6LltHn2itme5uKvDWRjHalEzuUzf4-KJ7A-jxbx1Mvw67WbiBOHT_LvU7mEI8SEeF-k6onQ4T3J9SUKy-PkC4D6ULgv1aVWlQ82uLEEVT62PyL6kbmm8hrpUiXiLeNfevrxiYi2QmnMr9SBzbxC0FgY5Hw9FCHIyniwV7JyA2cTOO-Iuifet9NvGZgmrQMypu3-BCX70unJJSgGNIItLXbonVrWPLgiAZ6H8mQCzNK6FUuQMAJQYMtpPAbsS8ToLVvK4_hupc_Wqp9nfGkJFIAJYB0WpeVRoJ4u83y-rD8Ho4RPI8IIhNA5FZhhxdJNznz80pN65JzdUKlxFvPw3RQYgPMFfujIbGkDYf30E7iDhkDwlXYU_YpgsL1qIP5Gr4eZ47hylxk4bAPu_QcdRttUS30b37RlYKjIGnf6-PWYqybTZhjsAlNM1i81knVkBi_NzXvxQhbVq6DPR_9kayNlLGZXsINSB6baA9qg3kyuj9bVILOOycVBNeqXQD-fTIR2LGx1F7O9RGA.s58wTXheUncC6Pm51Kh58kI9FamPuKDAHGmjkZJE9jI&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bd030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzEyIn0.GAlEbP4gHRg6RlhR95h-KEXdZNUoiu1eLPWIZUNDPgHN2qCeNAXWf5mtj14TTGp78MJVycJZYq6mVwi8gBwGr3SW1YfdZLHxkKQ9TuipOGGl4pDzNolVwYeHo6tyEn3EJ830Ej0B7fWh-ybsDfd78CPOQX6RLI1vQQaMJfLcGnJqt-RO15se0yLT8c4kDavzL4chq6I03BNtY85jkFpE4ebjaK-fxwLu5z_9elIrIoJtZHyr2M1mtn6UTB1ULsBcNayR86AD4HqXSO1S7pnUCGNAjNnLyB9gC7REYGl9JhqVk8JPrJ6lU4CrAVHVgjEmxci6GoofPuLTgLfikfRdyQaBUrAoCD2-yb9-LmYeuXDtofL7mPdQvIXeMzJ2OmT7E-NF6OGecOj6zjPglp1J6DlW10Oe315Tt9Pu5WtPI5TFGErP6qXmno2ljImqNRQJ6-OUNaqYdzNhqpN601vli8YS2XEmUSB8GZaFwHneMmlNPHtejpbUF_hAULLrDcIPs-hF_bj3gcVmEQnyQXZBjQ.ziwn4J8gKfm1JPE2fEmzbJZmkB-1jz-x2qRXmLal-Jk&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-ba030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzE1In0.l3fzrd4Wknu22DML26Yr2a2cTU_vbMX_Yufh-BskiwRdHBHg2rapAcPwwyfr76UkHJFcVR62leCqRjo0yZCY8SUrNWOsf_5zsSnAEwfDSkdj9DhqxMFRA56cU9v7Z_FRhUAv22eFph1X2l_fLO1A5c2HdcWRWIrswaDX5fwUdE63A4MOaAZnu9bwNM8g9xZGQFvI1cCMVCso3HWWLTu27oZuZ-nBD92zp26M57ycPlbYYV73vS9ZiOuG8Lyw0bZe1VV5MeTMwUWx9_GVdhvieDnefbZVzFOiO09h6jfxRQ3lRxGMy6E6g_8UohnO_1RVNXlMrWHZ4iQLK9bvavAtlZNQyAwluGaL4rWGzSRYnFVw_gx7c83tM0FTcsDH_JHcLc_Co1HoOlc6kTDsHVOXXcMDMflhvTcvzHMmP3IwNH86WnN3fZ2mZwnkVk1gNjyL4cqUCzad3K6l59PVoOPbjPnlcMmHoZigFcGMa0gacix_M7J3rokmo5WI_WHsi0DuPqm3NRa1Dz1LfS7GvSNGmg.osG8-G3_OMHPvE1vIdouYS88Q6Hw6FB2qJRcCmBgZrg&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c2030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzE4In0._zofgaS9P5RLf6n4JtFOJmMbQsCttIMGCxxl9nuKu959e3dFeMZBytcaLxyIX0cmRVZ0AeeH_nfRkPtnpmVvjZQ0kCzebRIDhbv2K0ja9ujVS3qzLlD26hBNMEbV3PS9nIQzQWljKPGl0VkyrdR0ClH_g6TXpHgLDbdhiWRIfK3QjZ0qBpybIGtUGXsqaAe_YuxMsTawLyAj_ToU7wDi__jR6ME7Gh1qtlewr9kGJUy7KYBgQVDhJg1HRzZxFjTRyVClxgGflLJ0ajEe8H8TfGSGfCXEMirm6CF-3qsJM1jvtbHIaLkYk2QOl_Ypdm410TJWPfRGvH55UokNwK1kslVBD4iHC6aD9lyrgwYGTRmnl5Qw_50jDkUPoerH50gw0St7IJMBCuPhbo98yzRgTKXxj9BlBfoymnEhqueoTIpN2a5bVi37oEIID5ylhp9MVBGkVUHOA4-h2oLfDmHsuOyqMdMSUIWtuti8lNnfUJkVdMZV1fSZ6Zwg66GcOwOyI6M_HWzBQoHq0X21UwivkA.z7Jr-uuJKI-ng5vC3vkEbQ3El7T4S_VU3e1rY70C22U&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c0030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzIwIn0.AIrEGbQRED_hzR-sdHwtV3XZN-faXN9VYWHN0gShP0RpEJmkhlpb-LY5OwJFaKI9_5igILvO-YOqUD9z_aQX_BM-1PvQ1uWEMIAoKio7IYhiWZaVEhE7elwqcVl2hzzKhHZd3Y2ptPdkRZip0nwKhydfoUaf6CGeTF_4vfg9noYbzMQxNwp_pCKqQDi4jFTEO30eClKMb-lWMDIEWI2PD_4oCdunxp4eX9ERTCf3crCi3FbI2VcrV0O9THLFD7IDtjAky9crCihNw7LtaWMQxsfMuIbRy90v9U7xP2ciQvob86I5GYsdE-J9_G0U9euyW6BLGeOPs9voBPsgRnKtcSBKnS1XbZhiontgAA2GCEYxZl407YekVMJdmmHQYUzh_RbCNLgfbEurnHtvZFpBTaSiukO19-dJe0CA1iMYQ3NaSnMbpVyZLSBjrnkv5unETC_bvpyC5y5KskwdUpAYzWObNV4rUoM3tWaTRedcSJ78cSw5tLoVV_sUhwpT2s95J5eMWhd3ZZWCJ45m9cBMEw.P53kNc-1WdbKWSyDLDnrVM2Iq1hb9X2wlCCEeXgobbg&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c4030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzIyIn0._ONDdmtfw1ek1208Wa-DNm8XWosbdj3-LrBbEWeu68_6DSe6wRhQCyaucxMaAeSgGYdb6nc5VHWtTzrnK-wHFppgIEh6oPaA1UPXr_CaW6F07z4oGaYr7oIBxuyJudGnQvB-IRCdxjZXbkiTv8y492kJ_5uHR1nRGD9hL0S-w7lldptuHfAFoBo6lcIwuN7bGXKbQdZGAANXvuwe4_38FlssyQGUJEmhwux2UrOda2dSaBXYWsU5mZCWVnZAhO6YUlkg4H5TLBp-y00FpVJAb2rr8qlbo_LNs8DULJdhDUoM5fujccCFtOKFo4sm4H5R6GG2NAVR3ZWOZl5iiHgC212rdfvS-pej5gMYesSEMrWqR72oYTj-Y9E3hnermyTBSQFF88As7pHefGgv_BPP0ZUyUsaitOocc-6C-p86YS6baBkC4niQcjBkGQEB3X1i4Ywzedbs8a-KNJ8ZynNECe-ZMOzjQBEDgWqm0d1oOJ8gcSsuT0YfQRH82ayjAZhCcejCZTKIdXx-cCsoGhZMGQ.Gi-uJt6NKRyMp4K3gqHp_7zMcKVLIbuj7x-Beok_X9o&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bf030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzI0In0.9ae4_Oj6hx3eZu_syvTtwB8snDXqjJ95MQfOjsZv03-vWyVrxOVQnBJhJgiBJtdPpU_LCG8JENhzxEtTmRv5V84JGWhBLnNtu-n4HNlzB0priz6mYZkCkzTQHbN3AKvkPz1LN4zGwsSrL_Y59TqqWGd9m2TAs_MXAzLY_QKIgEej6Pz3SEq32A0Zd3ychfrZgpjEwYPfDEh6HsoME3j8_F7s83c-BHDRtkWAo3OyGxU259EBbGu6Zs_dj5kYUXiDrBXbBz0ALztoJsw0xwciM3wqJZER7RYP00Ul-sJpSKQhV8hGVVe9us-f02bIc-k-zTkd-1VTvNWU8O8IGU3T2lNwCTBYwrKotF1-WFui9gx48HAIbgtZUxWB5GrdX64yms4T5pQwtONtEJbs265m3YNyvvKFYmuHRoEM8CAqDggVetSA57vT0Iz9Ws24EhBWi-tW2RM3PQJOEugeobPA4N3iPdE3OYbVR1OHPKFKMODH_UjZD6SOjtIpXEOvc3_JsEGkiHu-6N7PZfnVdqCOPg.O-1mOjDFWP2uuI8GIdbxsrApT_uoostTwiRf6BV7X4E&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-b9030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzI3In0.RCaaYWCsK1UIDvzCCsSUURrCQf77fy_1F8_ECcgb3DzDDTUVEBfEvvkv4LnUjEJZ7ix7sLvxSTmQ6cFYyXyKXP7Il9R_Wngm82RlaEAXvvMpQeby7G_Cb7-ufUok_IfX7IoGhVXdmNU5O_ZjdijazfngyTEg9t1RYvZKOmfjRNxu5D4kTT1bPDuiRaLi9qdePzOF_QkVaH7eKZrBAc71LGqHDSdXGQjdBRiWUIVymoIHoDkImohhXDPFVeVtS7PsjfB0PNYk8QPAN-HW_49fkDLcBPh8Yn9d4Y2xh5O9873Bj5C3loTq0UFGaUv7mKByDKPO3ES7w_5M47vZUCGSX3pJSxO46akW1KThwqvzlrpbn7ZHR0mkSM1LAwMn6RBVLDeQCiWV_TzekL33vgsM9wjqtA7A6xEToDTwNQrjzDFsmiYShjfYTW_wvWf_TKE9J7Mw6cdHbnuYqZPr9xloysaFgeud83Asq6iD_OPgvNl2K9zGvwRhbJs1bpSoYeKtYZYNs7LvKJkF6-hdMb4LOA.MRWSRu4xkzp3F3AKeNmen0KdUD0rIUWXy90vEkgFoOw&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-b8030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzI5In0.ZvL7Tp5MsgAsWRpEgLKwAgvjahseTz9MWd5Bc5cKhjgZHzcN-J_VdxxUPRLmP_EW1jNgMcOQwUKQ1TZ_s1UHJAGfU6LQqhwGuQVfEfBihLOj3zBs8JWSOP3LwOC86P3aFcqodLGtykoUKLo-xJ_3GQsOs8rBOZi3CpDR4pLaSppJQFQ8U8DbsNbT6fPTwb-olo86000x85T1DJNgnF3QjxIdho-xhX97vMEXEQEp_f9cE9v3kcN_uK25h-Jo8M9GWxSpumbg1nkne5mcGvWxJ7ceazCiWvTaIW63q9EQ3yatJFzsBjVPHh4lnBgmSqCv4bCooI5o_aXgCMsPbKHeHpt42ZibuktIXWsJpFUaPxtlbmbYfusY539-_xIVCDg1VdMRfuCRkSZPH6hjxlfzIyE9Lv-xBc3xiw5dA1rn3yxkZAB6UQRuuNtBvD6YK-30rKLX81C82TrFxvaVLV_UAT0a6UGRyyC-jvPV7wSquSPRFcJw-qqkKDfmeZ677ALZIWawIXNgAxNCVR5MPU6yQw.NFOwyEMDZOyhNaWSMgrkRXmhCt5JM5Q078mG_y50e0c&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-ca030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzMxIn0.YYGFEr-EucSRd4-WZjL_i4MoMIlJyDaMe1mFpaEZEs3w2sPEdG--gGsHbUWXoneKzDzFLVHjT0VrZ6k3VITojLOFebAZocUvWZhMlryIYPlIazl1iz5UzRZKgKOIxgqAhV30cICIdM1N_nNIhP1t7Q6OEy2FpqP97ai7uvcgIkU10tvbVY_i8hJyXz9qvbwPweiuwMH8YJ8nrlTLpFK2MCWZaY1pzL1i-wmEfnOrfwwwH1wp4itGnE3a1LeYw38hRiy20ssXSELvfM3BGqeLCzLr89PBP1SiQOlSRqqhnO8TXQu5tNCvjTzHymxhuGO-4C1POMwtZTDupx-qYQBOdy_PvFfjF4NhFefLi5UHXUNtiy7cp1f844f79dP2-_7mM_TY5R6W6UCNZNjWIJnIvBe7-x0DZ37T3WmnNO73FOKukEzsUoLl8pYLsikm7IaP7uYleH7jYPbcF_EFbMy47tuCXIthyrP36nohdOJCtg-ciCRFeKMIaXXb_rEbjdm0snJV-ZYF3vET-X1ZjeIE1A.iGRdsE1uP4AK_u3HjicE0xL0c3rNOur42_4DX54qAYk&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d0030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzM0In0.XtMN8k89qPZ3QjAnxkSJ0Z44EFQX3FiLQ9nrZ9Zok7S1i1O5PDu_8LHDj7I0dw1Qdxd7IB_qtGzexfFrHJ6qUPcNMAqWXPQa__WAkiqhbGk-RGm0fbAMCl9K0rV4_gmTwtKuf_I1XmwHaqtghgBMDYr4w8huxXj4VmdrmiJzbbgc4ap8Wn1E0WIVquiQX19zxoqBKt8s0hec8VgDPFiTW7K_CMLH2zQEEWljBRHx0J95M5PlPjoPwSYGb0V0NvBZMzophMXq9XL-xRYw352cdjtNtxto2_RFPMByQtfho6YctqG0DezSCT2t5ejULnzqZXPJTpvksz-d_JIbHERHs56kY4ci3KfnzPWxWbVzy1VKWcFlBMpnz2jOP_lAoeOtBdzaXNADAY_hA9XGUNELEJeLw-dcGFW534K24TdpPZk4elzwPJlu3mfLXBKchNbgqREImP94Bce0e0gAMn67kLKc_sdFVrB-msoDiKuL1TOCIcoZ21f9WwlJcnbm-ahda-Yt9DHKujfZIF9HVdBIbQ.4n3g33vazQDXxXK1SJ6JQ2zgqKrCoxnfDS_dTcsc9Uc&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d2030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzM2In0.BXDM9kUmIShPx7EJfkLclMCtaAyEwotdLeXjlTJ1gCz6aIYCHpInLK8556FKhLvRvuW-sYBDpCBSuJR2VP2rzCpTPCzGqizVToIRT7ixngMCeYaQL0mz2CJPkiOsc1MWRdhbXHhQdJwOMxqcGebirU_xxvkQY1Fu3d8BHawcFIpg4NvvQdFnOBZo9PdFDwi1y1B-HiYHHlxVyfmeO6t2eHPwU6TfvvNVbFJCh7wK66ovMxJI-RAiq8yk3iZeoO7qpcEBgtyskLNVqpnFQJuXqKM9vTpewGiac62dlICIhyxUaQDlQOQ5nmwq-n1ctBlJMC1yfNs9JV-LGTSVz9ONgAsc_BwlxbqSvoyenQflc9gSBj40_dPTx-1GtuiGk99k5s4MFqwsdmHWQB7CXKMJfx6HhmTBSlF7Iwv7t-3ZIhACfOtZ8DWYcDBuTecuGPyKbcu6nmhN1VB21mmkbRZrzQ8GLFFbOnvnHI76M7hw4aVNIsy-THMY8ovZU-fEWIpg2Y0n4wH80KleTEI_COEWxw.y1nff48wV4Gb7nh2IWrOFNMNWJzhr63zgNMTYAXy-dE&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c7030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzM4In0.RaKCg4IqIGTTG28BW4S9FzI0U1R9ZApfshfy12fJAydM6TYWZMfl3HM3jwqDOx2ZmCntJntw8OwynvliASZqwsSBiioaYLbEk1OuaMI32s_L_uZItg4J8_GTliAkfpiGW--MiFWsb2XxQCRtkzdHO8reHAeZu8YV-aRSZCWOvUaj0bXMUh0qVtKlIAzKvzKbtf0ROrrTA4uFO045foga_RWnZ8YSDMEbtYsxAwqNvHUJaWjBusq3DmzVnWcANYEnaHb1753Zys_n41nCBx9qGtSSj-1FfspzK8JTzoW0HuSdWV8mNcOdorVj0D31lAq7_MIEUx2vBICtthPbO9o-jv9J4_X-r8wMWY3_blFSgQXahu27K4xcbDui3h5IhjUg-ptGpbUFRRJd4YKUeGgLNFGHTvMj7e_vP6Ha7ZHQ-noMym0lNXnUldN1xAGklCcybhFqOAhOsFTQDXEZAUpXnPtgTK_0nEZ3ryHSFBkx-sVqQh01KwXfMjcB-9B8aagQ3kxPj-DJNsMknkSitUnFgA.wov7J_baawtuLsQ1UeVj7zg_TWRqs5zn_nN6gSUjUQ0&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c3030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzQxIn0.uUvKhXH0lysBTmdngNVITl1UGutZrscnDUQbAHzjlrXVJtIEdYLFJROPRUh2E-xFe_JiGZ2oOp0q2DW8Wab1gMN-SkgTpJD2B6uXQmBpKCZON0yxKUXpqTVgpV7u8qMPvJJLzlY0OmI3W6tHAyyK-WPu-QV1N0_p4P8oUU58drSkBljJRy0qbH0wC3RrRZSfIPsVIc1JFCEymosBy85AiVmU9P2jr5lLzo26SVqqK3Dl4xX9CzXIimZx8rSRLi38NR6bzJ-vnFt7bX5ZtyS36se6DLwiSqC0naL1_itwqJRolmRsHhc26N6g54tq3IkSWMIZu2E5FBDmMkq-bzD4HQ85gu9HpOLnmAZkYp9yohZDNoharH93wA6KbWc3TzT8meLwNDLKZeVL6UYcI8W7AvgnQKcUfdU99EUXXnWgF0RWNg4vXab21HeqstB6Kb69N94YW5uJ4IhAa3Tlivmg5UHuCByHBJEN1PNADD4I_W9yxCAUcVufCvdHDjGVnFEHxs3lzUT0qE3XXvsD-Zp8wQ.516X6Qm2qXE2BQJZOKU5iWt4r_KEASzXoSTswgQqWX8&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c1030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzQzIn0.kTfNQh7Tv2Ae97I1tBh46M2D8_KsKdpyeVjwasgQHqPY8lRXOajzgKeYFexpPPkqxzCizIte2Hnu5NQQ_GbCy27bRVx92EcC-02rGUwVCqjeC5lH55zz4Rki-pKxMxYYXgDOAQd5c2nRNsOTdZ5SRN8CVSrsAqixPdrIVSThcpfH8SqSSI-b2-QPlWKfgEJp_SrLNaDGmgi32ZkqdBN5YVZw1fV4wMK2xVHkTwaxDaBuKJJDyLHts3WdVJNaP6EEzD-zGXN5pW3IGoGpvopzYgAgYpqFL3tEor0DLDQbd0Rhd_BcdMkhCIMZU9lVJoZ5stksZv90SjYCU3uPf0sUyGqW9zljlc4U_rKs4FaYIdIvndcWzlMAiHs92uAEdi15PAXJlW8bbOYTJhcCoFU8LKtYDm9lCQKWtg0tB-kUKchceqgvUTJRoLZDDsnmbxtUhNT4jjszeBTVevHYrg81uWp-aXZHjVCp0HmQ7Vj-7_KsZhZ1K7ES4_oufik9OqcWiJvmGbCDXITkU0fyK5-BfQ.BThSTb5OZY4gFDBhX2FxaQEujFwZ5kZz2iYxXVj_yM0&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c5030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzQ1In0.Jybqn-ovGtCHtTWaerSs_VFDL2Flj8opaC4zrBBUtopmdL_Y19hELX8VgANu6ufGx5q9iC5Lz6Ixb5MlZn9yHKir__zArQYlS8_LKfuK0YgQTWAKRZJUVJnOC89JFy-vi5TxbDLo0lnSU9SGU--LFp1murGfbxf2MhLypVQ0Xdqm7yf5Gpq35S8N15NJqnolCdJQrALmhtXNQUFbBuT8xBh8HJlXbAqxtjxn109-6WCrLl1X8HLM93iWb6CnZG0Nr5cMKaDk3kFe6IW8Zj7mcTbgXIx6PFlwhP9kwQdAC8jemN38LCeWEfrq7bJAdsvPvg8I8ECGb_MOY6dflX4WDUErwddnowIvEt7UdFke3FWAQ0rkjdTezOzaWoGCq94FqKi0Vr0m7hlVdUgmaKor_mI4MwKRMnXN_GvUsQLM6HwBYtM3UBJp8H2GQEwQuJOHv6VQha-hOxgSi8vhLw65lnVU2OHAmbuHBSj9RxcJPIw6nn4j-AQcjHTQHy7JhosnR8wkVTRuAvz-WHv0T41AaQ.BHXCp5Tze-gbbG4Qds4m4JN8QB4X6JUC6CZI56Xowt4&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-b7050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzQ4In0.0Zb-sus1YfDxqCJ-wZPWPRHybWOWu7rrLZwo-Msqusqq-s7nVbZDN1GSpWDEBnQWfaxi0ccW5Qsc_97SZezhSnej5NS66rZvb09zFmPdfCPkBSPqks2tpOVeeBbdx35QgE8KXi9TmJkAlYLxUhHaYFtopyz9tPVT1gZkKG1strCOOvV8-4mEkUqMtXJo97NL15m-FbRkro0M6XnLQtO2rCiEzDiKcIdqqIcD6cvimHL_glsncv5fmH_unwHJ-fBL66hmDrLvMyjSbvTeALtHR2HM8Yp3e-oYMMTrhzHNJMncZf24_Seh0Dq5drimmObcA3wii2hoyEyJcoSwqfy3edTIYfhsVfkNT7SxZmfr47MZQumyD_ETQmvQ9AUlb0Hwu4vs2Mpua8KKWjXZFJ_bbZn2k4B-SgeHzU8tYtf6mPwSvMZVVqS710D6KD1I-KawJ0GzbBLT358B8rduE0w1XQT144zEPFbn4KiTfwQyUzdA49tutBj1FWsTDdcUYEFcYEi707kYLPG8ckZGsTnE-A.8Py5D8GPhah8R6JnSwh87F4e8tiRX0FRQsCzOzQZ6VA&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d5030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzUwIn0.4wW9mehHkqO06P3RFORo7Ip3CxJlR2CFrf76W6WDnaGBML9N9SQBESxNj9yzyJ_VzJ85mtCsHhV8QOtnax1xGi-hPCmECApjUhnxrxeBczDjyzcAoX43dLu84Cy7Lh3npBuzjmQNpQvXRG9mzdE1E-3M5AIW-qYnygC0ZpBU_oPtO_FLScIUq3PklbVcUGfDy4cnGRyQqxtv0bMxpQkvTwa_GYY27vWVPyqB9iI_9QO7jvzshQUF6_AlUWV_-vXhmSJwBk2DPep3__1rh5RN5zEfpH7YteIAxj4asJGsyVJYdBYjfXlfosjdXnMBoq8v61qvFACV8F5w9IoHrQe9SaHJskvDpJHcvO0LlcCoXXusXI4O1O4nqLJKgs5fs-6uYRJgc4VJVyPwZ5CLbU3zQilkpD014kjZgysyG7Wepwiaikw_Gxj5f35iL_-ouUy5ytqueilYPd8eWhXCEdxjECukOFbc6aqgKCevbktuzXZ03TBk4F7ZiVo10HR1F8PW4hK04zf60tGCwGp8pokpeg.JWuGmontKhuymM-ylx11O0uV3TTh_kriQgX84gytyTA&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-be030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzUyIn0.VDy9GWEwOT1ltJhFDr1OkZoKzuR1tNUaEmLiANHf3NdNpDMjYGyMgf8__Gb9Jfc8FwSNYIleUsyE4GrPY7fYjqxXMJmKSc9y8Wd3uj9ACQCDj2mKvtSO1J6oKyiR2pd6998-pUqo5wteCfT7chG9xQMR8v8Rj29mtcX7YPszbZYJcaW1VOx6M9pntu7NC9HpTCD3uiujA-v05yyKFYtL89JWDIKZ70QQGv7U8iC_ZACZlzIA2gudRyOhOqkYeACLlqUlOUt023u1rZbwKkWTnFqJcD6urgqgTWJwfcyibxUTaOuZm-ZuJ2JIFAwZikHEYTq-RotV7tyzI6Npa6YGcAPfwm5ySj-6mj3CPBjd9OumoDuiyY8Nd3S_bpjjXJphbRphWBbhy3LIliGdtbj_0aTn_FLtoS0iywFmFsjoEkzKkXdKdwo_2ajjSoL2PSRqt-YJlFA0-Ba5Le8Ym4YJ7mlo5EXjbfWMzyyFwEd1BJcer0ZLofnBBtcXQpqnWl7ya-nb9T9b-svkJzoQ9SbQJA.-_yeBJYYIDMfWhHCuC4ge2dxmApknnnmlku2r5aHP94&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cc030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzU0In0.b9CNsEfTnP-vW7slKFI8fhbhRxvkf9XY1tvuzvC3SWi4yaR7PDkY7ZLXFcs-rkSTZqG5xVX8AkZAzvIL7Ga_OGf-covQfRVLPrQP44Vvfmze7E165gHlAOkjVNQR734USghLbE77FjvWD_2pQiVChgjQ-iNM0x9orFvjQHyzm2YpK_UmmeajnsP0Gqd7QJraA_0rsD4UpObio91zVB6mxcZ-H8TnREBdYuPdoadXuTp-nsW0sgMPeNk0C92OiFPttDrZcLcitmcMcdM9hQuhn8AfA6t22UDC4PFzmwqzkqKprviRF19SbJbvXFxOBHy8DfCgQlCaxqh_CST6C5w0oX7jY-uJjDbG1i_IGjfkez4Gr0cDU-KTuQniDUEyEjIYpe5caugBLU1rCCLsKaC6shwSEMK5SXmcysAJIfAKG87I1zqVNtNNSB9Om2M94gflH5cYV9IHG46YlSAqxz43k-nh-A0mm6Aqwe3NH93JsBf4IR_pzW51jc_yYFBUhNs4ebeVJNuhw7FFdGaPW4zgYg.JiUBeM8EXhPeHz-rFpZBtcnZ8Q5vmHJSTOuinILxot4&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cd030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzU2In0.sCnytoC4Khk7xUaLWE8JlzX8s_3jwssr3FXBcGm-ck5-5_EWCHQL2GLgOekDK6rKXt6duzW27fKF8L-UgfzNdFJjeFEr3moO36VTO33-GA3nmqtuS1u4u-QM3sJoKKKW6u-0seKWj0pCaTNcZ3Pf-easTthTyOpSiA8E9Z6LzfYvG8abXxgRQ-afkcIQk_MNoEbhoJPPn29FmOGqrbMv0hnROU7zP_PslJhgz3p1fe2vFV-FZCKwlbR6uOgStxf905ERpmtAihTwZKzFo1w2Xjiqkofbfl1spb26V1c3sddjcNS5WBKSBtcGS37hR2o6E4_YHnOJrzKlTwTHVZdFHP3sAuPrDQs2gtTCDjSDeGIpSAIzDy32lR7crYWspIB7cuqXEl3tqDkgZgf8J_U3uM2nQHhFTCQpGQ3_VLVdUQvkLLS7mqwjS1T1Weqjm8i39gWL-ZGukATi4vlGs-oXeXRW2oRBitUvOcQ68chm2dZhCELCDoPioHon5jzb15VYfSQiYh1435a6eCNb9qDCpA.DrugIBR_GNy2oh_7dpRB5XDdr6dG2ZkhBHanzbgegng&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c6030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzU4In0.__Edr7RBmyqWyj9WejEL8alVT1B7boTDVzyeHfqXCFgcp_GMfDB8GQaQqCSa-iqjKOu61nl17dVr9-ufgCOQZVUsmS369GGxB0RLazDloUpsRIB0RSZKcbYWyifQXIBOc79KOx6Tq34Y-Cll3I1doxP3zuUT4ifREOpNgxOo3VgI_YzbG29ZiHLdqL_UTWca-609NZqFj80lR5Ij6QwX5GK6NRBiMubnuYo_4ZNiBBqy8jtWt9BsIOeW4iNxyYQ4PTDwZdCihy7pxjZWps1zKZerwVBXHOeKPn0abLz_pQ-IVjtpnvww71OVKWx7BdjgOM-xta5bQ-IrDazCi2gT0FNCz-scX6LmrEARyqfdnxjNpoILxZMMNg1AKHjMsD7eM-eO8iWB-F6SHSQKuBFtZP8RHDZl9tdJvQjLut5Sp69rYkcCUu6rp4R1xU6NBIDJTKTfo61lZvpqzfywuStD1IJMpYouiW5Y1q3LQcUXOXa6HcnjFuAZXtM7RKi2i3ndW2FYlSqf9PjZSEQeoMohAw.Fj5uu8kAeHcYJsFqrU15ZXMvCZMcGap8dE8rb7T_fZ8&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c8030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzYwIn0.gah4Ukc1ye_-PhevAevTtULT9l7G6v1sH7h6ulDD8KqY1xs3HLiTjTfGHXK7_e0c62Mh1l0bbkq8tL0itmoTYuubcBfmG30wl87dnpoCNssh1pk9z9tSV4jMlWxaVidw__fOAW1t8FRjkcHO6JN4z0uah_8rrdsVky6NC7BjR_nIjNVR91GFKZkzTevch99njvM6wmogNpheWTUSjXTSGx3Tfcrqqt7Zs4eeGBvWUZvk_tNRq1Fd3YcoT11GsN-XHeN7q7kDTWR80JtM1YTPxEZPL3VhNGk6233-uIzI8rNIHACysXqUtj43saeBN1n-pmrgINGujqXzRGTYHuILq9jUZYMrtV2wyF14zfwLRF0u-cijGPBtqS33xsL0pB2XhSBpeHfJVABesUh0GPrGHXmQdoA0Egr9nNeE5EowHdFjqR-UMiUuCQnPySMzwCPMW82IzJyvedPZuHCC62CUnEi3c09osr8ZNn7edZhUZZ0xsyVwobGzgZ32l0TsrL9l20b4oM8P8imN24SBNC4Jyg.i6kn8lMbCrjt9J0Z5GDAZRQCE9VJVUoZXQMnTz4kKbo&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cb030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzYyIn0.mB-7F3WXgq-FMkFPdDWf3zM8yPUchMov9PM0VIsM7FqK5bwrtBXKnQ5q_yQ8861EYN2MmPMy1x9g9UZ9pb75MXU4V9KewB71i7vziaSO4ItWbuDCZyl3996mcdojdQHsyEvtNo38zM4XR0aIDD2cMFL1pBv0A0xHh7JTzogQ9dmv78sfV1BpZlVvl1QQJrw0R3VkVuiRbJPpr8hOUaQwIwZnUFYfXEkz9HmxrO-8GALyT68vxQDg7kAHKTze5_BJ4oQo99c03wsqApEYOf-dLaDDNvYsttHkg_72nvrYqe0hDQBYVDiLgmlpLHLbaayaAArMTJxbY6Ezy_hLjviLiorMRIKlLFuckQ0KXIynRH9zSdyWJVym64jn9UNf1KVTxQbjTNxvEMqnC8e1DQjg873RFivN9A-88ha2zstYg-J013i-OMn31a_TUY2V7k6_PN0OsUVH78Z4SRaGfJ2gA2_exh5LFzP20gkKg4R5KMsx9gisZqMzn49DEeaJsEAcmo5pDcxLeX5kHReBrqNn7g.7cMmXqbiC5dyS2W_8YaHTr-FXLOvxXD08sWSCSYc0sY&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-ce030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzY0In0.0_YbNa7H66Rkv0ghwxIVuoFn6WjvPv_sKxQByxfvL2bkRPQlipoOXZ9SfHAiBOrC4-MB7ICcRRims6tQB3gIBRd-S-_KS3mdM47rNUYy_LYJFX5LZ_nshiVZNPmnh7ZvbnIu4u7EMF2-ut9nl348festEZk0_o5hzaflhmFvEJNf0lcttCZTPE03PjvSTj1xtKFDc7D5ic_ixR4NVwHGcMBhZnl-Ps-L89Y6FkiICTYaqWCTplhpP22lhPXpSHMv1obOwjhNrZadpPesqQiaOyQT3v5LqENrj3CL0Ks4YGTyBPGXs2z-wlgY-vkLAHpzqd_OizfG3mMbXhzwbzBz108mwgUszSm0CliF5DWslkap6Ue8AXxn_iq14dZqBiejAAFNIOfKcSpXPs6D3aVIXxzk_-3WI1khG_D0rEo-C0v9aPXWHcyS9vGlxSftN4g4LBE6P42U3xqebRyQch30nvaXnHbxltlDcX9QgSGUPwDYzjE_9KwbhXQjt8jkXUyal_d3sBviplxOThpa_D9kYg.P0wZsCHOuQ_xhW9rPUk8GUv1hLKb9ORPK-wU9Jkxjx8&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cf030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzY2In0.uTeioRRyErLnSlj0MPTClpTuQgNDWI9EU6C9YA9yxfz2L_xl_cikvVSCeA5z3qle_4Q3Rz1_iNeIyYxouvj-IQgRPU61Nz6aV8QHEd41jZxiY5pOUwnig7FMld8hWt9TdhuTcMcYesIBUrEqXI-ak6pcJFTDZIAn175vF7FEmt6r0_Ccr-yXtA1hDbodnOr3RWp9qVPtVH8sEw293yN9g1QoD3qsm2UGo5DE9dEbhJozwz7tKwFYlF1KWnHtwvKuV7lZazuMX7a3Z_yq8pISF00W4ss7eymFERklhoh4oIMmUnatxndKXS_a07fqpxwxa6emol7ct_XLy0NIFNW0g9KE3w8VWIKXEtxxDiCeqkqhhkRXt0tHBCqWGlCuXfMTDSVRoI0FZR_w6zosy0UdW_fQ1iCnOyrzVBwH4FzAiVtO3oQDUQno4206EBOXj2Oo8JocLSwQryVAfmU-xLVKzdYoMlUgH2oPKdSgJFuurb3jRcS-xcznM8_jXGlTqYZShS16-0vvFV8u3gtWbaxafQ.6-G0aLEGSXI556--s0xSDxe7yebkNZ38A6bI0CLMemQ&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c9030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzY4In0.sObdwvKX64xnvu0e2OVyLEHb9F3csOLb6oEzqr5vvEpmNZL27mM1m9furIG2rTH4_dBeXGgyGfR9ui8GlDcrLI6dZEw2wLxBDPvqosDHhupDbjcFv6VRLOzWGFiwYuymFpvbxrjPoCSm14WVF3qXExBxriZuF6Cx1XV46-0eJLyGTFxjWFKK2Cx9EtS_IZ-Wkk6MZsJfk7yqE79h7RS3awmEsFVOU99LhHoxq4O7BvPn8AWwQSwW-2GBSUhA9qtzojYKWQHhX3KkPZ5haQruCJgZpcBF4_2zByvGudaSnZsMF0j-5n98s88vJ4Zf-WIiJjiESH5QNSM2FEmgbZ3bvaIO-YOcgIl09ln_z4czSnSx-UKYXpmfF-5JVtwuKvmvOpZYmAqQuxRJPqlxdzytcUHklW4dj7O_Q5zAefJpx-nZyvd4_luLVs-qoUbA3bwg3c8XlI11iPtIOzqItn2-Mgi3jtAjX_KQ2TBh-3FZI7C6wMv-Ex_JDewgDDhza4i0ZtwfQ7ijWmVpJggaguqi4w.TwN1aoNg3E-wGPFzDbPlCrnfd2hkB3Ao4GeDH1c_1X8&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bc030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzcwIn0.vgS-cjS2J9LISrQSrPq12Zka29m5nGp4m7sAcmYanJFll_TWf4TMudyvyB04vf4tRJKcIHUdhNFWML-2Hch2YdBZXJB4cQlQro1ZOjPJ1JtDrvzI00jIwV9M3LLp3_IL1Rr-C1-MFXv6bFmC3vlmwdgFRhEEXJIyaj1S6soAhKfts71xITYt0E2tN0rOZ07Sej1WinA9UjidfBlyK61l9E8d3j6fHguQKcJo89TP7IIUhN_6JBottUKtwSkEigq1XbIZJ8MCJzS0Q6T3ojzbIq2Lucaf2-4G-TiGy5M7t0wjZlm7AZhnGCIFYC9X9hZ-o26Ci1OBpmVKpGbccQJ-T6WHcGaf7dAHNtCgNeZiVwpEr27gEsrMe0ESk7HAo0dP6nR5p0WlP1shXZ22onB-tyFx74yrKYrAJawVVtbpNN7pF89sHJ7VE6M8LtSgF4tqWsytYkZkuJDA64Tmkf96I9R3c-5jSotLwzfC4eWTwofNFJ0-Jq_gmHQBxqb6g30VVNyujCI_PLZb04Zm7o5AHQ.4XSSjIaVQNqkwlWQiBXf3-JRN-1gxy8vlg3fBx0iGEA&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bb030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzcyIn0.LM7nLXuFtD5W4q0-skLnZEMlF7Fu8FhY97GiIELx5T6ar8JVqiiQqhr8PCszFylprBvD3BjN1heNEqsSoc4uIZO_PBIj0fdBcPeZDeYM6lmHU_YGk1RfS8_HBmP0BeBLFzATy4gBSTQGHhFAKUkA8VuJvY7SThhU8bjigBsep-Zcl0Ekr6HIB1ZsediLjpQWkmU9_KVvQA5Y-yaET_ioKDoHfWJSQyjPO1WKhx2nGWjvt9AW64fIDEjqOv3pQZYp9YXejGMGem6YhzsZMUP1zBMvxn66W-_APbAz30RPKqVlNRZSp8zYJ2qzgiyGGaGm-JRGZXDosl93n7lH-oRMraTB3xcYLcloOzIu1Cp2m_ULYzccHrEsyUr1yD85Mkp_2pr61nYeNGWOkVgk4Gxgkcc8URWtpug4nyySaPHcnG9Hshv5Oerk5iJcfrrbvkxMLfFOrCcUUqxTx6RR9xjH_ZERg33qWAU71KzwqgyMcCvnUopZ7pfl8E1lqMG85FwBRQk-Flvpsb-hVyBpWqEXvg.8EoIvJ7qbFwZUHEMyDWId1aKj_K9vo1zRvA-jAyZ3oU&amp;ApiVersion=2.0</t>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-85030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTU1In0.nKnVC5EsN3tsJTHyopCRhmJGurSmO0J7Y7mfkN6L4JXiccajtzO3BgKW9nU593ECmiYB3_M56M5L-HoKNX5e0zBoVzOxsSQDDxz8NNwJsCADzR_bW329Epl9qCdmFrlszH7hGvrMtde_fi6V9XOmd3zYf_ArV87ZTL5as3HpeYWFPBAzPYqNBuNhS6lclSuHydItUOjxZVfdydNGuiJTWbN9VZ_uBkg5vDbauPc9RfOSV3z2Q5RyxckzGoN_0SfJcs7nRzV5DfLIWQFnSKW9Qk5HC2Y1kbOOB8OJDlYpPQehDQ3-roz196_C3rlHHdXr0xMw0UlsF-KVdNHcT9AV_vH7n-9ZDyowETeyOJm0GnRfsS-SPTLlSO0dDl-76elLtKOHMuu9PSaykCZVNqSzNqQJqtaXHW8jpiw8x6R-pPIs_xnsORBy1a7b3qMiJBk5MP6iHpSd25V_nAix9l4RF051iYTwg2HL2dbQQ3YCRwAQmnP6TvCWi3uOKc9g5RDIIIDwhPkjgg0cOsZ0GsqB6Q.9iYdlZzoRapswPl31RWkbH53Mkn8gGUjE2Br6Z1xLKk&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-86030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTU4In0.z5FW8rhkJnvE0xXCJQzupMV9ceZdMFf2KSH-EI-hLhoZd4oZAtUe8M2nuKJLqnUwljvOFOVHCeIR4a3p2gESSA1_CUej--gc0D8HHljcfuTqeIM4VfXFnKhoeRGNBSaQvCC2S2J746Em0d1VRtS50mGAITWFs2FcWMHY36ISVGdUTdBBlplc9zTABR8YPCjjC0gdpMaygBC0txRdq-12nJCOGazpfV-Hx6tcXsAQxHOVEIiJ5tq17X0xs5vWcpRVofb4_dkcBOouoUo1tapO24_om5xVVitz0Cn1c6QiB1ypQCJ3TNPo3S-SADxTb1r5yXJxKC-95Y2rr73cFX3PHT4Cx9Fe_y_BCoKNLHOcx_01s0Gj-qN3ZcN7qtgXcYQXl7s-pEblKlBFmUBja2ds4Ae0axHhnnmVM4KqYcnEJtwp96Qd9UwNAb2x6RMv4R9BqJVrdXI58W6wXCDtbkjehAReWw01tHQRyBoGqgq9DpvjHhKh4jAQ5_HhW9Ne2VglpKd3qT3Bav-Y3D8e8pJ1eQ.IqwmBD5lty1jCem18BunGI8wBGAFch3DGgttvFRgpic&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-87030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTYyIn0.qGEwkiyKjZpqb30pFIi2F3JyQL-HAMzwX1vSrQG6DSnB_5RZ2mBgJktILVwvgX600IduPujaOYnjNXLDV0xgOTFVlKDbB_JkRguMSv7locc-rPd8lB1F92S05Tn6Que9ZtRql0otQw5_eRkcZs7cHKkJD3OGL00F4b0yltio4SFVWh_0Z7AY97w7bkDQ1LDPmJW07IW_YCJPC9-FZFqZ9iDyWeS0Ki09muBUlyJmDLweZyKgRd0ktAMwvUHeB-4hlMQ_ezUOLZwRiZ4IBO3Mw5D6IjLG7Hl5lowJPFRhkEjGsVIJxZKFVGM_VgxbHsJ5kehENMNKMU9OOkTIginCrL-qd6ZTZRjKbfjs_mNQnPjOFG7wah7HQ3EpDSGUP9B7od9Gve57gKI5-reHp6cBMih6KrFpDOCmSbgLtDUIwgXUVNQlKuwiQUT-MCWlIublCYoTEe95Aphx3Azz-eNMveQ4UpaE-VMrhHMHSJDqV0SUp2QvtiAHrDqzBBD5f4PNPU6pqFDmS5Gycw4F7lfPGA.xgI0SKLL3TO6OakzsLuNXLEEDu_0BQrKt6LfG9FjC74&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-79030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTY1In0.M1R4iPw-e7x_HVwsIFhqzHA-MhZQFWkLE6r9i9WbllxwJcX-Eyp-jU5V4YF39b0al-n3FVtRmvc32lIlqbE9wLxmnqXrZE23dJq5y35pyL7yn1xudukESUecO9st0yhfGI5OQrKual7FpaZevoaMjcozLuisgjToyXI35zTJyRsTbbTzTAICPbGU8DE3Xwh0XmNdfw7Y0HwvI3sqwT9t6_D-lQOJUvxisrwhZ8cVSGk10Qah6F6B15d54_GrkEF1OQTh-c1AJY1WE5n87X0VIcjYkBxHSGfIuTnKzDFo2-cCTXFcflXA0PwOyuorw9OtUDWmzSr1Mz-okA0CMf1_YESfrdN7VSneY4IrwiQZwfWFlsELOIDG28RhRgxDICF-c8rSR5EnzAETqwbjiu_sr9ZCGD935zFSJtjREq9TbC1bd9QKGPDJVZlaiaZosInDNuPUiaWCP3POqQjpmeqUSlQMCZB-HGDW6nsRurzFghbmDB0gTDQHfnaNuk5QtynkxiLo9izctjmukSGSlwr6XR-H044gTtOwH-vY2evTWkc.JCO_CBdOTHc26AEWwcJxQmG1onnstJfjPCZVhh7FgkQ&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bd030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTY3In0.5HnErot1-4ht8OOFmMVWlzvkx-i-naR5RaHvMR-heSiC77gtS06Df8DjyfHoAVarvWNAvCsIw8Fz3a5L1JA7laTJwTNgnufUN6WsPHT2hJlL4Ed1lDcusUmcYqA8qpJeKNeaW1Fx7lqT1Coy_V5ZU-r6IirxCYRnXyr9ksQkOZO-FGkpSv9mOuFM2M0nEE9V9rNo6-VRLDtko3wlrTHycC28709P-3kmn55NPLgrLa9jybWxaicltGqu2wJVPU8AY84F_xwrAxSoHR_5Et4PhctAhtRjPlU_YpXC70vDPzES4ELUYYBWKMltRca8FSCAfhFUQoM3I8Q2mLU8upyH_ZLelXSMCGWobznzyHjBmND4xY0JLMxEqBlS0VrizukR9_2Kr0ocuwzeyQyEWHUO-m5GFZvQGrCem4VTIT9QDKGGaBvWqi4OBX72h55qQHB1m4heL1tnZUgZVmHc6kTykPedEZvoHKcO1jN_u0dStPq6bYVGsUtRrqqdTuYsckx3-gmSORPkQCsO0rm5lIlgpg.LdSP79EYNlBay_05ZTejYHeULOVNYSm3sG0cazfyZSw&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-ba030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTY5In0.uH90S5AD5nh1jvyslAEmHtM_MTwe2axCCW5ySv5fo3fc3huMr34s83cAuG7z6kxOv1dOrb2refrB65PI20gxwwxq8mtfoHaT8w0-KHUYJLacg_KgYeOrDkA-oosLaOW5qh34hoWy4qZFbEwnePBabncIaIshwgWu1bSm3OmU3CqR_DG-tCOXOs97EiypxH9ZhkupbNn7HFmetJSsrLgoXx0rnW2cVKBqebSOiOHVQNhgvZemBArofDwG782918cf73AUPHToHDcmjBKn2RzxTBRpg9MVE0yjIJvmA1I3G7PDT4hVWWve0HzLSsm0kIvVJ8n3P9oLxEIYqaLyUga9Kj8jKDPMRS_x8yPBi_2Y4oXIGvoowe1h5ydXTtKb0SW-TtGYmBVrxcajU3ScAzy35Misr333HQ9b9QBEy-OT5xI3V5Ky7b6p3_IuVVAIAGrH3-3qmIEYdQNKlanL4lQXwYD_rXEer3RWu3NAAG_Mp0n5HasDp7QxOFFYLkxoQ10AfcXHj9M22O9hA2mcbs_Hrg.fpBa1QEu1pD4SFoLUlHS5I-Z0RA-rkdfUvFeo4gJC2w&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c2030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTcxIn0.tc1oLxupEz0x4-vM-ajLNhDCwLRH-cdwi065EXIZboUMZi9n7pu-vUEVM60iYzurwUth-YtHUnnliKssTKn2DftctsoJXp-jGWtpoOPKPgQAJtNRYgUVj_xDuuQ1Dtds28dDR9jsq6WD1AcSsVHGEzmsi-1_Zn-pCFQrwdxgjDPDLsW26NLNvRuhr71kX-fB-xXQtsnM5r8YwPgpu7abjXS6rX2YyY4BIkt68Lc0r8dOcX_BlrW6f39mM8Q3l72l79XYYJs9hjmmDkW5zUGDAiKLHpeJFzd-xyLhZEphyJEFBW9zuwRwnVeA5FRBmW4TDLYyJaDE2GrRLnymOhyTJACVbYUEGmPUdxhyT-rfNlsYTa87NJD2ib_YI038v9lGmZCOSk43M4YZg9HJ2wMcuJLjqNrf2m_W2PXKg8HJk6KpjzWQR0CrQyxt4RwP46H_aERe1kWISTJ7mXcyA-GgE4LXu1aqWesUi2n_84I_j9Ue5anK3A5RHv9hUFv0ISYPOG-l5hCSDqCbLCCOjoERhg.rZfzxWc03g4dBUWHRd-6o4Z632vn5LW6Mu1-RervCFc&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c0030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTczIn0.YJK-2gvaygf4QCG4A3LjETqpOZfBRCIkbEClbezfVm6cBkzHiwOP1dPHzM0MrfUULf2yWHarnDzs3-ezJAPfq7Qt_WPrRji0tNK0r6bzszGDuT83dlSuI4lpWyVRWjKQbdNWjGRFAEASML9xCV2P7t7hdXqf0HrY0Agqz2FanL16FX_NEHgDJ-tHIYHUdhU_YuNpbeNCUc3buGF3jFwBSeK7cVvcNzW2p2TQg1KVK_Wz4JvDJfwyEXUeD08tcdfDxOJHZR2quQB0UoQy6UYq7iXANvMoludEVNrkWoFucY7JfJDUh9d_gIzs7qxGwrb6rHWngVlRQsh4scbwlf1X-v9GXoK_GiLhpgVoNSXjMdAvKILVX6KogoFSK6FCh1QkwVQeVKp332kK45zJFNmTZ3N8f9TU-ZsMb-x_Gf7XIy8EWpP5ijNeI_xar8zIjeTEYxL7EJIXanNHU7LH3eyIHCnOXq0xt8ZyX1jKc4hoTrlXwJ1Y6MNkystZms-FW8dHUyR5HzfzvXO9mdCn5YF4ng.hAZOepCJXh_lx-QnZSbkZtHaxTA83vSHbcvuf5t2iUk&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c4030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTc1In0.UFq7_AxoJ0Di_cka09cDHWbswwhJ7LkmUosiVAKoKEd3edmHXzwkpcdMdsk6RcoX6hWTyO1yJQqQ6akFZjqMpJkFuh6Kd29cHa-fLpdGTWBBGilYiS4G0eUM-BS0MnzzopaoOlrWO_y95Iw8XUouv3yTVrwBH0Ii2Ccu5lDZoiadNlktDmlqOLRCigGd79ptAHKJcR7hSbYveOEyhcQ8pjhqW_ZU7hTB4w5yWEMe9JVi2gTaRCQB-yfmOaRfWGLydkZycdFUlq6t5i6UtHJvZ7dtm6MBkYbjm2xNGnAM-oy2w0_MWvtI7A--pqR2RlwfOzsO9owLa6l1-uCM7_Q34A05r-Jk3E1bK2opgjMQN3ooKkxSCxcuZI2AX4_CgLEWz3U3Jgfk6AvvmJPe9tyhbBt18qbIOdd7KOOe0qnp8PjMd_u_h6CwHxT7sWUMCU2hWpYeVXpHrCMUeJJcxN5B9EiadhLOvqil--ASB7cAvDJ1X9Ks6jT9XxIDabcw4Cl3b7CnfQhXyoaRh5AfwTDqHQ.5EYXlndd7uDLGma-CDvTp7bVQR5JWGojhjykt4eC9Rg&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bf030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTc3In0._w2JFMKHdWjbldICQLXLtrMGTkX5x7VZcOqY8CQ1hdRrhyFJgPCrRaQ-4MFjj9uedQKkqSw5GgxRrP1bSB1k7C3SIFXTsTCxIHkO34cN-osIhUUwAwaSNIPMpRqrnuYuuY8PqyFB4wNfjFZ6PwkUoYn4cLKnGTRUq7GzVktLtKcFEEbpV-VApn6QOLUtYyJgP9Ir3JLHizzWDKQbZ3q1Dh-d8OcZZ5f77BUoZpHXeaGhhnTtvCh6LQbLRfPVCtRykWkrnO9WMb9JUP2sTsgrNQhpY60yhmXL0m6aCI3CIGlRPHV5L765GbxAfkOuPYWiSKk46uWGQwXCzTvpqdFX5AvKatS4fiDar68Cjld-Mjuv1MZZ6u1gvtSSQq-RNlytUVD-vJsAQsnXz-csvRVHgoPSyNsLKWbGFlmbPfnouM6ExEuurpLYYO-w8c_Y_tUukCkGZ91UHHyqjvHrUywZhaRa8I5jhr57Jzh7Eya-iDCPEOQ-eRDAna0eVnd_aPEGyYXMkFwkjiq80S7arxeU2w.o_vq_qVeTckbH4nD_l9SMV30j-Fkk7yqawWooFEsllk&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-b9030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTc5In0.h7Ui0eOKmMR6fr2-vvcXbfeFRfOqTku0hDDuFEvbtlEkmEhyYbcoCopON5pXxMcPYQR5anJ660lkHUTHSt3K0VpRWV-duu_yH1d6a7S11laJFFdjEFC9glyTaUqGZh2zt9k5jZrwiq4BXcLcCbBOrWsZ29M67ZsUlC9ARm5Pl1xaQgvkCgnsyUHmZTGxg7sCYzb8_w8ErTfgKizagsD7_POBFisR1xG42mPwJp3oIYPeyc2_sMjVJNPUz6HlB-PBfsee7FfwFhcyVIS1Wso8MqRnwToha0t47SmRMtsAOz28_DGGGUTT0lXVWa5CpHug_GfJrHYkVYxGbm2buPxMXCQoAtYsjsBiHiJCzjjuXPiw5ofnw581MJDvhpy11902MtUUTXhrhQQl2xpg1gckk1rIJYfKTTNeL_LVtKJD6wd86pELobDP-B_5xkE_t2unxNWcbw00uw_1_-9p99bd8kB4RLUUEeXnqnKn0YwAHwL7wRuhiWUR8W5icqu2ntW4qvNyaSyhePrMIrrovzZumg.swNpaRfaHnTugGhGR1xtoGVWuRIetFCWqLEiv78Yy8I&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-b8030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTgyIn0.kmmYooBdWch52XIv-IFekOau3KSZO0-DfQoeYGQsM7cG-hqzfeRLPZppMLIugagbJZwDQiXhrUC_cPXxcxpP7Ju7mdPJx2GO9mKbbPRg2K0u1lBR5LkFJY17W7wQSX4DqflFl7LBzZTI4pC2sa9bCnRFg5yZEWZvI1tEs57MmtkBmM0ELaLWCOBuMeCQisZt7QfQ7k5mf9uavksWTJao-6qiTD9GjVrWkSdg4WtYe9NEYYAVJriDDPLWBpKDuiXcuOAAK3-vYSZn3kNxqqtCDY6i5bfcZytbTMCBw1VqNIwsoKgOAh1_DuyVfQ32Yg9k4m76p7zFKhmVE6YIQu-ddZUwF2bMq2eX1h8w-aPy6pK_1lv4G7bVj6j8C7ed5DsUc_bSJdkbrUk5C43N-Mx8f6ptGOXBp_1pVuIxeNGFfy8PmxznBtuXT7C5C7QW_hFls6c7Pfu_71eMwY5ptNvkU27CrX3rhSOgZW5GHlrNDG0f-ljdhpA6DLDpdl3Nf2fSpJy-rt6NsSImLlMwZb_Gjw.GFNogGcOcSQBbkYOTPEHJTleHOvST6T1voF-SKv52eE&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-ca030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTg0In0.V8kYX6EioeBuVDoAjq7yL2EvFQf0vzH-7k_yYM7Jd-LXarqIXCsYgMAgZ5osL4sWwMttCDyz_Udn4aOI8pO1ZZ_aKaTU1zquBBc2zSy7APgjoaDUnUrzerNJii0SXpTYxCRsL_XyzPmQUKhptyJQ8BOBJiaYBYIN6xGWN8vyeY6hPe-n7lN6aOeHf_c77v0KiiseptiuqeXgvHj_qy_0h0OeaKe5lF2vLLGvKhgive0TJ-dbg5_nbTaJNTf1Yd5YNTE_QSEHc5SrrTXCverxSwlbaNfnkgKbhwl4ATS_R-jr9bLhuefm8pS-BZPM-cZpKyCxgwynjKw7XWj6ZZSfo41gEDnVmPwstMNxuu__L366r0htnbziyFQKtt4IqTlEtoRoxfzd6DjPlMw-esy9TX5jBQeRhmm7uEGpl9sBTQcNarG-BBMKOAtGmN8U47_tRI4_ZVx0dj6NDdJ3Ygys_tf6b9Bopl8jkIF6S5RnmyAnW7HKQZnsi1aRmaizwNcbtGkMp05X0DN0tUhRohvLcQ.8eP9E7kAp6R_LDLkeyG4O-yHUAMW78agFEXeSBZlfbQ&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d0030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTg3In0.xMUca2TMptlSHtoA__UbcypK7r1qHoi6Whnu6qfRR4UoQsrbSn38J5KLAyZJOYc0UctYsksjvXNuuXo-jrVhoyhD-SQsRIaOTgqmI88d9Ez3A-_un3QtDCHwIADCFV5eDn22QPo9Ty70C0AP6JAfRhAGLMEHWrZPTJRWJC1EOP3rqgo6emZNj45gobzRhVzSEIUiZy6Qqg0wI2lU0EKMZSaP0vYhwxoHeASN_EaaLf_Fipc1Vw03k1OU43p-Ni-2dJQqmIrc0uJ62t70u19YMzgVdIW0xuo3UFCoEIC8jxcuaU9FAFnFad3_aH7fiyhCgOy0H43s-oK_nPt3BfDFh8fm8y2G56_yzRxgqF8cxQWbzGM-VSoFuGk3pVdw7AD3Wiz4FhXEu5h0-99mTm7MF0KnxMfESwbcoySA9PCRI94N1iszImZViNQbv-FJV8vxLhjcTQ3ajV85ytdkT8-_MHUDeFxRQo4HkTs3m93NiXzlDJKj6RLAlpwIvRVLVm6308HG2Bm_2OzAyNTIWXgZSw.AoDysqieCsCXsuwpFUGxDjVZSr9uTC5TWVkfM84iGmY&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d2030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTg4In0.gueQdp-ycISBg8Rgvt2UD6J83BpRpZ85UNQFIuJwQrySTn0XPFSulyAEddLiWqgrNYiS4TN5jvesEWOLcf6RVoOTSDlawn7X_hmmwCHPSiWx9RqQzj8TWnbcasaJV1mCEsOJZAa6z3K7357A8PjhMmEhs9r8-NQWO-I6TdfW9L1Nj5RHAwrsD9u-N0KnknBC_ViiE8wssl47EjY-Dxh-YU-QSpCJYuMWcAmfz-YgSP4mrI5tf5SkRC3RFWS3UkzsYeURdVtA2lYJqq_JZ0RPcsLTJXZtUdi2cfvvOW_akUvBVvrgUDl-IltSp_9tPtxu5J6Hgn3DvY275Rxc9loFO9Y4O-FDoRwniSIoNjVXsXs9BsZWsSv7K7lywPfN3KKEZBUz2fHm5BlySTff0Qe1lzPVwR1ewSBHCwG8uXzaF077q2pv8MvBNJpmfeKM4xJASBGJUauxUD-Urp5zxSWp1mnNSBCeBrTNaqKz8qNLvz0vETocGelgOygeSax7bnXargRrHIBPdkF6mFWCe2y2bw.RqFjzNGInXm5745AZQ8p8kPewoolzwXYkxhxs01yghE&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c7030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTkxIn0.XcEpAppoYrlsmEYytNBnNGjnSLD2IXKvQnaadwI_ZLi73uCZHNe0k-CGXhSN1FnxflUbGkE2f4aFEM6abuDXB8dqF3sF9utRvi-lv4cpaAUBL-Sdar-9aha4K2tjpaW8GlEhSMVSXNZ63XyBh1xOVdzpX8g3eRLhEavoQi7Vc6hBVKxKe4vMlczSQ_vvtDKWqeE2y2AwBhEl8x9N4dmh3tRfR8cngGh8xS-FH6W1tvzQsB5JKzyxkpzAF-VNXzzKRV9sFWiuxrAw7Qlvjxx6hwsGFiLZHdPje8YzEYIV7bjcqCkIYEIzo66lazOB69QdIrn93oyAPyx-cBKRrQCFhkHP_BVsskTwNtabLvC7FtQbR__nBwQbu_yuZodWmz-U2QLhXDObFhd7-Xj-AOdyZ8cZ3t6X1G2gn3M7sWTQ965z05_2r01-1xNzig5kM07E9Prph2Qm97LVcn0bHDXSBPH0bwXH4hrw4cO2mYiBHzKnGIIJvs-6Pgj18QSp1KbJe8zUEv8Nte6CLflX_DOEUA.BulI_ZnMcSfQ686gxaaM_RzhbVIqkmS0YrmpUNLXYtU&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c3030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTkzIn0.S2RJd9wp_ZpfLacTsHJ_8kN2cHOXGnLTHlid1XJ4zw5yDXh1mC0K8E1d1-8B3u4xkwYDKOJhwF_9IXVROgeS9gYimnR8FL3ecjz22lPu-GtkHDqWL4pIw-Gev0o8lL76VXlRu-X020UxklVVY0LjfFFXeW19KozT7vHA_V92hyYIKmWEgG5eyGbFpbGsH3dTpLAEUB2zayCvIhaNaEh-I96rQAxd6hMKUSpIc8W3UXbR0QPcHqzEuXgVTQaUP16JMt7wwCVgXNwnFD9wuUtSMwFqwAuTZwjH630iecOvFl52dkKajvunUgPYrf4Klr6xLWPisQI9vROaOZWh9DvXptKPwLiAcSzjqxVxTYPYlydX5poytl0Vcy7nTSrs04tVhNDpzfC7njqBVhNqw78ZY3OUmq_9jvH_BauacP6Pl6opqD3my-HngYOvTVr51ZhCm57msBdYAstfajus6GaghiO0SwqdQAu8tubKhhtJMOIsccvYraYQm7vGY7tNS_VTUKUd_v_CJpfCvkJ5c617pw.Qry0F_wOicEGfpEUr-IK-h8GQE-CMCO2QMYI9Ai4FQY&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c1030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNTk2In0.PHZNQMfBTURlpaYQPj7gBQDEFa9aOc1gumi8DqNKq8cTfhxBD6j-fc2OZib5ok3DHb9A1VMURBjlbverbFM3NH_T4g1i0y05xOcwsSbQ2Cw_9283PFDbMfjjjSdOyoU79cwJa2Qzn9De3QcGB1eWwePNN_oyxYxskbyLYAvsvR8R0NbaDKNpHtywTveUElrHjZKjwu8R99e5zm1XqQmF9hPOfCy8FLrsPgVYfOAieR8hMOTwqAKktPnaVtySYx9Dzot6qiOwIOXOyHaK8qSorcx7HdRHG6fC-fWnWm9wArAC9bNZIlxsyShI87NdcQZjzbNhLtGenZqJFAD_EmHGFkjJzHTTGEWza5OK6uUZs6NuTu2-limECM8ida1ItqkN6N_8G8Iaa9ROneOg21rowGcREfSPKpVFWSBsTZAOhfOJ4mg0oNL43U-ANODSOiEMT8Hwuccbd8iWsJUDjk55OxD1e9DVHqV5oxfp8Z7v79asT7Wjl1KDyvq6Yd9lljd9IRDz3ObTqZmMLGbAOJSywA.Itj-hYVsCDadDnPRbDQS8klr6yR8EHJ_XJyRm09gBAo&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c5030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjAwIn0.q4BW9jHej59y6TJdRarfAyeT4kfMKjB0C9feUNRgnHEC0s11apaBO-4gT3MYHMVX_s9-VUf7sv8qsnpUvLs3OaUGAGlmRS0hePlmcbuDgkWP17UYE_9_sqSQnx9WgYazG5fVI6LQHX4HPd4bnM-HtJZYM5c2joczFCWUMqk4iM0hzbijlSg4fi3dLAoULwQrmLozEH58EUNJL72FFWc3rQIJHiVrhb23YK1CqXjHLEG_rvlI0uJ-myIs_LdoQ8Tof7obl-z6YT4iQviuiDOnpsfs2-PzQrBYECRG6ACrwxY5jc0HKKWwiGCmej5D23V_REHkg0jYpJD53e07iGrwngprzdn2Qj_N-wbVVgplZDTAZORndUlxdlTI3Y29qE0S9E6dPNQo8vyCLfJH-wFPRNS2MAiFX7uREM05kj5GKQBykoh25hYhEX7enRqw0B7cKTmxwdOHu_fham1E6-YixAuU9LXxeYSlEvYmZrIxDwEXnv1B46nGAI0KoB-wxZMrZCA8BNk_rPlTMxpFeI3E4Q.73-1dc2ebYX-7RLCMyJg2lwYP9-7rF2XDik6MsZnZ_4&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-b7050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjAzIn0.S0tAbvKQ0dwabj-NL68YhAaT-PJ1zHcFl4RLqSBZ8kAH3pe2zvyBIVHq7fA3Dayc2sMEhReTK_AOVcoWEvuM1WKRFpvSzU_R2w7oHTdjodK0xyqE5CHvNmvK5PCighR4t71c8MZ5JRr-VtRG-jJMBEDQDjpY46WBqXDocnIu6YKQZ6dF1eRBQq4WRCQ6pd8m6xSYKY_RPO9U73TqGWSYQQkYk81-kDiy1PXX9L7Paj-cMy9D-4S0M-2H3nmzdw6dhLbRdxpFhFpBo99mGJBoCzBgj-kkcrLealwj1g-4e4yQbxE6Om9ZTb9aHPYOIRi3hlKFhUH0-kleP1iiuhYUXpnbxODLnjErvL3xVdGeSBH_bRNJcphHszwpihZjCOSyou5mtY4vf1UqiW6XaS879xuzSC--XDZ6nMIuN1XIqqp6IwszV8NBF5fhVVTb8cX5gwYIFzlKJ4aEJ_TVEWZ7DD5V8bTy_Pz6bo8kSfceGdnCya4BtfVnhGF1NTBWIpiLhvnceCnnKkfcsM5HodSzbA.GlL-MqcCrkPyOTFd3PhY2beE-SBCnFBoL81FTzL22m4&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d5030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjA1In0.Grw1Jc7OJgNkZBkJT0AlhaAnrD4k8fBhLZ5OZ7ZHttWpLePXUc_A0zDAZrDN-QIynv1xiPTvRGZ0TNKSrg1uP1EaAVB3snSUyKjlHmE8ykn-KOBh6aG1QL9047sfYrfd_clHXcEfCmWy0rcu7tt9_NBz1sDsUc0G3KI1qhsnin5qURTJlvviRv4HkwCCXgNAyQcWb5IvGPaBAtg3DBWri8Xk7Xc-IzXR3hyA33TbJHYSQTQ6UTRGGerSOXiAjyfo6s2StyX7nNs4VMcZW10xwuztsWBbuR_vtkHHhmIyHtSoyOCTbmZ2E6lns-7hz-qrt0Y3GYj2GuiA74YukQD0nSQIfPPw0Y4hrE50hYrAm__wl8V4wl18-1LY_CnQ4hNHje-fzVIALhFVkSfFJNv_hKdvzUDE6X9fL5oNG6q21InMWTMUS1sGclkgUqSyxYHawnuJM9FpLQZiTwRRAdLnfAf92-GD3G27eAss27iKx9Y2nkSAjZqN1mwL6WkC5z74LuDDWf7-mFkuhMRaKfvR3A.M10KJSoPViK-Cr6fDOx694Nzav8n4hK9OmHn06ThTxg&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-be030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjA3In0.hlSwlvgtNoRSgjBQLStADFH4Bou4XgJ4Q51-YmScENiS6YV3VbpHFzieWLaWvOcsgWowcU9268HwL9etfjLtmALcRyeY8ldxE6-vvWg8jOA28O5gBstLcvJRxIOpXvNnHrIu6YYS090z3I_lhFc-GybBFeFd8UwtUFxvGXg4mjsE91QSvl5ckBVwEDoWkJBOMKojUFs9T7BpjD6F5HKLhWpzwb7cJmFx0ZqiiKR1KsYHdxvyDr3UiOw8VYbzOI11HLCfM2RBtM4-iAv-GG0atp_xRqeMUBkapjVOZJ-SlNl84yE-3RWghrptjtFrbfTozb5Z4n4RNNtK2Gd0RW3_LEWfLJTz-Apnhm-qpb1Yk1NGf3QB1uvwePs4MsP-mDwBdEMNZQV-QDNh4-EawadK6Xj5J7KKmTrLnz86oaKd8cmwz2tGOqJLHj-mYZIzh1LXIvLrJqfe3IdY2jnGcZN-To2wtQAnitLm3yloPfxcClKOKcKkFg875kp3XPNEzsYFw53_ZL-7063wfj9t5WplOw.QTHz_1ZB0GQNhIegJ-PYzoq-RVqVRRzCy3n6yHfN3Cc&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cc030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjEwIn0.gYwavwxi8t2mVg9YlQurZFh5E7FkYT6MxezA6krV6leoyyS1ALtPXiKhT9BYpXUsG334PM6UVQrdW8swkjye435mMZ7go2O3tSJ7m39mxiMnIq00zqfxpIa2CcXNYE5mVKqqoJ3PYXuRlGig5WCGWk9N0v4o84TadpNXEM8zxENTN_CrHRiFSbKTA5t1qUre7LznJ9NuBkMzEpnXAdm5ogF7N5rlQDJ6-fEMNK5iMkkgQrETaZADyocBmpuk140nLBmgGJjGOICjxZ7JqHd6dnGz484jkWqTvEbxCK2W-PK-cEwVzMkjF8tziJmfbqt4Y43L_i9SADFg19ePS3F0qtuiq_DKnuK-C4Y8uudMPQp5i6hK80FB6VFuFIqgKXu_fwLU_LUGCdHg8yTn9doe6g4gyvGiZK_9xZ70Su8wrepIeoEmrEiqrv7LUF-EnC_1w7NYnz0YxSccupEdao9gAGBiPrb2xhCHvJl5fIdWC_Baa21bFvx_lSVQgqdrnsTIwFdr3uvMlHJ13LK22pgYDg.S-0uRFUt0WQHbmvJCmTrIgyWhBg2eZXJAWTU7Q3nkZM&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cd030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjEyIn0.URkh_E_mNCmLO9r9JUJL5S0WJKrX1EjXycSE9aSFFYHfZPse5RReh3vBQDb6BwFgIb3qo7wWtwRuvkSRlb6TTP3hYTgBPY3qtwgOFhCKVKCwaIe6DKOukPNVHRZcgkdTeKuEL8KUa9TJJEJYY_jtY4VR_Z4aFf-mvZ8UNk48ZIkCTv2a1ihxHlO7PQzzBFh9jx5MlfMVVWf0TO3eHbMdqYIFbnn7b-1LOSsr4X2vgeafo5q9NbsBPuuVOcZZcCkrgQCZXLxH4ZBV-KuruFrJKwpM8IxpPJRLgEEGyxTtszSLLuPJ_XykYhTXORc0HRhENCN0Ui4Y6Kejywgs9-VQvRG6Bw1SU272kUkQTECUyopxEDeYxXZG37lpWkomoHuJphWV3y9J137-q2RdlkTlwTJGQVp7AQ6NqM3gKZZrQDugUTdROmLp7WemiBQA5gQJ04aW5BzB-vpKAt3SvybvNSUnfBQjkIhivQZk3xuCTgOw37zyw0FW0OMhPieNKMj7Op93kD69XdQP-KlK3nFF6w.nsr4SAagNotcfQUuT_G4NjNZrcuXGFgdue2zygPuNkY&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c6030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjE0In0.PTmsbqiTOjzKgYGKmL50RFFh1Jwa1pb7KnIII9s5hlvLeDofhEPvz0KZDR9IA7RFt8zmDH0fe0EVX7-16NfdWjFCXpfi6OYd01CAqRB6WnAPAxo6CoIc5ZHCIJKTeMRvqR0UAufvADVKreadAF5i-x1fSIKlUZuA_FYIIDYwUhRdEWI6x9XtQP2LuBMR9pdeHmx-pZmvfco36gMLeoSZAHE_CggeGS9RC5d5oNTDwx6inbFEHc3LHQThrH123-YSoRs7yOmloQdIS4cLlQNZGOeGrgUt-u1xa9dmhZtb5b8cUuA3aWBM_WYyr2Tca_TH6bjPZ8vX_dD-EB4ZBEm5mdszYtPqYi4SnM_TiLp1HUTPTa8x5bgkJ4jI3XKm0x2Pi0qCO6M1OBxzXDrnuVYJqhe_GjZlGe8fm27vFsgbIijqcgyl6gs5zCsuM_vlPM4R-uZjao6B8WJ1QS3I80u_hTPPbKeZUUR-D12OS0LEnjqTsa_AiafDKmeppYvEF_CMbtWG0fRZtwBuSbTNxDeOcQ.n7RCaDTjBh6QBsEA-qJfr1LM1ej7SWbIlz1LuS_Vsnc&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c8030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjE2In0.najdz-7xx1Mtcgx_2YHNMbtxbJvdlu5adG2l3DM-tgI7GsikV3-msjbUVsqUlbb2d4-u8eKdKFcUakLqy_CNa1LDkajMWGJaraLip5aTXrCIM-ccFJax6kl0FJKHkDJFFxJmuEGE0PzvPgZRa60hPrRvppf_eHemjnT-pJjPQAX7wGu23Bys9DNd1rw8_hK4iDBTvXq-raWEz7HQARg-vivq5ZBbaRyPTAuMqb_KscIR8F5CIpM0vbkgQkv7dIEnQTeZOcanUwBcgxU3ncvVa1NowwF_W30ZauSwlZraB-BrCur4LDS4TbTOe2tcIFDjq9VbhV-SZ5-1hNcf42Mu-qfCDZn-4N-Q-o9tiqfWvdKIffaMMV96dDg9pHTkVDqM5qyRxH-ekpctVw6W1lMsoOeTlhuYFsqJAtOBOeRnuGgHE4z-eWZ426wzzKmNvolmw7jBn9ElB5fXcud2Z3zEBgSJPScuyMdA0YMMdTpxUFffOyfmFjLr179h9rWG_CF_CaUcQisSzrhfbcUVhfr0EA.jWyxK3R7PaJek-9MY-pR2SAEOWJ63qR89WTRYym5-lU&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cb030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjE4In0.R8Z5-GYt5iuMHJW-BHtmuT4-vsmyxWqYGvVahrfjYhq87ZsOJzGpMYrsouxaStouwBcsAYzuex-wR4BFWIK1XHoeLDP3ZDKtfmVLQa2gLZTZHUUDnvC2ChzC48Q5IVCW5AmZ4Xr8qIAwNyLJ_1FVAFgCyrpCvpcu47C3P22ELaWC-pDn4Y0iF2AThdyUi9St77gC8kep3SQX1_BKCXMl8bBTl57DrCvlLEOW4ipYkbyoX24r53B-utZk1FkC1wWCNAQx6DGqS8NMBPxPImeVPBNYkZHS6jzErEW2Y1zy48fz_GNQe2B_xCY5UC24_wtZgktSJ9t-cQAdCoGTDNP7E_nEJk2GjxLtM_SoZJUQqmO9VECFB3Zn0lz4ADtdFA2Tj6p2hVDMCG7bXyh3ZdK_VDtsKXs-fbRPLEm4AJGgerJU9V830LoewDCU6f0f56IMN2iM3zSVTEwAimsOkqBtTiTRy7rXynuoEga2X2OnlbF6DWF-qt_7PE9VQ79pzyGgGFsV0U-7IMm0NjXJPwAkeQ.qtnQzmmKMZhWPRRFssC-nyZhjOVE4UwLqlrBt5S9cJk&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-ce030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjIyIn0.fljzCA509U1cqDEfjiNghkorHTkW8ViI62qZ3HWONQbOKrSi3ZqYJlU47B6DdFOhhJPdaA9ZtgOiRSFXJLFEuyHy8NiiiuUTS9VidwsyOWeuu4a1WO3IqXrovkwKeIrXQSYjiqACPT8hfA6SVuCiHjbo6J4xl2rWNChkgAObDEz2tpYCAjI6iBkhxQHJcPGFxTTVPBZ4Vzex8h7GEF8LQSL_cIOfrnM5Wfo3yCq_PPZyvt4Dzqo_dZyuhB_dS5rEDxcKuT6BKFRNxshsQOm7XYCEL7ezfpdS0OQhBgPfgjaAGSEWANfiTP0Y3NPj_zeM3cN_2FbP9xZ3Vt_UJraa3Pz4iyyyTQQz4PR8gJPssPDHmQ63637NCnlC_L01nU4NDOyjn7EP7_wj4Llzl0eM4Ct9_SyU5RSIuO3t2kOB9FXglkbXeG5RINzZo8DPORhOSunENHYndQ2s9A08a4q92kLCkLpJLrd13h9jr15iom2rC7nZUdTgfEOHYL4FTB69_UoLRZzscmZ42puLwiUYNw.dOTsJPVX1mcVZr5tOuXTRzVRlT_FiSxa9ZfaWjhtPlw&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cf030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjI0In0.qbeXXP3Rua_IaotxX-BBoeoV1aFx3NtHw_J13YUnmMakUWwSiiIufXsgrQU96j-6Yv0Nli7iDWdy0nnw-mwgd_6NsxUiEg5VOxHDxS6_vYDdQ8orEoEtkce3u-mXlYvUwQhmyb6RqNMxxdlR1C3e5F5Eilel78klAQf-41eVWPcw0GzavgC7L2I_qIUvhT7M6qs8Hnvz8ydtgRggn4KbzAlQ81ChFkulUjQw8tc2Qbt-5Qc2mbI1Y6epOjTXjoD-z5SbMYrEcvpqRq_3pOgof96KEs9LyCHngwTcT4d4yQrI-gHwWADP8vcasRfmCdAYd6gDPsot8wdbw94rqGh5nZSoAise8Nyf_ctJaoyUHhZkq9wmojDGBPmMes60kUb_XCc35Tg0e4jqgwxLNMx_Ep8zraDj8DgXvBNzrrzYHSYlHGY8nQQGVu3WT6epUxbyctpoks-CpvUgbdoiK5kMsnwn3t0kAd5oSW0iTvguQqw4LDdRKhsnjKmyTbAvT0OdEICS8AmSi1jAODvNsKfZqQ.N0wt4gKXvblhTuLxRuox-UqSz2BALtf1lNQ6Ot8eAxE&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c9030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjI2In0._yy3AHBurb8U4BAMtxTtWFK6RthsEJmnofjz27xbhpD8YXTsPI9_pVOEfj7729txI1eoWDabljVdRDijNwDxn-rpCcS4c1i4QRK4KLbBI4WbLS-6aWRO3VKUn090vy2Mk0xBNz0xkC1dRXOLnkxeQVqrVHkufiZhSa8FUmnZUKr8PnuUUAAfVojkwtxTpyUmoT6rZqVs2e-uJkvNhZCgTV-8qrUmqVr-q0pA_3gQHZv9-WdQfUMPcRtahSxIswd8N89sUS-FTjI08c4wgyeoebGhW71ecrvOSauWhlFdORMTiVQWlYMREXIVNCju3Od-PUI513s3siLVKtG_m32mE-8crHr34TO42cqU6BiqWecd8l1z7HLelhFOmfDYGPNsRcrpcPgFpR6lR_K8hBgC1Ot31W7Jf0gUX926zB51wUtG813OBknzGI9-eySTVtAvkmtQGDtGIgYmPO4YLsh_W_MZLXXpajxp3TaIlJV9FBxlgT7v7n9knPHKA1bYwaUBuFhVJNS9Lc-UkQ81ZsqipQ.H1I_-6NY9EqAVZMMdA6ot3th9k8aHFitgLk6rbc8pOY&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bc030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjI4In0.eeWOj26xGfCeU3u9tkqsPht539yjCG5-5vSHTSmcr8OEGWLCaZj8HSmN0zVeIB3tppy2D4bQtpJKDyAtuBYk-wwNdK47sRMvQjtrzzeLYlSvPDp3ok5SGCIyhD-PeGuSVKSYRn3XCSmNhPENsJnkNHVLEH7DimoVWDmni8YWLAKo5J-OxqmoOzlyEmNUF2zcv4T19LIrO9wPJtnq4gnu0dVP8uG75QazZg5H2k_J85tvOW256jwaRlDXZL-1GA_0aaU0VwGHXCiiAG6VFlxQIWp0Jfw_xg6rxCNbwCDGXQZINfumc5nymtiDKTM6vvXUgXv6UZl4MwPhdAhJgWDmCdAaYreuihDYjQ67r3IH3hPSJYmsPUzJvwzKLRmKlee8FL8Z-oGCxE2DL6mtkIsIjA-RqF8X64lt9uLpFxREJUfW2x-ERxYDogmzBl_I7gKctl1DRXee6D-k-u_veq7yO_4IgcC0AiO2c7dx09UIuM3kixtYrkasWGpDqbreMJ4Qi4O1q9RAm4NtJEmvIGXQbA.y6-FSS_PN1R6cVPss60T-nRicObNHa4NEESEUM2T-uw&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bb030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjMwIn0.tVVsS1LcECCbCpnN0_aPhzVAPYkEb_Rk2W0QCDm_aMJVTDIHBcnSDD3SmFSHi3x3OGOY5Sl6A9zVnZawV8IJSU8lDCVUGvK19cMDekqEzZKs5RQslzLI7yaqa9vKfGlRPMQemooAJgnJU9dlhw-bOJJoU1CvefJViNYDlNOrx5XZsFYkQf4TqaFS2SPKu4x09AIx0bHKrXTFQa_JfatdZJN7lLPoTziIPCFr9LNOor9rSPXdBh-hIsvQPr9I2MAKrR6w-q5zj5e1c9YbVFN3mHQHxoB6g8Fu_wYnxCw2XXngTHWXIKHId0-qRosX4LtLIMlX_abAq3usMjQOesZVTfRlgawZfZZh6c7as42ji9PxMvCfR-yt8VJVbvdXSNvLgvVX29rM5vQNSaiNLhM1pef-_PrD02FuvgFSbwj3hG7KiGeqknCrsZg31YxIvq2Bsjm0kvWjOKhA7z4mTIT-A-fsAuJ4H4t6szbqfZuUxuab9dTmGofKdNS79kuAONcC9foFTmsFOG09koCIHDDH5w.bSlQeJvqw-UQ3K6VQ_wK-aE9eBzT4f80r9oZb0q_0mM&amp;ApiVersion=2.0</t>
   </si>
   <si>
     <t>https://cf.10xgenomics.com/samples/xenium/3.0.0/Xenium_Prime_Human_Prostate_FFPE/Xenium_Prime_Human_Prostate_FFPE_outs.zip</t>
@@ -592,250 +592,250 @@
     <t>https://s3-us-west-2.amazonaws.com/10x.files/samples/xenium/1.6.0/Xenium_V1_mouse_pup/Xenium_V1_mouse_pup_outs.zip</t>
   </si>
   <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bb050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2Mzc1In0.SR6xu-g3kCpgSqpPiG8-xmgmQPYFx2Y6FFKzAqGzclhtpdN2evY8-myd98UaEhUJZI-71KZgFIzZSmDhNcvARM2LqPcMrv2ZNR1Vz1qymjGXiSrneivfYCtVmhlqyGE6kqgxRU37yWM0fXxCLoZ4CnUwnp-g4KeWiiiJ0K83IbxmyxVSpiDNKY0LbTUIjh5sSDP6btRH4gREu1hy1CPiozlMiIWOIZw3uStjmuEPgcOXexn0Q_HCyJTDV8iNFI2kb04RokJ8Xq_-zp2ew_WNhi0hRPXNJBfxk5FzpMR9cR-wLCtPFV_StFeKxWnv76Gj52lDL8jmWZpvXKTQP7JKdCvU2T0VpT9CZrstNY_T9f29jozkUn8y_xVeX77zWgQExEg5Lp0SzG9o9hS9wn3iHeRC12aiuzSx_yAp1F5gSypWAi52OBVapMgf81KTzwmOYNC7tkyEBb1maWWiZlyeykyUuGe_nNYykRYU1yeQLDsGcMgTzWCgRSZUzRvg3HeaWEAfo3PQ9Ks-FL7Y6QRmcA.2KsH7IYRjv4jHtFrCyaEgu3MiREeFiX6iNiUfA1OXcE&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-b9050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2Mzc3In0.1DVUSk5YsI415VivQCDk3-lfdV9-sqOA4NlysPc8mySKM-0ih-s8vM_e-FMaa9AibmSCrLoJXLE1BescZn-6XDreu4q3qkuM6-R4blSHEYDBjlDfeYknJi2xCnrSuWbKac7rQoi5nYMUcbo4DdBHRrm2kj_pMVCzTWxKT7ytbGLo5EdYyH5eP34YJEsew_aPOA-oAK3DjHxaKRuL92EMjDhnn5uS9m8lOjyl7TTNRQbGkC8tyxWWK-wdW3oyeKxzxaIYT41AmW_EnWSIkI8gAM06mepjoPifugOiuyDa0-aUkFnVTffzUNITWcQg2Xe_5huJsDbzESGFIMxWxm9jCHqpQ5ZPAklaEEWMWQwa41kconLlV9ZoW1kc0h_96tqnJJg0jOnz8eHSAYB2sC-UREnLMp0BOYOC1uvptTOZLEIGLFhvF83lb0u5qxECHMbY4WliFVGw0JofmkVSnGsqTIRlNizeq5KkhBWdnJmtPmfFjiswen9qfmhtncV9A3ibjyK2kB6Ic3WxoDOMi2s8zQ.q79K_n7-Nwncm2OSkvfduE9aMjog0IYZAuMh8_xYDLA&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-b8050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2Mzc5In0.RhkKa47sHBeo2AFeGnoWLk8nWwoqVGkLZAHDJFzoAjC-B40mG9k7Nd5BYu5Mx9i3-YB6GmadpqbQweZbQOWYPkkyyTHgyJHtvLKDNTNvy9K4Ku_T37Vo_oza8xY71M2vpiRJp4lLu5zsXjVR9py-F4PNZPOW054yYxgXtg3A5vCZPa3GRuavOm1D1I_3zvL7iV2IptBq8wUj8x_N84BH080BjYgqAfuJl9LhghLDqW2exCBWZponKuk5KLoQxLaSHZ5m3gb7BCHbSCYeoUmAteC95hAG4CIBnViMuIyqaAj5bYTlAmupVauaEzyb2iPJmvzaFQrRS4yQADWvbkmyp9CTF_puhCT8apg0BBWItXwHDOp5JK0qopKdo0CFdBvYEiI-diGjFMjhsr4yKHZ3G3hIlYL9IhmvzsT4SfgKy-oApcoXsShTCLfn5CIdmpjLmwT9gqY8kXYblZm5t2SCD6shwV7ltH5GH95u_NQa7ijcfLM0vG5Azwqag6znV4KfKoRK4vAQSvs0JSysdHFyMQ.X1USCecqNsaIQaXDoUK5q_pdDi5knhQ9hFoB1JD89eU&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bd050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzgxIn0.SVsSC8yoX3tpgBDVp-bybHMDIfJO1CYhiG54t3EL5zZXq7EwSLJYY8_lxIp-hiwYsDNwjcBtQMfjibmlRsbgkxKZuxWic7WmtkRrVOgADicjrJ3PeNXJccwwn6JtQjsm8SWBjXc3tsmpp3LBkcFC19Cqg2UagnYtShlKKLbOdOmyVEqbJQ8hQoAzX01y8lHfMN6rsvu-v0zo7DVo2sVtlgnq-53JpWbsrJfsZulID9QcTHfx8kJi2xdA5TtkH4XoO341EGKiGPK_wHNarD0PYtmReYVE3v_DruCKPRfn6cgBfPPfoHjJM5CahSZIPUa3itKYXen9e1W8rj1McmVMGOmn3zU8k2h9_-126jDNJznIoMHGzjPTrlNIjfuLR9vHXZCDeJ65fVgMeLImExT5SkgIk2mZyl1HkAajJzGfqU_MovFrlQj6abMxroA68k0YR0-fWTBW_G6pW79x9PrDANv-iRJaRxQzjov8imR2mTjELzwrC2AkMUk2XcEdoH9_2oirjZHlCS4YRDF9t1eXTg.OEJz0oE0VVUSZ2qamdZEMAA46w8BOREEecPGt6xdQ0U&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-ba050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzgzIn0.d_S9Hqpa0VdJUlK_TUL77XSUDgzYyzi767Nyjuc0DAphpN659FhgDXbMjwP6wc8FywqqTfyDAcVEKUgkh418hNqBy1kN_pl-lpycqP_K5tbn1I53DC_RO_D3f_MQx6aRes8Uf7rUHG6lcpNuBD4vOIc_grEakTJscd5Zy4YQeT17o_1HNTWu1zOerFCu6pglVq3w6ickN7dRipThFlgqoRTpORJBq-YTgvxBKpXFOALBKJO0-tRVuBafxd1xCo99HtfWkL_l5AburnnFkJ_fBrLQgNGcvsgHsHAztYq5sH3pQ0lp3foGHlM2GymJ_4sGlMCelbAM6VvpWVTIntJo8ocduLsFsQOZX3q7ws4-fr4R1EY7_9qOhxbiV7P_8HTJxaNsC-uWDbgHrYj8xLq7_CoXtRoJ9xbeuehyz1DZ_zPCmjnOZiIAEP2qhWSKgXa7VZjUxbMjRprrk3H8u1st1mjZBvYVeq40Q6LVaSg_-shY_AGMVIfvIMCMFFPmozW1LeDjwC4Vck3YCrWNa8boaR_1UE2dNdg096HqtmZMxXU.8p-4qIbg4Sh4AgiDGy4n86GID3Yvz6ZB7iccNcDtKjk&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d8050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2Mzg1In0.8h8fP7KrTLH8bEODFuS5SeYKMT1S-n6tFuI03IHJzFGlcbkjIk6ZF8wNW6ZXepI4-SKs-LkjRIOEsJyIvzmTZXJhEf1bmzB1emVJEv1NB7pYLk_IqCviKnSTveqgaGdYFnjZ2q5zfrwwLbRjnwxtIdv0lxd5JpuJ2McDxDMG09f1qS6oJzy3zX1DVlEVq35NoCUt-q0ko2lrtkiF1cDN3m54DCF4taBTG4uTa51g7YOpLvvk_uV72I7RFBuP3g5y-Eh6AIjQuXVggYDsJb7V_bYloVfA6wQqWR_nYZZk5PrHXWHCn5tVDAbulqiR2A-77MqIF9nOpYhX84TJMv0wFcU2hWJnNgsOG0iun3rC-Qcuz2TBSKvtq7kv5ACmCP3kap3C2vyQBN_yB8m9jb5vBTkm5JTOw1sGtJ0Zeh0GAkb7damJ4RPW57jGaSsv8xL-4pgv3mIQ4R6QpkwuiZTubJ9vsmmvcCezSdvpuYFP3gxVaaYkJfDIANu_VzX59G64bmKXRt-Yoim7r-Optu2kNw.E1pZK2rpyMK1Vq1qon0W6pS0-b66vOf9KdIN2u0lFC4&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d1050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2Mzg3In0.cQdxSEmx7a6mmDSXkY1PWH3bMjpJlVtfWO1CyJgTtIuCXSn4ue1OBKePAZfhW5HlkJBmtCKblABH3lY36t6LYw_4LyGY9LVYJZKpkD6TgIlf2R6nvdsUTT2l_jEZaqLLyVibDoKXmLaoAJchbGdhhiIRv7ryBthBk-A6r4J_C4SWQEyoZrCAIY51kA_Yir5px5Nicg3u0FzR3tBewN2dTXau7ueylTiqki3jw4AFQ_xrO9_3_pqdodoI4TgxCQnL-V20tUmG2ZRBGob-A9vEsd2MoEqor3L73jkst-ykYNy_BhTLkWqIHvRhKlGbKy2ynW9AbaehpcO0O_vssUs74RJdWeZOXpet-t6vACPD-_xATdF9N2dYdy1fORuwEUV50MBCQqwD7qTGCK-Nd15yAUay_X59r1XzeiLsPU4jl3lYi2WUVYs9e6PEMTX8orv9Z7k2vBRiKTH04YrTcEKNeQOZ1MDtn3C33Hvr_UxqjMlec8y92PG_q4Wq7EQ8Neq3e-InJwsHYgjo7NNm7a6m9w.OduoaWP912lmvmJBwAVT1qysbfKwJ5WL2zCdQq2JjuE&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d2050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2Mzg5In0.Ja916cvr3Pc472j4asvyyIRRVP6vjMTLhaDebNn-6h6-UsAQa8vgH8mM70Y06UPj5I38KBemt1Ry2ncTXogA7JlMPjc8sjmLP-ptrecFVU1FEou3sQn2nwNqyMSBQjJBfXZ0ollCgGbM4Dh61zpf2Wf0lntGssx2ICFTRG1N63iUY5aUM_eHGufh5Lz3zex-AGXjsyGycaaxNT48SsnEQb8sYO8pIM_1ueqKJ-eEsqwv3GMvcQpYV1-nmSNWfoYTG-pBF6YuOZ3icO4kISbWOQtWHhD6O9hIzDk33u0m9IxlVAZG64w0NO9U8TiouwCNQYnDG_e5R8xSGI45lGO6sm3DIU1eVokwRvXPF5BcXfyJnlJ_ioKL_ZvSr0Kw9RynLEBF_K51VXXbbK-X3o4cKAP6hdb1TGBBPBe_5TCA7qEUE6enROfnUOvbrOreq8PkJbdGJfAIpujElzh5KYLXhRcg8wcyxC7RxNnD-EVbCNQlzMFfCLiSJslUVf6aj4ywKk6H-vA_v8HYqZowupXZSw.4MUEyYiAu1_QC3PA8Pw5lqiY1FoZN5ghRJt23qmYL_0&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d3050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzkxIn0.9aZPCVSPzqJ03k3k3-voFA0zz9_zyhjBa3AahDUoqY7dUZ729cJwN8WmYlvMNsRKRT5-gkLJ0t8VN6BQBbww6J13-va3hFVdH-2ni0DDj_eF6_lu1D17KXDvT0Rv9ELLOZJ-hcjJJZo-szBDrcucO3CICXiZfXHkQ33Ys3WE5EfVhjwsvcF3lvfqny5PWMM48AtDf5MvO6f0a-3llWfehEqdIxvLPFlcaf0sCKQhZqkuC8t6RYhOeat-Uexfmy0ixVSGh-WbHz3DPDpVS1WBAdupRqvj7wAn8jUqPOykDClVO817_JddILby7j9fG-l5thWwLHfLaIwRDA8EXSJHehGhF3c9038iaLgGpkLR6jBHR-0A4BpUKtw2PFTr0UF9tEfi3g50TvAqjLK0Uz3GUu1pQiXrHUGTwxMJmnk0blpipayrW0nCnidDKzYyV2hWmKunzp1_MMlsusoSoDGMreb0LZ1AbvniP6Rlyldrdhtp62VgWPwy67BaoWIaD8qPisJu915xoQ2tP9EZPpByKA.ISrmMV7eTrDU9ymT6nThBMtjJ41nva-URG0KUy17gNg&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d6050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2MzkyIn0.pYCzX9RuTsx-rqECZnAAw9aQ_MnRlIw1ML-TwVhLnzFUfnKx4nHtqQDzY_iXJ1QVxj-Qjrxkg64x2Wmf_iQoGKSDEaARMcG29N06sTHcq2S5ZFMHyK9U5uC5wu5Y749n1zDvVnZEt-Awvz899pMZhaniXdCVCOLi_F3dtMWytnbpwrvahA_htaqgCzEuiBK9NNXNhTr65ZddMyRPc5HYZmqHJOp87p8CXCpdjaQyk2XqTq_U2WFDy95fQf9tKETX0vTDD_ZpYeY5tI4kOWAkXE_JSruzxuV4LvSbXb4a4vPg8IKM-FXgdSQOP0nDVbq8Cnl9_wPlE6a1Y2IBMjR_fNwGytvykOljgT6MFGIj5JEZVEuBjIU5MSndj4w5F0MVjw3ELELpsvt50sdG7y_1WWBsXjamRw3z9r3UcNVo8jRFndo_CSw23gdcXUHXhPUte2rA9iefgC4kYaMjI14a9wsDEHR5bI59j85pOw2biJGZ3juAo1psXdvbVGW3-EXxuKUO1nv86-1B_5CW8Z0BtA.CCHSiMc8FRFGMHmwmh7I9MZ9Rx5-UwPmDR1wvqsPyCM&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d5050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2Mzk0In0.gstON4ih_Z9rrU4Jc2Iu3Gir6I6CPwwPxvLlKq1pkVYOUWfsQecuzHupxXLfcjQ2puADACwqT0rvKWxELeaNDhnFnI5wu9rLkQhtLReNibKtMlJT1gK77YIonLE0ESzNkoYY3LLG6fF2jhZnr2daqryzVDb4mKlCRfw1t6Tm0iB--3LDpuYHfwL-_IhDYblniAgGQ27dqbM_DJEMGGZ0rDrEsUVGJsMJkuRs4SW5GHWmJEpHH2aDG_727Qya7q4_bCTkUpVWWOwrjewDJWi2eePlG0YJOSfTdwF4xgFOeMbho1zXs3kA7WLRuprYyeR-iN5hEMgzMDqbUmzg5KnGmyk0K2iNh7MaFWZv8zaAk6cK6U6wo_RonEAr6X6XHnqZwW1j4MYHulsWx9kDtQLPwTNYhhK2G4lqBOq9FaHbfgx9ncywkHEA73uEGx5dh-Nw19EHVhkfn8o9ZyCSVUU-PgjWC0-7iDA4nX7OvOl3bw8mkKvsXQupqqRFnPqr_3VEn0FIdRCRtMeB6F2nSRV3pw.vEfCWw4dxUHJVTsLc563vasf8o1eHv_sEUYbloYrDJs&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d4050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2Mzk2In0.NuPyn7f0l-5crEecJ2YtWA689Uxmk9txsP_0n9CJmpF6FM_MW3drnbf9NxoSSNykHEZyc3zvfWopoEJyk19rxHSrOdGgAtzlToLbj-ElIE1niYo_ZXeTqeNTFbIAnKm_fx7ZTlBfZpT29Lk0kuZjj3MgEgxY18mDihnh2NPMAhFvBu_ewm9aiDR2SZMGyJ-sZuI-wJzy9dGde-DiqUwelLxmaP5JLLJp1AWC21qdhJfTugnkoEOfZFoKi7Oi0nDtvtajB5xB8bcSomSLcgdmqlI0hXronpUb7zuwPOOEXtBJQlgDswbLJvqGC9jJNtnCJ74AgMrUioUAg3t-QLxUWxboSnn3lHYLdVfsxUi3W4Lwaq2kBGE_vuG9aFadKOimoztZVbkhoSa_BbeyJIYo57tzOcdLZwCULFnX1KqcRI1m29LLtvuytK0Dqh6Qkvw1bWokCxavW3XAIOwrWp98TRBvTDGLm03qoTxoN-jtTB5WQPUjqdGAY6renh2PDwb9Id8vekddt6y7X9AMR4OSmg.wPgWF-oWWvXnh5TX5NxYKKtvtXKqU-eB4Nk-HNAZf6Y&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-7a040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2Mzk4In0.jkBRzgPc0OJ9Mc1JUzlXjskebTQRCeV5e7G1sqLKjmkW2wokkFWwXs9ZuC2fbXZQUMz52ZdzfepuS68ZpxcSgQu9IK33zxBq207YlvhFCPaHCC7oSNdDCR0WVcfg13QOvRhjc4byf9n-_7t_asFdRTew6iVSoHiAZO5n0RSkyvviIShT1uyl5HHDMzpc0Mwf3uWe_5-x8KepKr5EnKhGpboB3Ey65TDdsAPCXioPGCRO3SO2RTDGuwXIOrlOQNSRfQGzQLZrwq1fVfD0rn0JWRlkt0P3q7xvN0UbClnZRTbKCzGsEqeqyNRHDM-LJqjCD46ohKqcNxTkaaE6VSoEcyFnhHRZnEopEoLxhNMk3YW2OpwW7MVEaI3Tu5qOsWLusSc-_qhC5N5xysUs-blrc57jHF4EjVMDKjFOiz9h4Vt46l-np_iATsXD6_3hsb7TPfqigLYICx1qJAmPRkomOxCTipL-O8moNzS23ay68Gq0ZWFW47VvtVMfQxkmjYLqtUyW7QaVBD6JIl0Y4rSncg.fGv0t2W_8CopxdzoMwVqzDKC9i9GCzyndfgTJjMmqUc&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-7b040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDAwIn0.5en79OwinVbYu09imOEtr9I1rCDAASVzhSedehJPhIzBQrlD2oAK6igQI0eRYGCabGg5jTqYeqUMijZqR5jEUqH_rHGX2yhOYc8UUY468C8Fz5Tm1QXCYtUY9RWi4DsHAGdp0T-xbnsQL1W_g2dhulKwCkEFVVndZ6RjR_gZcCxv5NkUEi19P9N-dYKnFBJ6As3PS3-sCaVKESUdmkAFweEAaHKqUlH7vkc2snnkDfvQhIA33zZQK0Qe21qcuG5rIqtrCDQ3H8sOW0P3jOt2rMuilx-ViTKdjYGpY02x0ldi2gvUgVsHF4uDFEJMyN5SJr6t4LKdJtJIA5OQDbuCQy9ZPp_rFHeeqJ-5Q5cUG06pYAdAZQLNbbq15iFnHert8Wl8qSNkC6fxkntKsum4JPQ4V6qPvHoEBNcOOniiSZXMWu-I2GLZQW23uK4ZElVA_65QvKSJcTHV6n0UmBqDCEWXslfIVps7pcMX-dw6NzbEOFuWXaR8Hb7TKK2ti4qfn9VCx9tLCJpsZ-CK4TjRWw.58nbt5ssuQS-1EppLaMVW-s_SdeVAh8Tw4rNImOMj_E&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-7c040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDAyIn0.aovUhPSLZTs5e_rFIaQrHgz66jcTpGFPxRki8Ir4l_63tgRBbDsqEYyZ59TqaIB5VIvekRC9C1DS2xoD4wvjOaL7uxirUh_zE5eTtwsiseuB7F32jzkNeW_7tsiol-2hmv4oWV_lLn68_suPL0a6usfa2fxR0UZkFShdBABTn_erjJWSb507bARpCiKDeDFrFIunsBfCbmIHbK0T9fCfBzO4bynMCIlyYRbzridf92xLC_vir2VeYUmyyGGCSXE-5lQu6CgE8vfYd4pJ_MiqlK5BjwXN5XsGu-zOeWHDvQZ2E3RwdrPFk65skDXoWfFPN2H8Jr-eC2Jl6JWq2A64vvBH8u-rLfe_cf78DJ5pwWXLAU1XvwNKTzfK4akJeIbnoBBtHV8GLXI8c8-eybWfbVqmugn8CSEgjlNKbfCeCKJUKihMP_ZQZQFd21Qhk_9vJEajB6jsNQdANzVsE99RSD01o-386epYVkN3YzGK2GvFOfdIw8PI-H7OeUaNYFuAfXiMj7B1aZ5JwGLtH_BMhg.xHg5ztN29_DlpOCl0KAFPmGDESckyLa1A-13BUgGKAk&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-00040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDA0In0.ozy2SJWQGwnJ58XUzPUCId3BceHK4mND6JQ2LWrfhXfjXfWctO-19Ab2BfRpN1qbDjyrwF1cik_RyxKnCLnWj1yHvA3Yb8SGJNm3PyZNe3s25Mq3qdkieTipXyopLMMOKM_Zb8Q34jqAHg9QC4KVM0eWZVxWkAqVJmyCyu6wU_JY605LfP3qUVgZ6AXqWF-ppO6dU9idvsSqqvE_hYrQ9W2Ail0Rv3omlaN3T7-3z_f4Flobm4ActLNuEdRbqk0w8kZRSaCTwLwHW4CGX9hEXfFvYZWJP2v-lsrO3wXnzPp9zXN6jnRh8X3CdqboX-dFd6EVdMeOSLjful1J07UXJuJGfZY-BOCHN1bTXiYspQCF4EFDQb3J1dQLe8Nx3WGWTPlrrI1i1CdUHbHhK5Sxzu4Lx7U-1AvVaBpTf6OqU_BGaPZdtkmiUqa4cpTfbnxW2tElXQwISezMoV1id3j7lFMpezoszbIsX6x9yAWcpWAt368wZ6IXbfy5nH2Tioe361Lwmvj8YCKwoLnDTJRWWg.fgkpk1gLuqOv3vA7vJeQfUftNFuS2QqBNQ3sF4W81Dc&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-b5060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDEwIn0.2koYWPqm_yXbL0tyPw8oXp8-xlmMBDGb8KwlN9o-nuVEXmGen9WpGeSqqCNbHdgi29XOTiOhZ6STQIXJcYuacDFgHrglPG4FQHXgZdBvKu1Bg9WFR_GegvRqZEU_THb39lQnlji8xom2-sJoNecGVC8xi8e253JgspmcLx5BVBY-C28Y2WqH3Kh_AevTcZc915t5zB7S5hqWnpDcGbXlL58Lryb4wnMCFfvQdGJcMxGF_yzubeWwQ7fJioATvEbXHDL7_kohJ1p4575jlEXxGq2L-OJ-8Y_VSiNEu1bQ9SvQzVfNsTIDtkwiJXhXVEy37cnBxSWiyubmnjB2ZAUFKioADjtrWWuab88eojq8Hc9iOwixAibYMXYt9zEr1h8sfBPocTeeFDZjQXK8q8_ASIVBF-h8v35udQppviSToNR6s2sQqNJIaomsW77KIOgIQSBDM_0RcogGrnW_u8kYm2_k-LaRmowTDWBywUnhdi5J6OXkNG6da76duW-Vd5FZztaGXNsEtdyanxBQ2qzlZw.wALZARkOYjXjP5LDq6Qw3S4hjigJuN6MhwUp7RfN06M&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-16040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDEyIn0.3obiPR1xQka3dVTz1HbHQmR2AFAUA1QuKGVtSUoiYW6l7WIp0bzacTm-_Fo5GlO_fslPrjDp9DLxkjma821nOeMwj_K7f4K-oJ9EC1H-PVOXm0J0YH-70zj2-rhh2a7qt1JlOu9r1m6FSjAI9GxghBfLudmwx5yg3q1DY_XcZ7aVrvHRnVE-9pyiBXR42d43qtLeEC2oQaNWEoodR2AE2-GAQliUeImZ_r5UvU_3oXvYJ1ZzUlwvSnlXVKyvsRXfNJ0PWKO8JBByApSwvZ1hih6-INkx3c6RhCnHDd2CWeLqRaUATU4RhqC_hJgMXcv8uu66D4NwLpnIq591pgvOm36vGQHcYFz8SZ0NDpcnDvDszZVvwp-FV2wKaChlE1B7rHGhjsi74K59hS1-IShBhVyWfX3PF3JyXpXobXHltbY271JEWnSBpsGF6R_N3iPlzP0tWl7cYtVOFRw3iOcEyT33wFtVb3_vwioQVhT_74j5B-woBeC0U5U6abg-ch0jCfWRbrQPcT9AcfcBiI9XFQ.LssdKe0xYqnKhJN9vLvIRlsXrtKIE5xRLOldtcEm7R4&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-1b040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDE0In0.ysa1uEhbJXTMoYZ25dGppkpcByVjM1sR88EhzIYvhEcRK5pNzO7GDt6PnMJYjvmQMKFof2NiW5Q4IGqbS1ZN2NPrZ3jxTKukiD7V9fnI8qnreewrKpCvhTciw4Tx0thoIgbOD3ev0cNirsGj3MHuHlMvs5gNaoOwhTyuVsoz9WjUJLagvcg7QF7TXBU-fZ-pfYD5lAsiq_4iIiv_7IhmPgleM9pkUDFciBZ4A3bpC0vE0vBM29LZF2vTTGb5ZPDH0ht7pXkAtYdPXTYxsfYuwo59MVWYRrFTHEDuflsGm3Hz2TwA3G12iAeycTXS6AWXMJKN_LF3sTrvVbjJAkBFW2I0LgjljoJ2kFs6Rhr-raP4zRYCHVX02Z3A6VaU5UMDkfnGzoa2jl3hUG7_tOE1K5ag9vfDWbZt5krbFpkZ5WVer1UZtvpHGpDnWmPXG6zKgB5Wd648sJz_qxzqvk_KxYqjqGBOWs5LtgdOBl8ssaVC8-AiidoYmuJamOLj43tbzrH6-Evw6T6uCvKl5e-0CA.rLmyfU9d-f604buzVdprmtHCtIObXYPLyYl_5VskrCQ&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c60a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDE2In0.L3XLjNB3xNjEQ0qrFA3OKIDHN8w-KzzQ909kC5wQonTkWQyMhNgy_OD9YUkNjARTUCt1M6NimJl0YYJnW86OjmlZatuLzNbxuyq4X1wEnB6cgqM8zISQCNN0qQXES5p4KbgUAtXLT08b2IYH-2hHelAqy6UPWEebmZcliCQZFzdioKhfYyZq002mCEJkxkqWLwttbB5zFBPA4UIfI4XPxjHVrsb1zus3cGjYNAUW4ZmP_KIuzzQ9KwSo3cYzmEOer6U0wvJwIALU9G4Rx3dt6jGpet8EiYQTkXN9c5jeRpyxcq-4CAIynDwxaVF67j6Bjms4aZ17gFVYzUM9YIJ9oHVIAMoMkCU_pdXPwPnTIoP67NWUrbav6LhWBNYcnhTXCkt9OiGn-c2CrHwJL8rD8o_vY0lT-Mq9HGtMK_uW01NdeOLzfSdVhUrTKt083_Rni3y-B948eudxJKMxcWVPbu_NyX_V4Gx3h_cc9s0OV5AIjxUhOXo8B9LNOv3n7rXXQ1siHvOgENk5-B-kEzZfTg.RpajtAwUZK4Q9r-gJsNWFTR2QjXy1uVO1Abt3SdR1ew&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c70a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDE4In0.fTyc-DFw3ioL7ndqeZi5yBi8ytEwFecwW6fy5_ZL1eOr3A_WhOADVBlfZE5i-oUOQhNiLSbER_9J3tQXCaOXYDxxKHK6_dkUxFHv9V_rAMbcLjoGOTuVNr__ByElugLThA2prYgKzFCiobL0ruv_DWuD4djQLlFJRRa2UPUKBtV0XA_-qYPsM8w5kX43YF90PDgOEYliiVyHTD6UCBWL4T3jadxSkGuDKIKy2NL9msMkWcQtb9fMPqVHe_1K0osDc-kL188AGWnNYMSYSYWn5srZsGUle4Qs_scBqGfYd7HQA09-z4GubMRyE0_lV3ESJpsoqc9XBr_ZmbKYbMfqxpTN2_YQSh8i2nuQFgxITzaMuFyS4gEekIYRBEJiyUx2qKdN1cjDWKAIKKAlwU0Jj9MIJ4TIHEQKzIlKT6HmAoT0DXOIp0tDCSKHFcTsaTPor19YcMfcPswMbelqXUahv8DwrPXzllKp4qBAkOMrKNlDao99DGx07xa5IHEWrj4n06c57fZhRY4MUHMNEVN_BQ.bIID-F9kAgcDxRMCQLfzYZFcknyiMEdA_0k9lq3BEtA&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c30a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDIwIn0.hXGd0l-k4kez_LoqTj2RVh44bN8QV8JtqTSswiRq4vK4Vh9B4N0rebeIC6AAU41yY7tqui3Er21A2ZZjc6Pm6iKBN2cqtozEubQJhIZjUfacw7mzwpG1UMoiBY4xhqi3pzXyQSZm7WtQJepmUifnJXuMx5r2O1FotoJxbtWpAZyUItCJo0gJKg52eSIXwCherzo5O8lMXRHymNrseOTYUueSAkcS4GuV-b-3GMkbPX9hM7pjR8Og2weZYrsL687a7aeaK0crZm0efPybPogtpHWre3RAaSKEvMLY553xJBMpcprNiOTtcDdtJPDP3W354VVOfqsbv9P3SriQ_3Bc-oXfoPA0gLIFNRdjAjmCtql9lX97Gm-bqDt2XK3XUDR35VPhN5kB36vtn7LSkD7_m1uEMQb6nd9YOxNyDoTFAldSWdnPnWDtQ1_J6kSfYfiyFo8FWSdSRa6ggUiBJPA5S03LDIg3CarY90r1EwPmZPOPvsnoXQMoDkvg_X39R-Aw4oaAMAb_k4mU8DE6ybdtBQ.JWmWVUE_46NFWDkuFpKvmmChq4hH2bGWRB27fQ5-djM&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c50a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDIyIn0.qdk2oQaWOOD0q1Nm3TROfysSZURflq0q_VOshcASG-L55IPImQxzCCqYMwTGHqLzxluUGTySMzBz3Jmc4PaT7d9OdDq1Wx1GmeL3D0tBYBp0vNjrGSVmf0tQ_gT5NHxvTrv2CW5JjK5YJ49ov_djoasytBgDKEbfBNZkEkRQALztjEARvR7qgDqeOtszukaeWFwR8_PEDJkcElJYiA5WlFqvbSlCWviX5F_uyTGE70P6wjiwbw80t1q5aNy9woBvuvu3k0OVlmpMtodxEjmOXXGxqMo9hvNF-jaLxdWN4QZWAsXbJtRi41yHHdAIDRRCBl1yqC5v5V9AupBn1Cxy0aNFetCNJr4tGarJVDqOGKEF6JfZS9Vl6hY_OWuBqUKDNXdh5IiaFeaofZTQ-aPCPU8xRLkSU-lYwsh2qxNN8oyZ_FtqTjGfNF7PM0U-YMR33o6cW5k99T7i-vp0Rsz7T5mAuTM13oBDIW9AjEB4vCUbLq_uRvbvohRU5ZkAodim5_8JioAh0H97r8Avfw_hbg.ODi1T6eruILOHikHaNhRDVZjpBuS6Yxzf5XbCSzdV1M&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c20a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDI0In0.h9DRuEc8ewDOXBH7jkDX4klaUl3pgoigc4vm87MDLSwKduAQs_fZK8nfri3GF_zvWjZDIdKZydS0DUtWZxPWlMM7cjdCTYyJJgpkxarpepbDN9U3lpAN4f0OcIxrgO0UwLwiHoKZe867l1iQ3JXxuUQdKMClbLoTI2LIY8AV5A7W9o3mVcrCYU_Wlq9xC_U9nk_ihiYbEJGrDyXXkzHtiqxuFmIXfQw4u0ODtJ26pyD7Hic9L8xFwrWSXWi7MWM6xlNm-eRv_4FRGrLRNEz9NWncFRk0UKt4VzcjKsYt2n0si5vDcpKB1eE-cALi_7XyBT0ErIacMcRfI1cM71NPmx_8YShPwmfKmGvhkoY65Xbwlc0lKQB4SIG-xnYyG8lXFhMsAv2xDB0KJTG3LVRy_bpGWfIMQwUmnUirg13eSDJpA_Fs1ngBlNFxHrG1ApvE4Y3c3odY1yiR_dW4x55s5_6bf9AS0hsg-0mSYNEm2G2j8w5_ilPZpRKr7tuFaDUZ_ZqfWKeAJyuT5uZsfCQZxQ.Wzye8wadtt1n3jGkli677OS1NFjOKfQobkt_pyar1EY&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c40a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDI2In0.Ei7ArJouL6xE_pSpAb8H66_CRoZF1FyCKcN5I1JRqTg1u_yzLdsYcNTVXMElcxnn6nuDiWGfX5leDoUy7-wdaSkdKKWU6unDTi5i14yGxOunk4TCf47rNXJpi70hg5OPDZykQRHBoY3exRa9OIgel2ioQK3UBoDygPfO7Cq-zQ-_PsRTXgZlnsYeSme4_uXpodlPntLATxvZu_ppEjqjyVmipveLXgU5Ll5N1S7U4CXEH_zw756BQxILE7S1ovdVaTZUd0e1gAMtV6jldWPj8TzD_FJMEFGs5NgY2QsxkZnrNDPylFsmg0raSYoDEfFs50H23MeMd1PItqBLquZEqifzpEpvPGj7DKVgs8-9fGLYPQ_Kf2ZfkjuHPZAPc7Fs5TKVZehIXa6s4zko6w0bdrq1XgIAnfJih4M9KWesgKLv4-YOtU7Widvbt4iMAstG4uURK5rEj_sxfW538jnedSf_mdpcX7xTSaaQss-oPKF6ZhpQ6cwlqg3UY6zg8SuUEtv_O3S3JPTGF62TXpCTNQ.Mngmb1SLXOqm-vUUBOGr-_u2KX-FmxejDux4MPjYhwA&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-fb030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDI4In0.BjoLj3u2tcyp0YCojNLCpAqszjM8t9NU9DP8GUelQbg8Ib9s9tpprihFhLrL5yLfp-Sw3GkqZ790xpPJP-ObJahAGT_ALnuo4YM6VMihVl7JmG9f59WBqY-cT-g80aFTcaNZJ9ivO4UTglIZbdgpMZESBeoS95eL45bKwnqSq1q59I3OF-GnhbQhBbJbYRncC0yJ53EEC_W8hRfvCiwkU2x-HY8OqpCIe0ddnPpeMLyniBM1sjLKBIeG7IIDxkmSexML2x-Ryx91-L4c07Rtc6T7JzjTwbXiGtTRABSh5SAhbbJWb-1YyETRd9XxRKfJ4db1ujONyx7SDwXdb2OAE4MYMlMFD9QH2bKYSbs6UJFjrOe_xYCiqKWdmAvmDOYWfsXzwu8fAHQa2fLCkGO97sWoJA57OX6A3WxcwT5Y1G9rmpm-MsNiv97KtZUf5UkTWRY_5uzm4wrh64-rCfx1Fg2YgkiWzX6TIdjaIP06UEK5NNOXkt4oOUK_oVmaO5xjwcmphb0euX5RvW5ZA7zlyg.0yhqetH6DvzDznBhYhpd3IxjNMGWwMRIF1dkwz5Iy_I&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-fc030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDMwIn0.YoTnuv5hCHJdTyip55Mc6l70TAHdYVEt4ZjKf_n9xJ0ZunNABmWvn665hGQJCIW_e2FBQBy9YrHuLw6cxsVmEL-QZiXDkAt0SW3KIlDjEha11hjFUzaT_t6lzLYu8DMzktZ47Qlw3AluPr4tmcWlraUZrntp82iniritm9eA6kb9k8EHUTOEoK1v5HBZx35iM5GeHENWcetPlWFbx6M13k1MuQoVZyyTmU8fOHCKMzeEsmcTRxUSRkVUNH3ltajHs3F6ZXjJSsLNPZ0Z2zmOJC566gbRSzvMfFVAoqzP618Z_2njuWlLodpRMDogOhafshxrCwVB_aIXp9itfqGAU3wv24B1NSCdtTfGtigiZADsyu33GVOsZVp4oM0n9TTU77DqShARTcOmKIrtpaGunOBqaQGuJkTRDEFk0_pvksawhjGX7mRr0Ql0GmNKNkKZ2EMs1TEpvk4ZYoIU1vZ8Z7Zn7-x3YSiQ7LStAIApvF6BlLmpZiqL4vEA_Lsc_R0Dg76Ba93xwGWafIq5g4GiAg.bHN2LyaEJLz6O_Q_JZB7otlWSiOLTVhk-lMy_2GtCtA&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c80a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDMxIn0.p-BMa4QJHLLI2A_begRyRi0Jj9cViSAUUiFgE_aYBc9tRONcfSc2AGVajt0VLwaTS49BKa1MRvmDlusDGSqOAD6JCYNQfx58l9r_tz4z_F5gz1UZrFB7dN0KOxOnspX8fIh59Ui4xyxKAXGk_KCBEdNNXKoTvVTqXJ1TikumelHIz46Cmf3CdTyOtxSIhopyjFk9Sae3BtF5OMi-SufOMXnxz8Pm1lC5LvniYg_Gk0PjoWQvjqJXPWxNElcMckjXAY5Qiim2ozKag5S9m8Qk-2lsSgzhkFuyPHjylapgC8QWmHjSMjt6wjq2Qdq6vTv1UMggml24Dt2VTAeqiFnXCEj8z6YaEaRqduVpqAfVCvUyo5Y1ONXcj2ujqznWVq6UKdIYE4JncFwXKhY6lE2LfE-SQrV1QRuTAfvJ_0afEp2b_Y7_ZCuNUMNI1g6LoZhpApP7ZdBWsNeRNuBTimAtRIpGkhnP1C48Qerl05gWPya6tOB1CS-rK3sN1axVa88yqJioLhoHdmBGR33AS-0qsQ.QPZEV-klRrrmuIAYoTckbYkoh0NdB_lPlRE2csPUZd8&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-4d060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDMzIn0.XXnpwbsuUk2c0q7Jv6M962WX7qn5kw2FcnNlX9qMRvaA4Ccc9TixmAJwiEAY8MQr6XIXwB-acL77H5XFblc97QfyNWevS_D9ZCMtNRG268esRFRjmJ6Ezwwlxw-e5FqkaaEiVPxJTElLaU4weNL0KHNIfu5B_4qYRJrae6x0UNIDTrHBH1Zpm5HdtUkczzWFirHGANB1CTnKCxUnhIJDFwHstxvBsmCyIcd3V2eNtxkm3Cjk3KxhF0rxBR_DZG_jSfyEwjN2c3o7k0J64rjmH_rKERrvLALBMQP7bApxad2ZIeGVCkGmIhjrLQdSMN6amRtqCiVmCM8r7R__e9ydQCX1fwnJYTYJoj5BsHwsuB2QuTRN_z_pqsNbu8TvcpWAMhdePTjF-5Fl5ZEN1WZrXFn9L1w6yXi4eRWZViOvY5OVzTfLR0rYHzD2hCpIG8X92jOWxeaKwPtxd9X0qf3x5gebrgNWcznjEJQdLygC9QKZVk87pVkKWXJ_VRnUTtQeeJGvGSOTd5cRoaLxmeKDnQ.q7L_xRMsFvpKHw0ZpH9GaKrs6k7A2KPwKZfp-YuAtms&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cb0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDM1In0.x1BJnw5swCforXEjV9Z85RF0gLPP3dPT3Ro7hrmfigoFhC5o4tENdVOEm1BMbiPKvJG-XDMX8qBqiFzqeuxWNBt9hv5Sq5XVxflzjlw72aNcd6diIyNl4Ypsi3X0WjNDWqtRMlkPU8fgbMxoJj1B73SoSY9IDI2Eel8YGkUmMLH2drcOAouEabYoyIGbVyso5-YLDULoa9vQoDh_6T5TXe8WBLiAtodGnBCzx3yArwBgQdZ3i9Hlpc4si_oBduOyiS2Iy-7M8fPmtkMD1O8VF5GWcw2VAUlKFQZJorRQaDWW0qFVNAo2BSClpswXKqdWoBcXyfRYykF0bzEwfmBPEXHgjnLS-Sv7BOjxXIx1PDqFAUcDJzeD0hNlPSI1Rx43RWq2OHKq6mgAyyPVQmtpK6oYvpyzeuxlagB1u_KyZ5AMzLbkGq9XFvrQHzNlrLh7X5luwilUCoLT1YtR5eaYoFOdKxm-pD0VKIpKig2eX_G7gKtXTcDxwQcInkZtXi-97Ykhw9cjspA7QNWOMssamw.DgHAfVTngTUwANWStp1tmyX1bSNbAGGVyfBmoTpIpaA&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cc0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDM3In0.STOCj6rfdnPYxyPJeuNe8uJIBrDe0d-Et-qMDTa7Sf_W1z6eNTWLdsw7nPg9054QpB3Pm8Gmc6jSmCzCTU3gV8ZTpaS8QBA7_5-uwb0UELrVFgxxGc1AqEf1PxiIWXsJsYoZ_yFgMBotJaCH8TxJYu3JcU3u9UZJrlZ6lV_wwVvawwTnmEwU5wFm5qdMvd_S-PkI_NSQF4wICg1gNmcsOrSo5Tbu6cBcw16XUrbSs7Q2G6PtmI44A9wIPXwNH3h6-76IzKl-HQ08IBKmCgmXbe0vCA4asltZzwWonzA5V8r5fEttIzEUd6L9SSANW-5gFxvQrVgTYsxZJJbf2eXOIisjW0Uq2RYZ6i36ticceBudgg_GABqjGkBamERGa0sV0nfghQY5cetjUm8z9n40uHu08DzQlTe8NguJ-AqSTX1l3c7Px16YeFBz-MES7sniz2ykSAn8sImT0rVRMcVMaVBo4H6_vJ5shnBKk8fOv4cdL4U1uWzJF7T1c7I8leYCV0DaY944rZA6wshM3CLTyA.QLA48Ry-dx36ReNXajJiI7ld4bnWkPrQxqKYOcA-hEw&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cd0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDM5In0.chWpULlWRIuks1y9z0yEOdDsx8hNZPvdc-ZxKtYi3ReWh8T2EqG5gxrApLgL7UuurvDazE1ZqAJIqVc31JcHi_wTCvtdLYnQBN0ruLSdivoKVgRXDCwCsoajIQeTk7Lf6DaESxT2kOl4SMkSJk08S-z5SxDvr64CSebxuv7jNxwmUUJOfzEUv3FBWSKb4VyRGKk2mKUZp3WweAud6lnD4_SkmtTunUCP-bwtdNml24lqTAsYLFojngMpqJu0fedawn3cZW-9WWv2qZWNAJATVKCv83BaZmSuaflQ6mXJj39gm0jw6PGn46QJRaIEvMHrwsb3nDmkRM-97zGAIQDyuyNTc-JIrem8JnkxZbWwZ9kLDFYjL9CDWny8vV_p6kGYowIrQQk0dRJsgGzYeBo_ZfwA8dIg7LcyR910PYiiCzT0WprCnYqDhUThwW1USo0Vxc6HndfxoM4eSL_PQb5M7ulbrE425FI23EAwKfdaycMlGxJrYSk7Yj1UDyaioZ2_j4WOyZj6dCbUovQzepNUgA.Rrhlbu0rTRc9bCkEbnIOxhA75EF890GclmkRNpwKmPs&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-ce0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDQxIn0.I3uzISPw60ZWwTbrfyQGGAd9X7T5GoWVHErAWc1SD1r-vDFS2-142VfOttCyklbIR0R6_e3TE58sYTeQRTKs472xOY9bZXzFvE-jW3eCPa6z07mvwRffqqZ-_yRgbJBhOY0o8yjambaL2bNHdiV8oq-X5wyconU1he6Do9H4_B2DB2gj7NRkvVUVQnG1Z3fihvuX6Y7w3tBaEKyFd2-A5ZsGilotcQucohxyD-SDNjb0u7ouHNLNRk5QagURCDKizD-R6-9LoRhnyR6eTZfCg_9rE-B1WG6kPrEch-1b2Xlf6wrSlhN4CV9YR-57DUhv_ewRGGmig1OT2VjyoXFzeKkXHoBzZI6paly4RxVDw5k80cwiHJKzo0eItCnbvERvbK9ryFPoVJcltJCGPU_kAoGw6w7bhHf-Fk4le6FhOGRKwX5MHUojNUH2RS8CKuN7mcWKiaCs9m3hQRjvw47YuCIn_F2pDnepgdoxvcI-WsmcF2x0rU8tBAt8Vg6cTYkoa1ItrYth963w_LeGhGl5mA.gDSLnC40uUPZnPw6fuQO0g9bQU2LV4t8ZQlaJ-dD4xo&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cf0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDQzIn0.oXc57ryh93XNAyfbvE5SJwBrmu66cGaQJWNCIenRkhTKGSqRiMEAmrXWE8Qw1mxFSSigkFD91ZgrmUMs5KN9cpOpTLCuEco-2_gm3IdsyKQqlMBcO8Ncm1fCREQ1bsth4JsfhMtsiKDsFfpjVtMQEhtBCZyAw7sr55NgJeyWsBax-AhY6k393uh4QQ3-8QdocNCk0byDyxfVOjmh515PM2CM9Gce1PHIOBAyuK69DD3JKRfSnTvaOQJzjQI8waDaUwRj6I7Wd9X76-aGyAfEo6Ck_Gq99aZPxX2ePf6Gq1uz3EnTdGaEJ4RTIo4_5fjvIkVtKnRxzA6XcBtU2CbH2lYPLJp6Fb6wdRYQzuJ1MJthGDcMlYISCaD6ufcXMq8nnr3NvW2S45U33gH3WPg-npXfvXN7gLlKtBzHVnoH-cOeGzFbCXxU3uZJQPa-NZGH5dpu_K2BYzYYn514Uw1FgLwih8TK40-ANjsewA68PKROyzYMvCp21fQXaa0Vls53W_SfIZLieL5lq5qoFPK8Dg.0FvXJpDnFd60gb5G8DOBXeDkQxNMlVZ4cnCDVyAmBOE&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d00d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDQ2In0.WOHWvYe05tj7xyzYNDALkyYhBzepuRI5liuEHv_BtP-MdZXDynGbo-dmlJ49qp7y5ukXDoNDTD5PdHwriQL6GmF3ULkPrL-ciszZ7ZDwLrLl7RatWA1fg7WmTb1TI-7-x-mP9cWPYOleXM__vJu0e61bsc8fizgDJ7X5Q6qu4CoPpO1IzbxiFLozvpMszWYS18BNXR45lkFMWfuyIJWCHgNuU7ggBbhCn6L-QVzfUKW81J05F7GJbed4Z0EGf2wpLN27RFRQi_KtXm2TKwlP4u2ZRwxF-mdGMIsSEhkOXB2pScclE8NqNe6yroWjM7bUinawGvIrU2u8Ujwx5AOjCslShn_h95R62TkiSJf_-_6-kvYv-FmifCnEwnjeoe9gEbjBe_RjtFXed2m9PzXDGxL8QKJ3oGkPJ3d55WbqwsTNhaXUnY1464SV-BBmEkC5QyG3bWKeSBaklidOBF9Aies1Om9pvNMtBQ2NC4uiNg-rIP5EGcdkIV18Bkztjhxcnb3jqgZtK9Uu9F39fJ6Tvw.1P5ckBjywLXkV39BoEX2qGRO7QrzpOg4_UpnwXLmS1k&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d50d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDUxIn0.8JENWmbtiEmbCpqkpv-8TemqjwDRxhFocdj1bD4PxtMIOXNyuTH4vrVSBSAKgNlGN2XEMX9ifm5o2_HnbcVjE3D3w8puAKHwizh56PTY5gzzMi0ld43eWo3Florao3qTyAJgLCjFKnSG0sbHw28VkQSyXcahFW9g1OskCsSISQdEiTWltxMD2Tag9eoWKsMXKPWQDsRmzOwYBfEvmMwo0wi6tdY2Dh5pP3Py_TJTwCo3-WIEWs2Z6TDB-P9Cwb46ZIBLkSyUBEonELiwBKEZUmb5WjHIDquAWnsJ0TMi9KTdskqz-l-TFSq4P1My6-qAribDIkCo98rGJi_Or74oMWgzojFV0AEvA6Eq6Ap94q4AifO3cBD23YMKCw-x_EOH_TwzJlCSV4uAVR2_42I3vvY8PvpG4rcDW0iD43RmXg6qtYY9yl9AVUcbW6bXoMVf0GwHAtezxkveDoDfdITM9ZiC42LHlhTpng4EOdiVT3OJix6wVB4P_XFcgAuDJWNg4oIehBnQbMWjVaQg8V4gMg.a_DAPbNLyFEdnc6AInnJmtiwnX7m_1DL1aZpVkwYcF8&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d80d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDUzIn0.sqUHXKVJgf46oNWvvuEDifrk7NGp3pIchL4PImayIjA88Y1piMIdc9LKFAwGgCq328HRoGUn-vGPTwczBqm97OJ4AWvAgosUDY7F2zKDviGtITyZez9mUNnOGezPTpswB-a0POFcNtrdypkoML7m1RQHGterGQUT88WxpNp0GPT6FZ4zm0iJQAwqxkQL7eK_IfY7kW48yBhj_QnEhK75XCeaf1_IsPqRcmhJ_SMqGWMBxGIdKvW1H4zSy0a3VtwT6r2freYkQyiHkc3YYypfVZj8lJWwjV9NFHanrDAA0pW2zYRd0vWfyBQxdy0UsqUXOu4J7bNAATCFj7T5-5uyBNFxEN600oUhrboe1wiBtgS4LF-GBGI2iMma-59VJkMgQfa27UUV7tFiRdkcVBtvl61_zDg9S6GOQTRoA1GYaPfMuylVl0MR0B1gRi1BJLYZQE9JXaorTBcBrG4gTzbg1dBZxRupfBr9Y6skZSdzyxnRbQBCse_J1EJ6-rF_MSNflLrVnjBjhiK8kzj_jwZ8cQ.WcjgLF3AJrb0qdbo3v6A8yAJvgoAhAm-4Qm_L98DOS4&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d70d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDU1In0.oBy_6WbxbPuHbWoMexX-TOPwuNNITcVs1XCzDSWC5lo4Gd9FTUay8coZHNy-tkF5HKF8rcqEh5ehKe3U4K8WfRxiZzJbTAFXYFbnqSqiqSUUl-6ALVGpGnTKkW3nXQdMLgThYV3wNlpUkH19mGwlbRDzqIaDdpTQRN-EXOR7FtqnkzZaSi0rz61h9V7FNUmZuOxI9v4Wfuv-VlSPAUeXbPBxlhpwJ92oVrxiun9bkD54z4-Qf3omIymZpiqa4c0JfNKAXLc44eM9rD6-45xryZDW-lPN0U9MhzDg5tLpgUN1GP8PqKaRlHpifmNM9B93hLZFKDG_cSif0Gey8iQdRpV0ole8DAF_apwfSBOWKr7OUfcYQieBGJU7aJmljrEieLTZPtP4IwNoiU2HyEHO1ERTKYBJDpHKDdp9cllFhcOP1Vx-juyIMAX0TfZvGrJJgRryO1-vZM6P1sCuyC6uhHwhPk2rVeqjvdSHt9PeStSWEX-hAjVXpvCs16eCDJCZgM59JA5ILorTcmjP6HHUbQ.gY10nopQIfDtf-kOk41vXA0LaNKOfJUC2uUnbknWxpQ&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d60d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDU3In0.Bb6P480HcaBF5FWhhk-A4TtSiCDHANK515kkhLB3nu90BECZivRIozyxbDy2OJmirHGb2bjvYrA-5y2zSRohdOF76ODCUrJ4s1tqBu6AhLbvmW9YciXrfuOhJ4kDpwu2FSCE3XDrCsJosrME7CqRw_zLyFI3c5ZrzUskmGSmUEGfVdEj5hjsHi9iaJNjGB7caYB8RUmyfKPHht33LfCRm3cDD29QLnrHOmrfn_u-GIBqqzOHZQj8FV21BO_JtV1N1XWW-tR6PIqP3XaWKu7oCyQ34BrOU2jfOZ1X8YIVl_kLDwPziIUhGR6oJyRYTAjrkDGr7-MkRR_SJsYzfLaudHT_uir-S8shfsaSrUb1ourGEHB-tehtSfZ9FoxubKQZ0loJ-D4CPlCtFu-kuWqwcFHdbAr0s3_6f-flC4Y7R9oGcGmBKI3NLgjfiX07cBpKMHbM6LUvd7RDeQ2aF0W7Ph6mx4NTApqSL3k5x9gQ2IKtcHbqtulbasWQkhcEXHd1Kolwx2Mf6hP6YyXm2sTnFQ.OajmtpMiqRPiP19mdoHHZUpKj1MTskdyUAhxZJ9aDwo&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-da0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDU5In0.RaE-pYL793PqpP-kxsLOOaUbsZZsaXU0TIuXjZRI9JcaJLG-DC6hhxO6MvRkid0LUVlZ_48asQe_9hX6r1P0jwsSV1EBURIMQMsxdeizvXErLY67wIDC0bwFWoxXSBYmO0dKAR_voFjx2RiInS4eZkiXDbLkwTtsQJvAH-al4SAW-YVCjDa1a0_9vRTpMNJEEf7vbL9og2J1_KJYoq5KdlVyRYTFekF3mpt07tvANovCdgk5HHv-MzM_e2Ig_Os0HbhyB5QZ9OKVbl9HtQHBrTFrICh50Q3jzkxmPt0rHsD16Z1YIsi8zU37l2aZjIfchmeN0Xypbhw1qSY_Rz-3qEvrLruTJaQ6P7nbWVMpr-EbupinFEo-J991LSRQ0AI48QB2HIlM2dOYBzWzyn0VsteLbdXkCdTb2g3Ozdou6HuGdNswOcxazbwIzdysrCqX9WtfRnkxiR8BXs9GVCMTKm6F_HmpPLGTf6679Q48anA3GYJll8W9AxAQdAkfHzwH1VhCKkrlWkfHD56Cx5i_Rg.VirzEMOmahzxgG-JWUnKVXIRz3XDpdf2S9JuDZ_YLYQ&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d90d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDYyIn0.CTl25uK6j7vRFVBMYAO5ZojL9IrTmeHlHKShhtlf7lOLRhgP71l61D2gIb6vT5hO9UR8lLE2GplneVpP9-3qQ738WRCz-CDIWu1gvK_w8mwV2t1hOjq4ThX8l5QGum2f0DIwRNQdxSbpzO2uqhNro_GOxgEISNzNXZmJFLL35BphW2DdQMIBz7fULIRYfkpi7alx-RkDhwb8fftgHl7UrI6C2cP7VMCS50e4QAp-FOvNilRyw25pBYZR3y4hbIvwnw3TdSfNNE-V09hjMUA13xJVIuKZC14hV7HRn7-pTJgUr4-tXhTbaxWEsv5oz2zHO7jH5h_AbSsrZlX272ojRv2Ub4X1B42np03XmgTWDn9mf53n5xY8amYT5xYsvutRaIHUXEwjUIMEoSRcPuS2ddVaJqHkOO2hA60Dai26EBZM1HCUxQgG3grdYavRXHoDG37V80rgovz6x4oKlW3VIX3rebv6rFzP5mEtNt_PSDe3CXYClsgZ1apEj-tPbIBqKTFw9JbW9ROFOu8-Lb4hag.sOw8nxQkCCNXlqRKxoJXFOJROaAh686EpjWr3hyuArs&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-db0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDY0In0.WwokgRc-w2vt070ZDLx5qdAFwPr7liKpWII0Qai9Q547xsCgLTUBdkdika8Blk7fEkUnMcP353lDqhYMz7Jn3hn90-agzf_los-tlocJHeK8JB_RSx98APtAqCTTBCSuZN6Td5UYCCeKe2LEW0XGnTb55pszOXaHh1Sz-AoHXAQzy8y5FZrBGLfBcyAgBgeb_gsHLSwfKNlwns9jcPIKg-94ywvngO0ZNC00jxI8cbBaHM0ELvu3ArEUIBFsDi9OtozZUTaURP4w7nn9p9_SRHmaBV3OIawrI0KBNiIMXV3rPsldJVUgxBra2h3wo_ymUykwee_ysiHcyWEfw-E5Ue5v_UmDlYWv52wAQXpZ9qI4AXJ_DkPxjZi1xFWw6sbHr7np7lCq0JqKvlBMiB5RwVhx2XLf-kOogmPq5JOC3-072AvRKvNAohO3STZVg4L97zOSxStgzwCjPDhLYG23qXRxp0tWucdKIr9sS0jvv-hv-3yQPdJObI4E5mSzGTPsRS1b9EhFEkmGzHZ1TiqueA.vUOOwjtz8gwAfpFry0b_cL4RtuNXepz6AV0-1THjLmo&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-dc0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NDk4In0.BdoUhmHGYKPNzDpE-8unA1v1MQBEzA55CaTVjuEVwohyLSsdDPjQ7EC7jZfleZIikJHB3UxQkX4ThF1ciJcsKZ5b1vlYHd-25cHZYi4wnEO3ySRwvnYwA53Cv56XdKboETdV6Wa7UpK6JiUvxzDn8t3yTo2yMspi-HAUrInzE-8L5l2vIgaHVnvtYvesMWfuAokqIVVoIltrbWHezxkewWBcRdhSsWmWT1ASWu54PRvI3O8rgGr_iOYDc3AcT_fhU2UFcvSWl_Gfcb96pjmJH8sWeECW_CvutXcOoipqwyg-bK-S-arttl3-YMinmqaxZDNyb6pckr9jXNn7n-DB6f9H-eWDY0DyIuozXZm3vZ_ZQfxwtDUacacFM0NlqFIQiB0IDmsTkJYiZGQrRMjZPqGceFsOiEoQJOXTidEyJz-c0CoR9cZlgnh6FI2n9SRF5FRgOSAsCnmzBOoeGXPtLDDTrBbnEYr_Xl3aP76cFKbyND1KnSjZYc50fsc1ryVZ17aqO2_99XZOA3x0yx7z7A.Ran6g6nHeFUbhtdlYzUBlYYZxDVY75KKJnCWKP5grHk&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-dd0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTAwIn0.p8MpdXG95L59aAdNw0khtHTGF3PiLkzHdKrdafi5PCXPQKSIL4ZYWsReRiPub66fvJ9xdILAtg3Bq1Mb3LgzQZjc8igwc7o3KuBX4nKRpZYi6CEf1K9jIDX8pXixTDFKxVoxcdfksfAlbb2bauWJGLfjfvw2l5SOrzV1vOcHRIqEbDHoCSRQlzHjkMSwP-03Ay3iD3HWqj8eHOAMdnHlhFCSWbp1fmZ1QbZGKkzQPWH4OHvWpQJIBwYkOOsZlYCoUn6g2xBm09gRSwC8iKnyuiNXbScAnan6yrYszHJfLYVRifcK9WcTs0-cstZ0-YOlka9QwlMriel78rF4-vsHkbg_tRj8DVl7FnaI9eVSIvADK83iqShFcwnSVHRw4Knt0899pY3cXqRUs1PYDYhLJgBA_JDDrWgqZklYo4_Q3cQuZrZyPxxkMcNLz392DxEPom2SskFlXOAiwTxCb2HFFN7HxoQ1GLVSEfXBrR0MLHthSe1Dlpx9i-F2VuLbJEfANTXQ5_YZ3APVj4Ps7FEtBvvjLCe2N0pbZruGyQ53QVA.3W-auqeJRWfKTIU0yBfIKO9BtRyQYuacDvDzTvu9xeM&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-de0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTAyIn0.fV30PtmJYBBGevFoFVCpfL4ncGNMZVu9r-_uoM0S01dTy5JKu7cnF5vj4xsPwHlwJCIKnO88jw-VJ7CzVYvPGR3C8bMTejUil1OM2OA7ACx4Ih4j7sLXQrHlSd511zt521-v5Eufl8Qbh_PNJyThrItuARMwcj-hdkC3Lm9SlJJs3d3PX6niCzR7ZEuyGQcMyXyvvmbdbRMVjMqw0wT1oehrht1E5ZcBNa1yTwkpP3GQwXxHaTEhQ364M4gix0PTGgXsApuJp4uWo5uZ9h09gSUbX-8XFzQTECSoysVYmvgNOPHSD3cubHCn-NpxiWLtCZ-IseRtQKcD5qTTbNcDYOcc-poCi5ZDM_O7JLThQAlBkVNqfqWPV1mJ8vEwyzE8w4Ibp6ukwytic1hMaY-756ZSPNWlnXMd6QAE-TQg096UngNkHUWorZeQ8OIbjOdDMlAAcvspJ8fP6E9RrHyyWY9sg1fw7yrUmjUo3H8rkc-R-eYnirrWsBc6xOzQ-a5gLtuDNGABaFEaNTHqoitk6g.B5tDZvL2-lb2GisBWw6LU-cJ8R33frEYl2Os2EkNbFI&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d10d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTA0In0.zwTHkqa-XTJONUWgXcO7c6GCNRqHchMWgwkcBMY7ndcREG7hk3uZZ1egVofSMNKQ-6HEpn4FXo1kTzuBDgiPWCbD8qfcDlxggNLtw49RHGMVb0duQt5-_-uygoQKhQqzWw6v4GLfrt9VZMkbFRAI02ilLW-N_T8-1fPXnBrlSCAXBUah4htoT-iRqxblqIMOh23Qy6cdevFqR1TYPTo97M2yJrIGbLEZVSPIGP7oYao3puv-PSV-_GOYhcz5bZ9W6lgn2pT-9FMeTjAHA76w3fwMRGT1mTznvleotW6-p10ZgrRWd14qCyJoMnTgykgOCUJHvCEceQUwMjBMFSnB4H789uPQq99nmHyHpbiDdi3UsymDQmWkkM9FurL7KYvmeaVmPNZ_VXxc8V1FMtV4S8y_GSXG0l8XPK_51jKXzCuuHWnRbD1rjGqGjpeINqWRK5IPwmHeWExK47XvNmi5dXr69lXvA0Bv8afyWSqdTLbQcJQjkRTas-3zcqbSFJAlbE36SuRczxMFGNYapwkcPw.IMmmt1KeiOPVBN4fahEitn7nvuPP9r-yG5XfwHeRKJU&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d20d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTA2In0.IU10_OAarU3-PJ5ry8rKgW2ANOvCIVj-hPXaXKKMbSWRgrEPmWN7Zo3cSv8no5GjndcL0EpgQ8uG4rFpMP37W7w3ApbRU1RzVkXvmz5ynjSY9dVxnjzUBAJOMo3pamCG9EqFQmp8LsWuQoz2Ccz16467ZUKRR_kH5IzxBb_avuXl6Erhh03cVeVgUG78harlUFupskA3alGeVPKtm8o_8nXqZiMZNH73RHaLXSWH6dSzhxTThtzeASvXKVKHNVwWJaVIqJ6YxKrkVbA67gzxcuL60tJY7zq4m3tY90T_Uu2d4S8QdaLNT8CjPKDLGBNKnBHC-ccxTZ9u0G6yO_p19uCj6OQV_4HrnARaGeYBcbsXQ-faxwOT_2EKjx0cMQSoi_PNFlvZJ7cO3kpgenmCdovotYeH8XAdOTMMAHKIu6b12BaTYWWJ_xtCZ2Q4u5k2JMKUMITrSZUMHQXStLLlxFtuNW3cKGHaWWh5i7JQ9ZgoUj2DYDM2NjdOIby-qKp4Y7yH6xd5tfRleq_YECMvJQ.IopqiStmz0njAZa9JZ2uVkZJMPolJgurLQAFKYKg04o&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d30d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTA4In0.16dtLUefeU6qkMh5X4V0lO0hMCAElY_mG-E8XF72qLX0F6LHOpKuyfUCtwdpiJEgtgjggljS0qMbUq9JuUSuGK3QD47IfM7XnFWddH1n3YYYAMsZxzQMpauUGCEed5h3f2MwuwsZ2Prt45EuWsQzT0_buI-DBU1Kga-6Mg8rFM1XfX6aW-NjXZeyn9ixWU4w-rNLMcFZsWK4O80ldGWXqoRx6mbx0ouSdYTIps0SY-gDzZm8LXtKA18OXt-Ey_7DMQsC0UFRp6WtWM3RvTHY8Igu1z5fUk1q6kWtLGho2NIsdsBuHF7F-CQpIZAnTmaZPbHmplhPU6Aw4YmYD_C_i-7yUkG2WJwpwUMmAhDew5aXo3YwHelHul95KSMayQNELKDYlo6ezYbKNA7xtJyTAsR7xpAJKeHsH38c8ZIu605cHfe7WbnG9lGX7uUAJq_RcTXSnUC2u-3LfhUMA7NYEIxN0codK3vpdQ3jht7cJxQFFfTFjB9AztVpZo5qZbfwScb5Hivqe7gcZHAbf-hD6w.kImMviyvR_3wSH4tzvVqH8NDJepBrdadiC-FWeCCl7I&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d40d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTEwIn0.bOdGVd3PgSVahj3YAg9TaJJC03gvOYIAqpM0zavsLnrtBtGQAB-E2ET33CZGmjmWOUMIFVGs5VPFo0pRvJy8dPP44PZaHUIZTyYHQZd2_0diraNwL17Tx8ZrR9IpZZBbMrVuXCXWJa5FCDqIFTax8X1hGPSt7JUxAbXEvz3dQWgjZW1w61eBlbrA4RQeWseDNJ8-hMCkO6Dh2CGxsX8QN4ouyhTzdRO5gsRpCURreEgWrOJlIKpy6Bu1i1N8SF5-Pp6RPAHJAzPZQAWpV-p7sWnNmjQWZsRgzyCg5uzcfzIc4G7qp25PloiuBaW6zf4ZPpSE9rl6DNKN0TcIITO-J3UJRA1e_cWNhT2LE0mLHXvWXvWA5BNq_f5xcDW3mukZ8kr7A8CGHe2d6_oH1M27wzsPutopRnduvOxrqlMIuqBI9fjhtmIJM-lntf4CskVHRjhfcngK3irInqt3DCd0eYcsh9oK-PRBHYDYRXMlKif1mzKLLXafprQzubueikK5T0g2tt4XuRl5RQp4U5n48A.3qK5wvj6qZ_QxNPAp-L-zjVL_UvPLDN6HiXJh_JwBqc&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-0e040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTExIn0.3ChFYHLY0klHQVMode48kt6nC36f9dhmdQ81x1QRAk__5TOxjeLg3lL9KyfM3V4VJsG6C9foFzUKL04h_eVsAP14EJQQ1rhOC3z-cZeWe0U8PQ7EZVknoa0B4wp6uoKI9L7Qq2R1gM8vknqdIzLT1ewBYdO9_8K2ag83QWDQ6Sk-_sT_2iyeUfX0G0bb7lIzvmA6n4x4vukIlapaunj3IhogY-pdS4a5T4ERvmxhYzITn5fCm7FeVErFh56cey0mKy1-euwNTpUNBU0N2iAXNZY8uMmu96oi0TOXiip0SS_k6SGqiNw-xgZGJVnLgZOcFlmnL4Ytji8OzlzamsD-EOnzu8DKXHBaQsg54xC2Ya4Y0jqFiIkZvP7F9oW6-sFqqe9xoGXX-VXv7Ne9_Q0XEWGzzECczxjFVMC60qYlG14tbwEFQUvl8i8c7Ln28ErdzJEghyCeg7gTMfK4NqdoPzleCAgn80k9EBD3nnpGQxB4cXwcOspi5LR_IrYqyIHo40emzG64qonkb4v0Axir-w.Ck7YCkztamIqoohIC4KusEVIZg22ar39zrlpIQUA3CI&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c1050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTEzIn0.EH5UKGpZMm6ki4JUqawg922ISCfyCfvB6A6NdS_ijifGZhB84X9yHDgYgJtahzHWDrAy9xeiN8ZyK8qe3IgoyGhgZ4XmLwm_aZnvFXrU4_o7RJS3Y4_2IZ4L-7WZcviHIRgtcGdK9mQO2S5TPC16V_f6VTt--bkYMnCFQ3m2geE5Z6zlL09bKUFwcvb4Co9WNvY8Erhu_oFOTZ79AezH1qMAcQJHj7lSotlUgukjXdOMp1ylEmSH3y6lP8Zj4-5fWpvp4RFnR4LnX_0LKEgBvUXBLfjeMVEFiLXYS2B39WqadCh09eO3hznpg56txZ4IMFCbKBP9LGkJ5i_m4AE8NYzDMsdL0ZOhgIchoe_T4v9Cym05bDjzXH34rwFHFHLh0-tJiCe60bAlh35WoNTRNQK4WLEJzgZ-WJNuKkNmGh2avOLYAsbzXwYKBFIsJztYmJoHQwIAWGdPryh1X1YkJNC14V1EFkXI9HUTwpBbEjExI0l_hfkVDYsDhQSigRkDY9jdxjLAb9sHW7tbkG_3EQ.3DRk8Wonf1XW4ORvHM75q3j9MziEIDwUSSFL30i4djU&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-be050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTE1In0.0fXJOekdLa7XOpp6owxmjCm7XvHqqMAn9ZXQEgflAO7gyrplMC9LpYcGwJHjFFpWKtgUtcHZAbew1Ibp5HFPhCAoDC60F0i8nu2WH8XzYDSWFgkA8k1170mlfuMRTKIyIxaJp8fOXo_BRfXjJGEbOUVxThOjcSvV3u1IR5N35HtJUNUtKisf243pI3JsjwCNbvW7Qm3kQ8EbwmtUf45iB1G7iQyj2i3IBH3__mbW8YXGLI0L7zsZioE0I6ARDy2PBDNG6cwpnMkFMiE7jXWKDzVlYWuo_WWEVwFw14OhOi0rdlEaK7B06JYR93QOWT0Kve9LD0qD_DovFCPrI5KjmBMejitUbfXeAoR99G5wRQyR4Wky9RSamgt_-aXxSmGhpcyghXv82JbGYUlPJe9GkMGMsP4uZTYR_k-3g2SfssckngR_NFNIoysZc3VUQKLSP7b6Yir6GpVr3oje5TOyB9WxkyjIhOPPsD_2Gz91UEkJvdgnraenVz5jxX0gdChvCEn5i43AGDT0tHcTF0bW_Q.Uyvi91C8k_62dx0ss9vxBovg-7SQNr1nixSvWswIOCY&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c10a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTE3In0.usSyU2oSHIGzfIPtEMkjwkX6JXDMPYCUPPgw5f7yukD8gKgVnwOXCXLtVO7l49x0ttOlpmRwMPosPLO9qr-KZwwjHy9_3BsjjGJhNeQTz9R3w6o9rCMqQ4DdjuKPAdDlZDZBfV7qzQdoJXI1ShrKsx6gHuPiBVA8Mpa2UNKGdWBUmb-cPl7SdkVGAM6wTX7Nd6v1mSYl4MjAMEvUCJ8rE5pPnQEgrW4_8FSjYqDfDvjelbWS2lr3VN3mUNTvhSBjfLYH8b5hQsNZb2m36XM8-Bl57yi2IT6t3La4JpsWyNf_pq9cjv1gYp-duGFXoWs4G_t28ViJayK1q19OYWQIr1tF-zTlAXs6KKeMI9XETqcYAN27tzipjrOrWUON-qkBYFJFz_xwAAxrHGY7FocVF57QqQxHXF8xdntpdai1n_3kXrFAU4icyBKAo8H8wmQVI51GMXRGmkqmUwV1AFXolWWqKkOSe8G_Ze8voEiLCDkoai1-06eV6fFzfZoUsnWVg9IpFZGmvBaObur83bZaaA.oCYskevsKlHVbohDPOCvkkj47LfyP33SmHs67XmDMXw&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-a5050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTE5In0.LVOo_NozXzzv_D77_oIyy8KnGybaOjIlh3n_v3w4JtuEQU2m3mYT2ozdSTWVdrpCjC3Otaxh_OHEwxMPe335IxABGEXhL18H7IoW60poupO-EeDVrgh9r-N1ArpYeK2v4KVG3Kl7aqwrNivZFzlvWzGR_dg_2xC-xvCrfbylI0hoYTEb-7k9CDlZzQXI5FN56LNZxsNpt7WqM7O77E4VM5s9t4x-bOcWS0RFOwxLFkNCa-ERMmU3lq8bwxFv-Ps6aP6Cy2XGO7fE8t0ShAqbPU7CokNBr_AJb1ninwgC0bQ3iIhYQqPjLeuDxVjCMGtZ3p4CHQOV_pt4HHEmOoTuiD7jXC3P1nHIlql11pjvPZkdinry-zZGo1zOEXI7EECsHLdp0Ed-Y3dW6iHVek-B5sanf-zMOHVecRzqwtztVcoUBTmC1XtHPUV84oc9P71Cjf4x-iLZ7Vynic0-ppHaygovH5Q5eC9Y6UlGhb16v_n-NVi8zQNGVY_5G1sMj5bWpjo290FxmZdmjZVnS6MMQg.i1Ix6USX3Zsgkgs9QYQdOJsc_9kQ7HgxZrYz32-BV64&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c0050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTIwIn0.a23b9KpEt15d8aXKfqlSdBtKzXADzUDWoqhQd1Tm1XJSwiy9NN5UVujmLyZlhNWBrKT27kgf8G_NSpA8_5kSqEjj799xy7qZ_X876eS3Y7jWKSHyrUlMuWZsDHnbbNvGZ-Ro-NA9cvKNbfG4Xwcj8Wwf1fBiRZMHd-cmxhFnORKX3AosQLKLqaQbyW2_Sbqi8iUU_cPOOO5BOopXVcjVSgMo5swQ4JV7-V_v_TL7q7FmbsrShpmasoDaSImmw9eCjeMgtlgLxLDnLeXOLqNLn2FifksXpCwYHeH68P-D8Yh2kuw5N0qFBHO4q30P_rRgug39cv1hpWhsl331st9jPXRr6_46-SYsrBDkammZavNJzM28qpGTRNnhMpOyTgcqm7zm3NlR1bDGCiMCAOb_spPIJcrzYnOxGz8DIwMsogpAQFPEfplXx2fOUMBEzRQ-EdIN5W7OCuDTZZEKpD6i8FcwgiDEPs8zkN2ubDWhzmjaa4mvxSPc0iGY_fm0Gn4U0eqqg-Oz_MdLQBAn8SQ5dQ.jbD_9hfdDulkbf7Kj27bzNEEriuiiSZktkFEZf2IjZE&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bf050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTIyIn0.ow3J2_4_IPDOjkGYaNmp0O8O3vybsPT-z5RzqXqBEw4dR8-mnw9woMf7CTzZBEnM41MP1wg1x4voijkx6yPkZdeTEeiJP_--_ayAsQ-Mt9ZWN1qmXawIm0JFMCK9AU9HGmkcK34bhJjPklSrHxv8CUO4YAmzW46_zQFU7SyIt9SCNo2PJHE4meKi-4asY1jCEAaadpKXlTdqd0YQ0InwUg35l4mrbmYsmspFcBUI_gDUS3WxP4AW51UbyF9zQjchMPUcWCMk1EiWTbJwyRhcFnYr08rzcVTu01aO_jfubAJUnd_vndWsiix2umT1dOn7t0l-IEYJelj4Vz1tirRTPAiI2GUnOMa6V2q6XX4xAMl7NubNtQ9_s65B5gk8-HmZZ5jVFDlkoUe8__eyhuFCfoF-dj5S7RZ0H--tMfZtGzBhs_7duslvX1cpUs5V5PaVEEIEFxMaPoeS3KmvVvJ9p-f1Z1wsNToEhj8dEnfRjbW5fCXx8qJdZhi9wP8c7MX8QRybvcjajIZu7Kld5ACD0w.jt15S_QeU3PYqQJIy1l7gmX3OFUQDUwVChW0qJ72WXc&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-4a070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTI0In0.zrh1k4cwP0YxkXfoZJKhV2dssYTt-V2Rb74F6_6zPO1BkNw2hN2egfrCpNx1Gks9dpj2duIf4kcFfiA1iRTxYsmtazQpHca2Z_3nYM0FhIOhLvuP69JHVYuDU0wxjKQwbLRdzehY6o2SfQZ6vEA18pfJ792Nqd7N0NXlGpqlGeVu-2VQn_TpO1b5rYwAZN-QejjkbJfJvvUGLF_EijoOf6jMHZ8W3vW1fq8K-T9V8tZHOOhkDoNaVR4YQxtq7OHCfxP-HB9ia4re5oxm6hLiWHMSzAb82lXTKdwsgEXnYjECof9RNZHxmcMLn7sy2QsyYotCFClECNFog7jXseKEF4LUlkvyXZHIAe-NQXzygB6C9x0eXGLYX1IlkDJGY8jV-CLIDpCnS8dFIfCGJwAzQRCks6O24vzN3yfz32O1ebA4VnHLECNSyAH727frB2Di-Xu2ry1COs0mmsw-KcedGoyX4AckgyU4AfzO_pSTVQUsZIFcEb9B2ylTv-HzIRbSbAIm9vU_PFJP7VjX57P_FA.slvGz_1bKviaRYTgpJKH_D6tVlsUfSGN2WURwe56Ems&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-49070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTI2In0.Q61S8VPJYxJ5ltwMu0PbKV7VdLQSjmetIHwXHjhdRU7X426DQkcHw7l2gn312H6M74B7TwOqZmTkE3lvXDqsrdQKmW7ZmP6D0pRKCLA_rofbEZmRhqm1vTkPfdPbf4QLfGNV9k1VVaZW9X0PJ9JFuckIh_yN-Tp2JfHKtIU-GFWfQYaRwGpS2TOrHHNgwBl8E8lZ7aTXLIvsrOSua7rhsatepMm9m6XvTWJJl1eUmu8lWiJ3vrZhbbsoK_q8BGd0RS93UHf9Q7CkeZfJHO4XZF-cf_3YxuFj_QpQSwC0iXP_sCJDCjGEX658VANrTQDwnpMdR0iFpejXEUFoBqaGeQIUMohVe0d_mAB1D3RUObzs2RicLBmC1yYkGphPPMQD2NGfu6WMzFVV1-myuXSQWdUj_G9eDv8u2fD4PXXVgZc-dgwoGksmnEtVqPqLE8-3LSIR4wwGtRGds_-Z0cyb2CFYJ8KYRjK-RZjVRgtarPBq397HCPaHZy_nJN1jeaouXJCgRziFAu9kns6d1ncqPA.aEwGBQEdbK5ELYsn_5Rgnf6SoOMdzNxnUwBSknTb3C0&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-4b070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTI4In0.moigZHJzHveONBzxA1URl-iyKD5OJXryPvrNFwc002WPqBtDU33BxnQYY-jWm261o0WYN3Kz0_eFsGcoHMYAmlhDwRKPgqGhPv2UkF3EDVbrOQKv6sDnnX584sRTjP0Cu020fFAFnyStnUr1r2_cj_TUpuYE1KZ77pWv3x5xv97yxPqy-K5-JRM0pe7xQUL2b7COGOwlqOQUOE4I5bOwc1WQ8e52fStZfX9MSBFX7MZjioi-ZZ3Tpvoz76UVn4tAxEfx4mRMiqCz62GY3l7VfcR3RDGdwHNHFVByffVN4CtTyvRJSAUDzbvQnQD6lTYj0ayjgQg5cfHMDIT3LcQgKZSwDdDZmCNSTwOZk_WKepqjH6XmEM6hLvKCrmLssWjTDO-_drwd7nVk2DG8Lfe4rayBp2DqHxRV1BGGrSAAQQxe4zMv4xUXE-IcWK3fYozct68KYdIcbmZJYIY6CbCzkDEJm0FvTlxahPnI9PyollNRF40lW3g3SZxJC0-aMX1D0D8_SwOXXgDoPpNo_bn1RQ.J7ECLHECkeg8K8AX6wPfaQn0BxByijaT1d-FxL0x95o&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-4c070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTMwIn0.yXrODG8iP_HXN5sFeNBjxYfNzrgAIFHIegidiA1atXPEo-ejpRKg6dmMUsmy4sL-bCHuodlmg2ZYD4N8FYar-R_jenVYmfjjAc9OF4t1n_nqndCFpJjbkYT3VZXw39rYNnWaxY08LhFv6P6OKEsCFOiXqXdeukuUiX2i4fE8tFESBCtKb-4D3mGtW5PpxNI0IEXYf7GKAbWF7YOj_Ge8s5G_NLNQcLPgDHKZ8XP8XC9ojKqaTcsOmOFjnmM_tHAqOLsBkI5h5f8tWTjH2YJSM2ttrWNi9A07Ey28m4tmKoGh9RgWGkFnvqD9H4Ffc4xx9u9YWdYibeafXfjbiPQUc7WUBFD7VtZ_7rpx0ItsFNdxm3ljJyfjuOzfe0tEd0j3MfvgfExhSpewwk40YAotkdYl-KNDDO9GOKEjDyKImBehBPv9CeqDEC6-iU3Ss5sfX-oNPWI58Yyqs_gPYFKFqYZM4gW3zACDa77c4N6QA7zG95ntgEGEHzxbQ9vj_r9vA0a38TYPAROYumouwqQ2Rw.cq3cko2UV6SsKIToTj1ZvfS2aKPiGuY5nADS7n_NUqU&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-db050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTMyIn0.hYc26UdZRJNWMG0adTIGrJnP6fCQHV3xTaaSHUxk1p6wQtDhRZ-bAFdyYlgkEvAVsgsM4_gM1uCivUkk62RI3yrBOemtjFMcwgt7N6qo4U9W55yDdSI8sRMDI7LTgXV5gVRd2l7-xzA2pUv3Yfkc4gD4TkvpeSCJO0QfoD1aUYGqKpwoJCLNQMFH8D1C68pzm2mUpnrrpThAqKkW2HjhGKD7x9rwtc6bSviN2-9c5O0DVoTUQHWZFjqYD9k1mUz3Z5y578R5FVS4-s70aAHVfWar5mOYp7aIHpMlcRUMjrJPtHCL8TjyAy97FgAXg_YeJWyvEPFmiz7-D6W2GvnAu8f62m9eFm4PUCv8GqwJhqoJsHfG_SXRbjSTWXm1PGvkNKHGupiHtc-yG0LVrovTA9PlzbNrZXA8gQWZr4yJAVdQ2N5rOg_5NSZqYPA7J2fWyoSLzD9sGAq5umZO6I7CyWPOXD9rhUTbtdpRbUh_rHbKgmnp79RCY4R-ToPaxpsnZU8Q3FbCPe8y2nFPNffT0Q.tagq5eyWHn45hXhxkAj7sYwQf1lr8KVFk_Ohj5qpXH0&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-dc050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTM0In0.r_sQ2yezj1ZeWyoKfD9mNJ26WTmlT5BR5VNA_kWU0oJZ3CKcKCk9aMnlbspKxcyBc2t0NdZkrfapubAe-NJdY7u3j_wh5F31nlBFqMpmplbMpu0PJQqAyP5L6xpaEMsXy6vA0AKHK1-So66y3AGH0-wPIWV1BruqeSUwRn0PWlqM8At3qunfQ3bzYZJHJ07xMFUErYsppmwryc5xNOCprWFhnd08a5i_D1eiycCRtfSpzYhG3uJWpMQfFqi9-KnHZKkKLhoqJ8xrwXcNAgKtCylOq1CR-2Gbju7sC_vvTErflLwjVIhY-n5qwLAgAdSMX_FwbkaKtOrneJAZGZSzOfAZqr61v9lrYHVpBWF_U5xzDs_EbtYwlamyOayRqDwawqpFa_16Qo2SbjyRDvCXn2K5t2Qvz-tPipb4lxRU1Aipsdgh93HGK-EjV1n8f2DG-ly-wNndg9nGCIIQkBBX-K9b9EXSeoHksNMLi3OPBPM_0ivEDDKY3cbKRgUSWV0wFi8oNrdo70dS39RY5bG-Eg.QCIztGP8byOrOek5obN1INMFas8ssCANiQsdt1_f4P8&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-de050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTM2In0.E5VmQt66dRtG3doz_jS3LJhX0m2tYVQvBrZYT3eeRenrevmz8fk7wo79shnfW7lsuQW1Ug62n1GIeRtAUA60MgInXlBM3gzWO2RH9hIRUl5HzgTzJykYyBxb3T5IaMxwUdATPn-RlvTc1NaOPnBiHGAorI6L9xWFBVNO3fLO4hLk0475yloD5i-5LIcFJq0LvsM1oKAm98jsDqSVTaYDyF7fb85ZeJtXteWqlhui3R0VI5rUNHqzWfnmiMT3OWqK1fMc2X4ITfftws0IUBL6yh9VycTIk6tFvd68oUlF9um81diGAMJrKw10f-mR8V2Zgut9-3pu9LsTlM4Xi0pNxDtrJOW7tx7ysU_-7eq_adR3dbT0s86hJmHDvx-9oOkwjL9pT7Tte50a1zJ9QFVW20g5eKPvGKKeB0KxWNq6DhH49GVErnkC37E6XBt85vjTuOL5Z_R9GhpkmEleKjOgm-kJ1DK6JcogL-Ap1Cb_shjg5aiNwsiC12jSj7-NfhJiJ_9Ce71CyjW_2uAQEYzF1Q.fYP_bWAnv6lThDsFVtRyA920zOmIE6N1H_oszmu5Yo8&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-dd050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTM4In0.rTl_GhtaHPbYTtsNmwMimVmlFLl1Yp6kn2Kl8PlW6T_sy8iyx3aDQJ_B5s3G05FmiuetbcyucNWAUFKAyVflLLKyDdbcR_PDKetzZT7LbAtI8lvUVfCH3H3OJMBmbYawTu95te5PcmGSy1N4c8asWoNeDEVq-Etc1vmaCaHYKKR_i7Bc_gN4sSqAxc2o8h82gMNXOPFn5YhYxBE8-h1wsRnlVhezcGBN7b4KSgysFVbEMAoWGdUkW0mG5cuWx3EZklOmtEZoYnXdRh9l_eAALm0TRXufhLA1w2ltZjekMf7NEqiu00HwYnLuxFyvg5LL08388iEfX4tR8OHbiJ_TGP3RIrliqQw3Jhd4YsvM-bxnfpVBjEfAlwghCsd4T4IEaWNf_W4pvYdmRzc7yZIowklbFS8Q8d4CChN-QMUCmZmxrCW7tLr1KWgMdmPGAYAMeVaxil9RaDgs46FYLG-aMItElSCOOavrvfyUG1JT9_N5ZGZOz6u4Oscha70hhYGCtxNWrMdPN4AWiIniMbTDCg.H2WAlcLYrjv0nyKVFC63wV_X_7vTUvVL9HvsAKnI5kg&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-ca0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTM5In0.8xX-fD6wOUDFABw2E74uInl7FL5foYbM_7O9pD674D0jgFhD34R-0jM4OmfRwbEeapQWK_z3TMHj84KPJwwQRZYhQlnFFBZVf6IvHwEqgMSoFBA2V1Hv0-NSniTN-jW6eSlFHxRarirPFHu-42br8gJX5fWYbXAscOP4biMQ0DP9kUEHjMTXTR0o-RSeiXypX_W-SoDBA8yV2KJ7tBAp8Z3fwumZgC06HrL5TVG31L8vSs1x3qFZsf6UqxnODTw5Gc0huQiBUCW_V8OAUAed5efxGfLA2ENHAiCX4j3IHHKPBYkgdj-0Qn97HAjutA7jw5EO8Wm0LqQXuiZZb9-LwYdLdfa4EvgDF_YbWnNu_DWqk7RAkVPA5M-K2WDBjWyqs0Wr9e_zlZADOEpG7_N8HLV_W6pv2FZEiRBcw-DAq_D6ckJcXClqd1Uc0a2Et2alb76bXbXWoDYf14rgqcEDMbU5MejofqNlT_qbTXBsP1ROH94dM8KBl480JIjqWbRZLY2kVigq1EAdz2gVZOrRIA.MNP-Ne4WEbjn_0Go4M0AUV5RR5FskpArCLwvBhQd47g&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-4a060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTQxIn0.zQmDIfkDLjOHcWhUAia8qjcN-14YTd7cbV5UJ4zE9DJ4_J5uNG1UN3dJg9lkxUq3YakRfZbeslxN410n36ho7a_fB4zF-YsPnGZHZcabr2kx6F5_MBl0iiM_Bi9g69ETF8BYHNh8EtdD3jrjmMr93JHGYN0uDzgwJT-HnnMlGa_VNqq0784JBkJKtRyqI0g7EbGz8exOhZr-pH9PiuG_L6OCGHbGb4a6uikhgeDIolycz_sdoOktvdrOspI3-RkJVsY51fZUMRI18TUJQZ6Wxv7bK3mt0vLHXZwWz8vhqW_8tHEzUosxymiEseDSMepmlC3x59ZggktfXKwrIAl6FwPtvKwGPQQmhrcqNNaWBTNOsCr9pCXREruLjwIB3e8qfZEbvCwI_fdpdqlYEBuDoYAD1xZ731Xh_MplvTEailIO8pjmasbm0POXYEzvTc6Exr47jvM2mhn1Ho3SpOtNCgU9_xpdq_65itd-RF99BGrDmRGTqnI1-p8xmPS8ZqhrDIRWOJoRArLBCdygXa17XxM-HQcp4HKiyFWXqC4eqXo.uUceIOiceAxM8L_5WtQjQ8rx05JGEVXIQhBW6gcxZ5w&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-4b060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTQzIn0.NyhLgmyZKxnrnbXms05M4us4g5bIRA1MDmIZuckDVI0Jv-iHixz-q3c1F-REv7eVhhX9ctuLsgmVrHYKY52O7tgWR181WVEL78P2QlbI2yfEcGtHr4se94KuDzRkzOK33Dt40BOtG7nGx-RgY2XeFZSP6IxnvxdeeHeknY7wL2u9-T49EjM9iHOMFqnzN_tWtRF7ogMx8yykvbzN-ZN_eh_tvLS3aPu_02143zrnu4pm3syQkKlk2BXmjW1RutnElMCOsRXLBnHxRlaw5SMSQUuBcgBroEEGWAnCI_iBPEYX-I7QzyS0eJm-63xWku-EhObtaChIgNsQHe70zZsjLGFvf4Y6pDMlMbZhuCydqwit3uQ1ZfyRi_oYROgtuF4cWpOvVurYUW0BEoDasGtgFsYIf_LQ84T_5cieEKRgFlYj6d_pyY1Dg4bTjo1B7VSSIt_Yw59Diyxl746i8jnJTdfRlcpId_IMQaKh-VgubMx2CrvgN0tpl8hLvEWIVCvwoaOED87wYbpkPpWDCb1ZRQ.EmG3zrt6ujfgL6zXj_Q-t3oQlbWVBwUvU5ByVEmKL2o&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-41070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTQ1In0.B6Q9l3meqiWg3zt_CADy7IsI7TKDtVwxbsSBFLibF3i3cmzjg-hq9uSfTkOtf9WkUI-a-39yN_2Og6tnypsHgFhvykd0EildoazVTfXQno_bOWXiqiS_vAfiCXXOesaR1BNfr5LDOV-urRGjDFD1ynjBYGjmq-sNblX87oCgZZgl0LUlEoJcrT8ZkBKBJyI-RbSOGAm62ANq-2i1OieLlxSm4qm4UYyUGhIz_qx-ULwiFBCDFC9RPfmsfjDaY50Ei9xX5t1p-g4ZyqUdo8O-6ipLYStfSYgekVZ4ClWXvQYb0ULzUF6MeXkelLDobCVQD0jYH5tJ28j-WWPTgUeAOkqAL7SKU3p8iAAED8vP_X9Wx5qMM6ABty9vIr4zJycE31hRZlCbg3_TfblYkLol4orljs3OxtN6cX7jPBE4iun_02hOHTNvdL1CErOPvvkSM0je-4u_jWAmclFXOEsRzNHvCub1wK61atA3pLGmcWb8QXo-pQP4VqjOc7Dob7LnwGWkdlY3u6kK46pNO6o09w.6GtCDN4Q63ooPGi1HIGkjc1eCCd4SXj8YGU0_pL26kg&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-42070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTQ3In0.lKfl0OZWANoCGrB1bExT3UMEU06OCJLnsiBMjzRwn1QxzGqMioyriom1teTEl7iQM0wcWto1B7NYT1u5NJqVfOZ3-RWmwmVT_dWHWVLGSuDR1jFCeKxKf0LFO7Bn5XEu3ZA0OHe61ssL4WACBAkinCJBgDgCbPWyEUfCMMyQ91YiYnH-0Sm6vcIH8Vu9ny0WkQF-LzG7WrtLRgarFEDway_R3FWlKhZqgErlrMGAxVCvhR00jh08XtKBA9CoDaI0Xz1PgZlfGZd47Rtufv1EqF1sueUJmenPEVtE2ZOMvBkZDo67vez7DstwtPyd0I8NukAaB0Mo9tS2dVbCYkp3J8vOoLedtWp3jiFWVeV09otXoe4GuRv8fDh2sXbYyQmka4YchArk0cJsnjkgLBJUI1PUdtcHMAR8VWh51MRit-ZnQntXarvUpRNlZz-o937ZbNG2THBkFx5YV2EuHmInzJHNiIsKeL79SoqrQxre1FreqV6naGspz059bwYL-pbTAGEmilSgFOfbr0h9MgtUiw.ifkFPxGFXkJ3lRoF43ZmQJNiyK2IeOQ4wkCS4iNnx1o&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-45070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTQ5In0.rakKLKY_LC44hum1D3gncJp2y51gxd4oPvccP6CW0Fj5HqzZ69oMQw5FEtAvmUs7eWskBs9D6S-a_TketSfuHqCJBK0V23uvnQR-F9GGCuEEIvDckIL-GRL6SfrHw-JdhqrdICxUxBZRqfKVkAj_s2j1MPUbt6wAzI2fwUt4Rd9KztqgHJ_0GZkav58WxNsJnS-1U0Bipz0y7MeTgHVZNHA-lmgwp7fsQDIICife2b0Jivah_ueStj83kld5F3oUYQGGqbsY4m7WfUMG3K34r_zCkH--awX4L48J6KXDOw8YLfstY4zb0u416mM9llCcu3ft6r0r7c8MqTqXe2IoFL_H5uE3cJqMPoocTbe1v8KTvKegP0NHsTZhDgxxnpyrwYexeYI96kSr5U3TguTj38qV7RXsUKMpxb03oOhu7fcOjf7deDfKRuaS0n7zQKzMZ37ZeeSzc2Jowpdtj-a9Ga7e2aGhIjBEJqXq2S8sIsJAJh0vJygZSwGwYkuQ139CuOdAV3Jh8bqTHNK7dtoT6g.5_tWcHrjGfFuNh5rW7C6_U78nsPLa6H4MLv7ADTj-_s&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-44070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTUxIn0.QbbV_MsHI2DEw3E_Twc7ko81jwk5cF0lJm5yJ_M-B035aLK4n0Xc4Pbqmy620yFkDGVpCadyEv6vjS_wBiAZdHI7DLtMB-qIO-AwoNsk9yleB562hzVELZv8X3Mub6sHrLXxxRfWEhyNdO3AkmLNmsz1ahJmA3osqTRXfPqCnNJv9V77vAgu0AINMmZ9xe_I0kR_ETXdtioTLhZxhos2YU1517FG0_mHr9Gi7HmlrCwrgng0pQoAByD3kYAW7yJ-OBkOScP_weOumS4ny6VYmYMd8TZKPgkgBrEZI4aORTnGsaGe5HJb9a54RTJlfVMD-I47hhs-qi2qtP9TLHpnyl29YMD6akLvpURM0NmnZhXH8LsuO-fjzDToKmF7qB8XQaTJs5rJ10ux9KT3HvGS7uVhLrXwWZSEUBwsXKxT_Wa00Ye22zlbkEJGdwnbXKTODg4G05jAcyQgzv5cfU1p38W6TjIezv0tqoUh-eiKQ8jt4W53ngD_ZNg8yO1Q0j4rvShm8dzhbLg0g9i-V27biA.QbjXUQKrOcJihQP7mWyJ8F4Ep3EPngen8CExsIW6FYc&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-690d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTUzIn0.DQYD5lFN8tG9WZxSefNM9AeTGuIiniTcHQUop4V3OrrNRIxXeVa7xk-TzugNiL8t2_b9c_86P0Dux5IN9KBZgTNGwPAvy82WzpT9wawMujGkH_SzvSat2O2XQx05CbW23Ni9UfnIhgZkvKmNRbKHPQjPV4itsv5KFskJjFiWhsWwYJlhvNdKqeCIIq-LEFPnJ8rcoOrT6ycDHX_zGEGLdgfFdQnl0d6-cg3T867SLQffFLmHF_N-UFqFO6hzXYGt37eVUxzm6MIG3a667LlpRB48Uu6b5_jR9qn--4CZE0LArBR5JmhVk_y8n92DBdIQsgrMr82oSzk1uassRjLC3MwW-eTrJLRbxjVAVdeD7ywvf7mESi-3kues9o2_AQUQE7YApMzfDSYIpAHmmQUoYaUSsMZgrJsLTU8BhSVH1ojtqsnJ_xrHV7MfDTkz46hfdc8WehWeIa7O06gq1WPIL-qiImO7xupE1MpmBlag8hcrhESaTTMakCknV5oIz9rhNUMvrSJF5oABHrSdHaGFEQ.8bK1mq8WOMvB9Xg9K65jmx4KhanFHIEMhhjTjHrdp4Q&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-46070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTU3In0.jKqmyAk4iXBLbjLToVRASq4HviKHBPlfh6BRLw8I5q_Sgtggwg5Wx54Xv3wMwirD4eAu2ddfxSnYbyQdZzN6-vlaFgRTCJd-wkHYrXZU-MCfoDlMNlEr3CfWa_tMopR1kF1VPKDvFRqPYnfbikk4n3UY0-wtHbuoPpZscWtS4z9Di3SIVUZi0Bw9BkDswRfiF7NyBKp55DAXtqLpq4BnOXArbt9XeleyysnoZpIYppRSIR7H_hQtY0w0VAcOqEZII0Hbyr9raB_cN8VqDVIQ7j0YHOXDMcacnwIRwCRtBHr3cxudzGn8dOEi33oSykb-iPffWjqxDPeBg92GsBg8B4aMB4lZhOx48FeGPVi1YinZtVTa2snyT9EPMptdXFMPYAEvIUV6t1WYGzyTWimmdoUwSM9O_Jls4cXAfksXH67mV-wOOG71Mcmk0ojvPmFGAVRzrJPldbp-MFtXGPPuh2rExfIjKDIMHC77bnO4qR1mVf7HpU9fddMI5lGDlqs3qoQSS4qL8yVnjgIX35nz2A.qUtt8fBT3ulVm8s6q2sKDatNlOlUvb4_KsJhhoB2RYs&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-47070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTU5In0.AzWXREeCM73iPSia91HC6eiTRlIahxc0d0q6s4j-_nC6XCJ8IpBobqjDCi7nYfQq5iMGt0rJzS-CApMYuvqUj8_2Z-qMUDrA744g_cjf_dCIvnLTPXe_8zNLDNodKBGrXt_3SptuXrWgM_qRGy0WQwQoaVaVwRHr8Klo-EXhu9mesd4LLlvPvLHjmYMVAzaHXskbO81V7-QGpS2DZLXPDTasU0Dk_RKJr1Nj2j-d0D-Wf20mCATlmRPFPh2IG1KfgSIJej8AYDfcu3slT-VH0OYhAy7SaVocdvzKlqe2L6_vJpEjOu-rivYekOasMwa9DXSi9h2HN_o79v3fDD8AG0vQq_RSkX3vEenEBNC0eh0bqks2BqCNTBd00gxGMNdpvrnXKqDeH3VMpJJGeoM3noWLpkdBKvNZqrz3tTN2i3mjxXBeOt-RxBW7ElAwvfh3BcL0eVEoX3SHpaYmQPJZhYVT1aHvoqXH8-ULnsmIjg6YVlzMN_s12KDstSF1Jj-CVYiSKcruchPf7kzTaCtvSA.jgnH6SxJfNTDswAwLcSWce_dFxlNtdp4-NW3Qgp53oE&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-680d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTgwIn0.AFDh3fztyH_ATW-RpdHCfZmuuNQbws5usQd3pALgrJSOlwFHF9fNoI7zWi6xpU2ahxNC257xv2Oz1NXeafpDbp4XfG7CyM5IRFS5IJc4BN6LI5MDVAltFjgsHbg89o1FLHkF0iPk8PBM2fg0PmkNHUwKTS8CeJD7qQc_20vjEg7CuIRie-FwfmV_yv5kGiSdZA1DlcW4jYIcJ9fyG7RC2XVDSFu5Pa6DDM0tz8BlL9-F6Jv0NBunH1OIH2gGs7Vf3qw4E1XSAxty7jIjhJG7_wQOLlJO8jqmfd9g4LGsI5GUgURmGO76G5lbAUSHUvkezbq-LID26ZGaUWabdDeb1o6VHLJswBozGAu4oNe7Skpw4LK7WLZ6bvXJ98_8Jmq8eF_SR804Asc_qNkRL7PzhN2SpYbKMGaS9vaO1g0brn3H00EcxgwAU5fchlU38znksmcWrOe7JJIL59DSwo7jBsnsku8fZZzlXTqVKr2u6YAhL6liX4w22RB4-682MjxIR85wW-yybCRwZCt2V2LGFw.H17hdX1YqjEwgn8d9rhoYgw96N_mppcPpa3V2GT4pF0&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-6c0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTgyIn0._p5zxabOUzl3C81QHSnygG99aPvsTPIn2jpkIMMEp3Ptg9YkaAvCTA0AgmUfCdnMg0vfcWCsftrGpNcy-iNsqfXkjJbAxNONPpKsdFXeaM0Tgr27kHZlEjyGmOrm_JJkp7EBNYj40Z7ybg_G21AnKQhB-PfoKxJvo5Jy3KTEzrCiAaedgPmu2fnjTp0IubbIWQYIh41A_NKjH5SiETnH28C2vZ2lCfu5eYlYOs9JPF1ZsZB7q0vGq_coPN_N6FC_r_phQvyv7KsWucILOO0LXftHtdpiM_AuRycIg8Ikcl5XwBwe-s7DoSx46Jq6s0M1xKiNu4swdC_nXz05tIyFobnK-lPsARj7N0jhmBTYOJh3jm8Acf5_cCNcaWjuZfaezOk90b-kT633Wk76QWjRFFgQkzN6q0L3fLVZ98mrwBpkM-DibU1JKOFUxIFqwKpbMj9A6bAwbvV65mSCxQNulgZLSpKSbVQT5q2RovruM04veJvUgt6-8aFtgir1-7IUJYPe_24MXcx4N3nXD34iEA.qnV-UGDNjmV9cmxZXfxTtBDQ7Lw3_eymZFzLAEmQdI4&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-640d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTg0In0.YULPkGJm6_wVQGhhElX5zpAvJGD6LSEK75JPNEskTkgEa5nVKJKapu8ttkalvchlggYUL6Qjo1JtRW6WcMwj_GBn8knXLRo0LNpxCMB5GqvMohatdCi3OsOyc5rVb5CGCo8-L1ZT4FweqX-qDKocJwrU_C_hww4tjdyv-IfLs_wNyM9Nu8oDzBJ4VXaecEpspyTFx2DGLUnlaRBAqEsr-kh67B1D3KdKM1mFG2yIuhkaR0KEdRzQdPJ7_v6cbU17nRIn5Cz4wm8aAucBSGITEgAN-z_hWy1qt-F3KGD1xCdJPAKfuAJy_L9W29PGxIuxYwqGsgcjjFQR5txBLULqx5XwOdXgUeWvncUrb_TlC6kWroENxL8zbY-ZCXgpdA5xm8eNRDOfd1bpSvU6AX3OpYBlqs_Ti6OmWOfKJGzPkubH4wF6VnXILjl814603GGKZU-0AUxBp5BTRN0UkkW6jr7VbuaDxNzJhm1SURNI3MT4Cmi_wYoOh9X9Sgybm5_ICMByXniZT1BEx5xagCJUig.2djatUjkBHXF4zO1waenFYVoxusN-tQb45pD1YBh4YE&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-620d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTg1In0.SJIHmJlTq4ZuXRspbbS3s6Ay7ga-J6jV1xyKjxTyXqO65iV4hqUa2b4xpFeYb5rH80VFlsQa9N7Hb9HFSvFzGfKVUyggFnf6mmgBhDnR3yv3kpb5ZDPPOHQY12yUDPsQdJlKaH15DgrdKAaTXDnysJ0urKkrX-c2N_QYQQF8VGLj_2uZmUD3xQnZtlkcrha8JpCWffqWd3ct8sKnFZ_XTbRKXXaRlmiK_yW4xo_50D_BX6f9YQ14ebB12arIpGhEN2YpQXurbHhmJeQyWaB0TUVDs_l45neZ_JSwXcnwS9nvqxN9IZaRNE5NYyWF5ZuQ7h9O30hnhyfk4UTc6P-xP0gys3NwMr5qV2T-VD_s_ZUKoW0sMJIhYW0UgIzEkpC0NFSUJix_-HXVXq__-iRIaV2jpLot9gEQ6g3AwPZ5MKZ5AtJrf8cIVOn1hkSiy5oXC33SJ0sB8FUmRg7EZo7ZCwoF07Z5lH1d-Vw5Bszho6_8SICeXSvp-QUzVt3x-GsCP0NXjrYbccakbOJjcsUD0A.uDUolVJLnenyT7QRtKKVKHlMB4XqPI9vWCXqEFcEvcI&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-670d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTg3In0._ABDHmAOLZ5fo-b8N4DGZ_oc2MuFUTuiZ1B7ZhDBA9MF__uk3UCxgB5StyvIyTETOC2TEt1aWmvuA92a0i0q4Bf-aey5dFneN6ZJJUH4ZeK3xiR_VKDWhMZN6kTyzuxyuB4o0pxtQtPCxkZRXFgMDCptCMNvfrn0l3-ALt_-oXEU-HjWIvifEBSuF_RgYsZ631kkpGQOdhXs48hw4af55bC_V0cqsxl50UL1LIJNJMdbX_agK5nVDNlhzDkr8bUuVA6oMlLrQ58yV5HgSnM492t5EYwfpsGP2RuA3SKatLF3wH7GY0gDjGU0gHZs4mOcquzSVLf-LPqVE2Qa6FvfS7AI2HygN9JrCgzTRupZgOW5E1rFMX68NimtyCKwYzm8_PoEe-XU8D0InBSCY0OVmBqoKQlBO5cZ6hRKgVRsVwVvLVVSiZ0gEDayzBiPQCJdn0QywfcRMZmqlpA7xkGwll5Qaky12RunryuHLFoM9oXrl78wAL2fkaBy166QeFbB93MLDl70h1zb1WyuTFAbEw.xE_3f5L2H6ukRUffVrYTnKmL-_YqBtFNGJhlPNdqpvQ&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-660d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTg5In0.2VHbs8tYmd_s5Niuj_fC7xOkhAdT79PmqnlNMJYVX0R4TQabkMcHHJSXGGhbRPWAr5TjNbjN2U0IEkQBa_7c86L_5OiPmu5QU2Aj2_R8W4iA8E1W1ct87y3R_Fe5fTwzIX9n4lD_8yeh9PXAb-8TUKj0glJUbjWDQzTD75MWEQGWFpXAihYGslKqRcj71Oce567C9StMFKi3kxpp_LCCS76_G7DLPr-Tdt3XdHUKuTsCKqmw4G9MVovXC5g1ysIAJoy61H1hlaFxIbyRfks1HFG4SRUNGdxWKCCoAwR0L0clXbl1COrdtwEUNlR0UEhMVIM89DzP_ehc4f-yMq8Nlc7XoSSVbivwp5OMFpXzl_WvBDe3IVZZiQ2CuUMby4Llj5KyhkUyOH6AtvEu_vu8Lc55fEfECk8D-XskQqoA4jDMKCnG6KezV-4KUQ_jtsaqIHY5Ygq-xaOhek9jck07aK_8GJQ5FKc93hOLvSYJKTDdVEaIq_5bNolYR5j1HvfL1Cash6pleo342xA1324bog.nRMULDVbsddX3gCwcF4mhIb8zRNWdoeNn4l7gbTQ7kQ&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-630d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTkxIn0.F9ihE8WQ2-MNIuafkilKxC2HAdVTHiplzLRpNXk2GtEwBo9iyMhvSL9luYasONH3KZ3J4KvibFtu3NyDVpyMJ0y-WuA-j1_HsYXQLy4m4T0iSDKfxTTtbZOTLm0G6DXgUNxHa_OohsqxsEhNUW4CeC6VinCE-VFrf7IYjis6qDxTcJ82eMowaNND8FwR9IBA0MpnEPDj9GuF_wXyf-KBREBA9Nw6z33GbFFoo50udlDjG1j7mYxyyPHcNLKN1X-SJ8zqExnxiD04LzM4F6WTgqiS_zrDt5dAkKZZ3DR9mEe_N1FzEulgoXLau_dbff5c4GCIrmyawFAvY2UGZ6ltLHOPQdf_cunRkwESfQZNQw8Rxr_Hh4tYt20sJjiVC7OsnyAjgaiXd44FTIEnpDT-UuP-gfSq4jJ2lLt4EfJxGcIO54G_KC71vN84YDy7OxbgyDmTlTROW0vml4wHJ4MJ7YWQQ3KdG5fBem5mk4ehrFCSJYcJtY9aUedVL-PuQlMpqRoIM8No-1jfFj4rtSqA0A.XrurfTYMzZaeQnJWcDY0hYGj2I9g_t6q7PYvl4HlSuo&amp;ApiVersion=2.0</t>
-  </si>
-  <si>
-    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-650d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjQ2NTk0In0.nS4xk-N0M9-YN12Qjt79BaKusTyybvWSiBo0CMoTYBq7YthcBlU3KcXVVYp9bP8veZUXRUm50T0EjpTxDZyuv3via5_yn7DvuvGGOOby_Rh_95_IJd3gzz4OqOlvnFES04OFRfMdcx3XU_FQzyyzO4KApYiH7bSJ-NCJDQ-gtDKhFnEDUKl61PToxUp9sY0YslcD8QoPJA2KyJX3FaVr43qP-ifdCQ8VWVJkhKfy4SZD33OGx1hChrH7X6tC0b5KEKBUOSipzAggQp0Jgix5ktJGxpTc8hAB4-OB4YbMRvR-P60fK8GxeKS1kcdnVHdcg41B9YtLWuL5-XWK4YgarkhuU_-opcwp5beYju_VLHuJhus8OtRTf0ucEgP90w7q74dn6LXuzjmeojREPNqgvpQMUpIU8w1ZuLduxjGPUYTq515COHx2NuKiQFVOHRL0gM1QP3WKwMZSBVEpWv6Mi6rzIIclBT5eFXq4TCPsIuAHRd_YNp1MiYzD_lFqKeGFb-M5oTblFrzuLXR9L6zS7w.EY24n3d9ML_VhSC2jvnYBh0ESaXp5RM4j7ANEngGt90&amp;ApiVersion=2.0</t>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bb050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjMzIn0.udspUlWvO-rygnwLSPSeS0yElwlXbDdGA13drJYIeYY5nPA0Tmyr_XD6kors9ioqiEWcr9_a3IHW7JvjMM_0Rs8px6mri1Bu9q26YGjH-fwXZGqbiIu5KmxuUGI6eeJwIE8sC0pcoNPVCoO4fUMmzMsbclbEr8-VeU8jsmoxs6TKtAIIj46U_4y_F-KoANIJCuHz64ws70hODHzd3q62gIKu9HUHu7uw9w7ufNShgAFRiQQpFmobxoof1tOLhojqvRVWOtBLL1icq9QzxknngUnjLyf555phRoa1XPjJoajDMPS9BMjPD4f5mc8DT9aSBmejUj3yJMf8UVmzS6set4RqTWtJsGtAsDX691J9R0-DzoA0WSqE3a4UwePKQtldyOlW2W5zItf1cdwwiqIggXJhYtOkkjfR-9Wj6PAqoZy8rZFdX_9dTet_s4scPUlbGcmWc51Yn67e0lzCmIUZOZd4U1_1hdvCkM3lXE0T9lZCQRsxN1cAh6lKkh-wtyvCBnM4khr2NTZ4ronuYXtjbQ._W3A6HBFCVtTnPX4j7h0Ii9ntrlp-Ocv_wWQ4insC1s&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-b9050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjM1In0.FLlgLEB3TlDY0nKsi1ku2nVuliiBJEmh10414mDoky3-BC3lwXgsb5r7T6mPUqwRWF6d6oVGP42e6jk9noMbhRo6CpV_fvnj6tn0_djhG3eYtCOC6g0I1pkDpLxHHz0CLDJPl0jz289eF2tWy-NX6A2xgGReobDPu0Rkj2JJRHIOBplRfj_rvASWYxeEJgN9Q_hFIuE4bR3yi61lvQvXFbo8Pb_uO7CZXGmSESKvc_kWYQCviBabgzR_fyKGUiEaApwONY5IaKzZRLIc4kVhdXm-J-nk-CLSzDghV25hwrZ2AHT8HtoUpOlE2zntIm7uQV2iM34nlPIxhyg_l27K3h7fkQSIRDO8jBHPE7FU2qbBu1LBY9AHBxU9vN03nqsak7af-sWPULnneJfer2_HkMy1iBC1TWnPYAApP-4oqEKKEbIvI2LgyeS4T2I_R04Lplrj2T8LjnUPVKbm-uQU1oeCgWKRswGJMZrO8-a6DbrX-tm1r3VVO8zBb0An1jplNbFVzPmvduHgZaqZwERK-w.DM7nuFHif84GiMC8R0Gc8IewB_GKZbdWed8UW6ERVjk&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-b8050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjM3In0.URDlbYqvI_4xgC8__b8m4aWJD_0htpH6r9MvMa5ciqBOQrkKnN-xuBgQSXeSo-YIb93mK1_o1nxt9chSpH2WLBAz8RgUzv-GKwpk41K7Fz8JQIbP-FbgEUJBTf9qN0nEb4vNLtjU9FYUrNVXdJSjyRV439_8F7tVZb-ZG5Og0iFQ3nJ3ROwQCNEXewOFIoYgkSZ0-SZ59t0qh1VnCa3FUgvzhnfmE-rC0secywPZbhWVx7c1o3IfyaSA9FtCjfCLG-x21oN49H681eOufBms0fxL_gMVcQbRztM7wSbDOVZCYOFjOIlxvdVy9YRTTRJIW9g8lQldmHx8LLiMYt9FpuI3DE2M15M4s0zBcP4pXlb5IPiem2abAKhR2dp23WUODNecmTnvrV93CTfrS06wH3qN30O3t_2_TgU9gObPRKrVnpSitloz0Z67kWzfDFBmXScVQAimgpApRPBsOAMuNJ2j36Q6BtessDPzbMRbePf-cii9DEE4QbW4guD67NnUC5FuHBhHbpoaBMJUA4DRQQ.OfVoxtvuO0P-HC8jAuZqwebH39-ruPiBiQYALrP-AXA&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bd050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjM5In0.WCkNOLUfdIuF7_aHoHKyUFb6ctNInYuhGrbPeCZDfdRVOtCgcvbANUd08QfcttifYc60txh-VEy9hbxzRKFXs-fDqlZ5OvnEz9h5yEtIYOSIKupMr6-fLFhqe58-B5e1wu7o-a0zQRZBP_W5MbC_EpGjDHNnzqLwRo6vZlDLSTshM0uQ2oUo69tvIZfeFZoUv4n2V0471CLt-2i--q8LDzjhlrOV5SXTYFi92S7l19i0AJ2aZmRNiFwr-eHck7elB1_vI65MrX_8HAe1jT2U9gAeC74jUa0SuFrMojGEMTusn8OV8ql39kx9rMq2_TrlfctQPrEs0TaktErsp_QXitCGdzeRLpm_YeqFr8h99GmDI4FGHYk0WgU0ZuxMu6HcqJ4ir6zInS-hWW9KVKH4Hcl6zGj5EalFbICY89b_V7ghhwXts-ezjw1qUI9-8ktJ7iXWU0cLvUC4ty4QkEaIs0jF6DJc0bSE8nhGwehZfg3UAhs7hNYTcTzQg1RQ5GQTUfb06vpHExDRDIW0QtBgBg.r1HmSlGBv8T9Be9JBK1rO900neKpOLfkurFTnkx0k9U&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-ba050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjQxIn0.PWRRG3vf6QEsFH0f4pt_udIGP_7GcoytRBppAh4ZvSaHWErJ-ObSkkengAk3Nw4ED8v7a2gM9FdJDxMC5VDTXkHU9z_JxdteVDkqVqMt9R7K82bIbtV7swLUF-r-CHspJ0bi8lDyctNMyQjw6wBUAKLwODVCDH9MTx1AOTbGjV10Br16KnjfrNddvmN8TfLuuZuPf1mVFyMaLCFPvKo5JQNF0xOPKP76KsuXt5GSAz1tLlnrdUcbcGplAYEJrZAdrOFFnWZ-iFilquiqgodS4SfT0WUK1QgH8h3CL_26gmO_K_Wd-i5VCCLIUVyn1vApYh8qVQxpfyNUcVwfYzOVBd0XEQzLnohwra89UGSTdIT9daY5Oik4fwmhuYidZYQ6xfpHd_l4AbqHqreFtsescD0NSm3_fh465INNKFIA3gLbTjqtj6IemidJXEfoVP4MjHluQiy8jJqgW7ihi6eKyLRgE83nn4Qg2aKs4cJAJfhXkZ-gU5kZpxW5wxsx8SJ1LG-3qwQXGqyoXWE79hkSxw.YCTs1jYG5FYUjHXXqwFIuxjCU12L-iT2_l_X3zYrMXA&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d8050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjQzIn0.81XaSdDBrR_ShSpoKRMItcLByngKZcsNVzQf5CmI00ZGBn8z79USYwjd6qjIHZ3UhZchIbgQTGVMlgA-F9LG8hS4gB6YWev88Y3zl1vSa6w-gTlBipL4fqb0DnpzcYwcWIf6jd7H9Zv5fQkQxby4ZjwEp_XxdXmheA6gAZ9N3NMecu5fhAvoq9UfR6Zw9zIbYJBRhax8N0EoCLI12hCYcoaLqvemNWusOxaj5cQvaaM38txgm0Lwh9XVoy0zJee7Pzqhga3-twNWI7sjiFxxyvyB-l4dc8Zm1mnKL-d6Q-9Xk7Bnalo8wDt1O4HoUw9OJohAVFqtE7wMBU9jmR8cl7QpjuYnAgx-UNaCkNQlxO0vRtntB4i6Lty7iEIFNsm89r3d5Sviwx8yTMpLDjTH8-tjJ_1J3nBM-cmDYhbMI1mja8FmYrwAJEVn6IICaPT0L3jnw0hhOu74nLXZip7qRebGiSE-5vOaqV2XOh7uNkm5UCsGdKThtaJC4DSAGl1vvQt7ygTYJPKdZMPZbqS7rA.el5b4xs31iewO8m0kME__d-APAaF1IoonoQs5-Pt5s0&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d1050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjQ1In0.g_jyXcfhYYRFN2Voe5eCLebzikr1TdQR5M4TKpJ0DF1FEIVMNLQ2GCcn53y45oBS8jaTVM8MGii9gqQm0OMNDkZ_3dwM7I6RC11F_cnvqD_jXHN6jR-_mF_bCt523R36JtDrgoUSXXuT2V1zzXzxYSS1ks7kDoGbcRtpuAD63DIf3D3kkRcKXq9_FaKYMPvotQr9Q1f20u_tBJ5Pb01Vj4vTHbSWxrbHA8owPRzRZE3bLiZXRMWS4Drsk42xxNBpZRWeEXnVb-F7llYQPYfieK1t3slIGzqwoFC2-2ZVSNz8Xv_M0W5k2aFWGQRiaxkByxqnIrzwJ2CvW5vcPg5ZK0TSit7dshFtpcjXNfu4I4lGRQcQY4fY9Bq7HHEC44ieOIwPYYBlbq7DbnBQgVx6CsUQKCkSg-ALuDH2FkKfXPhvyHccYz9NxGnnGxdFdJ9mAthB9K21YaGdlLELYobLsyg9WAoQmMaSK4SwAKnXexDRefHDi66RcmnpA-LgoW15GIokiXJJGa1uTbNJXQPpSA._LakOePWe3Qrk1VP3d7tsm-njejnuzGXiAuSijv31_U&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d2050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjQ3In0.Xkh9hUFldiPMIxuEJkPGWPEqH-K-DP0sKRDTp619pLpEzzU9F9ddBIumbhwJX59bXThbuLOmhSXauy9nJJbW8ul3VScKh5QqmgBzuW4B_ak1_89m_9HwPVT12Oc1FEDdNQnhVNOc4wtMvkWxkhIN9qTt9lZFcmdxFXRx3Ljip-cV-UIvkKsOK1hesgcyJ-c5P4GMXphUJW9KC96D0VNtVD5q0608K-Mf66-OZnYBThAqgAbUBC9j37mu-K9d2R19I9Ue3kVFE2wSf-NssuEVea-qTXoyP9VWkuwhfJ4yfUbwm01iDe8z9UyFEWqnvU_F31wxN0fOf1LQ51r4Swr6RloHTIvh3HRmpgM4WB2_NeKHyvbT49rPjjeZRvU42LzEDQsDGr9bU7Xvm3A9FpDCZN_Wg_ZJewpgWjATrKvwpgqDdVEKaFNimRJLl-yafT9G9vyFuP54_nLd98SuWkaGFzttFEQm2sGHUA4hecSHej37W5olosZVxlyvKUCV5aj5bumvg9kR8G5LVKBeQNOoxQ.FqviXcI5xx_wWfFEzOa92FYIOqAm61AVU8V1n3sG2ug&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d3050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjQ5In0.PedO9k11IrEpyPUonMc_hU-5HkKIN0C5HEJACklnqItpv6PJVbTqIaIWQlI2kvOqJNGYCKWOugsJcBwxiAo6VIsk5bP_pU7eD-FKPo13KUNMzxU4H-toOIxhsEl_c4jrtxaefKh2NFnuydTqY9lOgyodzA9KQyUboqgn1TbiJxs_Axa5qFq8iNczHgRGt7QhSozqek18i8uBa2cmYyEahLv5viHqAc6ztB7HzPl9m1CfzT0QyTXHzXEoIAs5f2iHs7H-D4LYJP1xX4Ia-kBWpnTwxyxriDsgqhsdSUrg0BWK_Dr0UvaxmmrkDUGME47C6diP5xWefQ2x6a4X2qC6suG2EXn8DoafRrLQer1Oeb-K4B-g4tDD9SmSfD_pHjkxT-uYZvfVJB50p2PUzkbvFdCDb54uU9oT5NKlJE3Z_kRj3AdecuaYlDFyqIYX1J4rHHCVBOzhKr0nkdN2AFuWJ1mxvL1Wvvo34apzLu2XXHbUdL9getlOzkMinBSi8hJZnHg6X_4drD9pnqaavf7wLQ.T7GqxfnYS1yGyCHHNu1pNS9lenDW-W4gDAqc6WeRLqM&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d6050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjUyIn0.KK5QnAMZsODe05dfe7OQxB9-NocMrDJsvYhevLUU7KoE7C44uoHIWQ_knLEgj5WhnwQ1G0KUruGo4BTQm6F_qotyEO8-RQHjtmXgdDUw77eZJR0fkwjK_NM9yUn4FWPDuShG1R6nD308K6FEZ_PNjhhFI-D7LWTyZt-nVqMWzPl3sqUzILXjUXAa8i8DdIFN7ejpaKUvuumEZH7wUa4uY_FKhThh4L0Tl3dFiuey9AAZ6GT5SwTnsQ2JLzqLp5b87LRuI5J-f7iQVhPB0dFPPN2BkIh8GAQpJzcQhDBJzA7C-F2GmEpGUmoijHc3fvE2ohKBJ9QzoavkWtuQbni2hdI4_GFoL2DN7sX8z9a-dHx3dEaJYtRTq7p4wtDlSqj_y9o16fg1mEeu28kTW5wJViGJun7UxGubfPkFCuOyX7t1DfBc8BJHo7h4g5BD1IcMbmzg8yVvP_5kWYHen96LysaIQgl6QpsXiiN05vDkDiXkHcYVS-T8oFn2o8kzEsMfIhxikT6jc1ZVwYhnRCpOYw.sehxfkfOqgUp-hXDu7xQmR8S2RLyLsXUVm6nXchLYCg&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d5050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjU0In0.pJYG9jT52QRFQBEXnhwhFobwI3vMhe7lRyGRXLjwccv3TkXfsfmd_1yxpi2Lp-__5Lnm0D4vFEk-shMVgcBqGFnODxNJNY3zHNYlAOfQ6hLr6PwIThN41fbY6Iuaei6McQ4N7TM_0ie42PqJagTE9Zl7zqzq_Vjaz9ycBo5IszKSmRUTX7uXLnFKxWvFwwog98HMMdjk54A974xoy0ZKDbXNsR5U9YbSITjnH6zo_SXnfVrTfzcRhdaaR2MIWZbqAw4IGpX-8DIIjtCP2srBTmGfDNfqUhDerzYX4mtZdGXjR5ch3oylQfT6k5cclw73xrsV8EKmqUvsS7n1Svel-F9A06NVUsdYJI7OYuLcpp0vUPfi4ozc5R_yanwrSdrmIiJasNHjGQbRSLALZ2Ef1-aIvFzFCSEcVpiMYwUR8yE2CA5lwGjvZbidUBiOoh6Kx54WKMX4FdkEO76xWcmptOyNVYQ1b69PRBFJ2vkXKBzxHs4Cod30UPfZ3sCkZoF1DvmS7KKU9-iFRanrGSo83w.zwY7neMWBGygINb61D95m1uLPeASaO-C7uXGNqCohaw&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://1drv.ms/u/c/91277b806043e344/IQRE40NggHsnIICR1AUKAAAAAQ2lh7w5vpurz8uYvVv2x-0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-7a040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjc3In0.jpBfE7Iy8E04G-r8VIDJXNH0uQoEw8K_tXbD_15iZbvMSX17PNLMGISePHNF1fa8PekzQNGdEcVb-5TZo8IaznyR0uoBCoTfHsx7dJjBwFLU696eMPc_o1rCwLgCC-84r91jYQMPysKSCxnvdN6lNbC9H8P6a1Ckb4obwhcUNxnPC6TMZtKwWkk8W6kMj7fsNVCAwp_30omUISpYjJ0ArSfU3_a7_JLExbEcQQsOodYMCSpxo5RTJER0qMWK2h6IdRiI3j3WXenwC2M53hIlavQL44LiAawOf-QIAkW7X1e2is1_3LZmm7faLSmjJwX5L1qzrXLMhcBQS5_FKFfA8WijUG1uQzHnE5BzI2mDZ7TogU9MA_vNS8bbDK2PyTDBP1E81JQ033leKfM1_jNhbsCx23Wie71vgm2ySDRsOvl0QnuEP8KTgYzzGDjHlhOpsORXKjFYUGlD8hIHvZUoCnX0fsuIgPbbiXa7OZKUmLMDziC4X_fBdoJaLMaNXExE4n3iz9zzXXy9n5w3DLOuoQ.yoTpAXU-YXHbqOXBbhVYbbFwBtLgTm-9KylmPgXnsHk&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-7b040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjgxIn0.Dz6q5XC3nmDPIGx1w46J9jag85_1oeRaNe8yF0_jSj-I8N9ROxKtddaM0orK7cYyH0JYTY6e9iSe385DI3LnEADgBnpKXTFjQt0CG-Vxh5eCZWad9CDV9ZED2ka_4VuQnon-YElAiS75xDAY7RRND25fgL0wdhJAgVSqwY0OlM94n4o0EVYZMqaXgVciNENga-aXM945lAhOyG4jD5edwEsAnDFqHBt5OwhD5ERBXaB-hjIjShNti8Ap9hhmrAsHf2TTGsG5lhkpay7olFfCcVQrBQehHGu_tFGdXMVj9T5GirlzUX3oPSna1wKTcNzmiTyNpz0K-LqAhduxeWgfaXyepexlMZotRKOhv-sZ2Y6FQpvH9sBWocyJZzYoVNMtRS0tJR6qcFzQniJA6vCfNwJR0NZ8o-TCSoC0Gq6kqoIH4D2ahxU7BbKO93Telcr_WWfxXuV8Qoa24gdb2HSm_JvbhovMQxXXTpla3kv6HOo5wM18EM2RU1_OvZJTyKuJqb2NFDQX1s16QS7LeKtDEw.b5yelYVWQolbNML6jUiDmY376oZazwedI83XXv9brug&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-7c040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjg1In0.jxcRc6lc4JraGvxIYDOsbQtAFL7COuImmfTYeeplkaiIXxOowvwhHOXmS-kwmc1zxSMZqMDtgNR_uGUcch8Bun91B6hDKkx-2bF-VY1og56Sx5469bDwJbMSbEDRtRm6cLfMZM_bz72A1iwLvafcgXWtTREtU5R6fxUX3KSdpEymTNos2GGj7xictVB_yCQ67ryMvqCvX8ZVGiHnddHEj29lWy_xKogiQhMrjDnx6Ddgr7b373dHCkNNoiMgNO9EP8Mich-9OMuxricJH5hHd8iPU4df8a3kiUfW8pBqTGAQGnkXfkPmLiRaEKMGRlO21YJsFFsPX77a7zuUbDPv9qXcXFmYpV4389pXiPCYdGJIfQ8tP3l_VWAYiV1ICpXIVfSG4pPbRedMTTbiFUpyozl3USY0sh_lXzGiTF1mKpSrYcGjssSOi2QcxQqhKNYrWGUY9l4Dx8CpHVOjESEmVX8QL-mBlqYWHmUEr0_2AO1Q8nktQU0NCFM8NyfrVitaMdEkX5pmeaSGAVH4ssIKTQ.2wt7zv3cH24vQkw96FYhtojAk47Nhxoq6jtnN6zH8Us&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-00040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjg4In0.ICakk94Vc1Mn-E_WadcCfJAyPnTG9cuXw7fTD_CjYUWZV4LcmKtARaEU43VyJVjDe0ekRsJDoTwktpm9I1x9Z23yxBMaTaKRyRDaB2BfN4lP8Sx1Fv9qd_W4s8U8nhXNl06x0s--iDmJujyEbEf-72zUPQDr1Tw8LpP_UOkP9KnLwpNLOHfJDEQ5GtzrT8Y-kHvY-xL7egcZIiP_ehQkqQXqw4k-92WJlTZsIbNCsjKh8J3_rsV-m36iTnZpfNs3ftqVeq1atCLA4vZIun8RVeGKLuFTxnP2ZV24Z8euckw-sLPnud5JpxATeW9roK-XQqaABUGoZ-49cET5B_CMweyKZPbhCt4SwgpsxrFeyXg13zixK2Ly6j2AL6OwbEjIXOa0xjKGkqMZGCD7IagWcgNwV8A2ZvNYGKRfyr4usrKHBaMTjY8C4ZotkeixmtWtnQMwvkiWp35346GhcNtobb7nr4eo137u7ShTs2cRFzd23KW7f5gg_aZepxVe7hyjt3JcNhVS36cMcP_1d6CmwQ.lkEhVeriz0hyWVZh-cmU9BCMdVQAqOO7P-8UwH5TmP4&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-b5060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjkwIn0.jERfF44J4gExz5dRwLhY6Inlwioy7Q8BlZripnTPLxQujYmgWJfUHyBPpbgBWhIzGlu1IvYEs7adAdN24wsZ5PbTiQiQ5Ce5X7CAv-nHaIzISrZNWslbpGwKg_ReYx0PVLdb8gfTz3Qn3wXIcR8tSBjWM6C-DA8UZCNRAU0SGtlgJRaw35V7o5IgNwe6Gwaa1VTQhZl5m6oKOb5BYLymH728dDbyly4QWheTRjwCxYJlBhwt-B36AEGnZ8qKKcTOusxYXQixYmOuYGDJfRj03UFWDinq5A6pTPGbHar6KPzzBajy_JUYiJXEAIwTgPU2USxMv9I9ggTfhNksKwX9dr2aiEyw7D1wsdjDKTV2cBnlRyXj-oE2mkx9YMor2P1fF-6U_fB138kUxl96WuPyHXw-VP59tDjf61I1rroMmGSJwa1hrRhQFvLUuhAF4Ya_5_60dpSJ_-t6PEuQuRRKfO0sdQafdWK0rJMAMZB0txToM4AkijF0DV-OOcad1tRGb9uDvh3yoXwS1xL60XWenw.wn0OS1wG3VFMMCfiGUoTYsgatQ2khHW1HcrXmYf3rzY&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-16040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjkzIn0.NI6N_fAJcw4ZpZTdanPoaf5FwdrrR_PTM7CDmCkX_JXzlXJr5_k99IXAfJbVAIdF7c74sszxsi75zmpplmPHIJVL5hHJDI_xawPQTMzHxuKcdmWvo09qyNbv_GuSoJbkH3nj8_LqdaSlYOj1etmpVeJe7sZg3_dfv0YB0SUnVI_6hkzQGc3oORzSADEVCdRCNyxBzc5jQKj4bBL1UDXzIn-RaWh_6pL1rfaJ1LdXFo1TOiWOaZDCdIZQQVmzl-2pEaYgcwZl6A1xS8mH946DEeHtNvpXWQloXFHQkQN7eFuUS-zsj7JRtOgSTmf_HgbXjOdpBQIVBpjAD45xfJFyNawggEkqEAWNMDdTuEw1CII09nLpsKBlHKKqrQijcXAGQy00IoU9IEbHIkgYM7WlpPqqVULvjq4N0xBmCbnnCkkAlafh8nwD9LItjpII14ilhnrLuTLapKFox4XOHTm946tGx5Lz547nLBl8uQ7zbVE54JrvxkJDEyRkmFGmZznoitigUlnsk1jpELoEgGeybw.KyAB7JGkv403efJnNbWV6rmVN1MORuElp-2neDFi_2U&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-1b040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjk2In0.i7tVjFLxwmDkkFvUV_XchYD6z8LGkszQZvsBQaINs7gp73g8wRlosCc_bVWUp-8P-_xmSdBYOvFQnH96bzJEP4f8aDw4rb_pxgFrkq691PLFwjE9Yb02f8-D77mIjYwXikBoXILEPGk4OOcojtZuq0cAZs6J9NgiPpVRFB-ttLeX8YVrIxcdU6qahkUmsOrjE8MQWd-Tez6iE1FTVWOcqoIPkwoWviXsSIdldCqeE5nyvawXFquqDwG5ysNtOh4dJY1Pn5bK6LG3vAwhGH5cg11Y5fYK7kphv_SFdfD5GzA3hvN7JpxhRglFsgedPM_rojdPJmmToS6OgNBxFkM9p2-o-fJhOklDVuWkaKyVEt_HsNqGL_N-C22ewPYncLHTIcrXC8NWmqqOA6l9CzLyEeozkm_7-a98V8JNClFP55utjiV61jLPUZSlUrMKGlCojIaWXI_Tmy_is3RxBW0P_Sl2hW_Hz4WyVEjbrHIGJZn8HQxpl7XdWlr2t-72UFCz7WHmDEpKFiBjMsc-AcGIdQ.C-iWbgnoH_UX8mrkF7735X1eymamLpI6n2rHMchdfL8&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c60a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNjk4In0.C3OyP4aMIuYkBQyv6NJW02SLCoVMYpM3tAR_-FrcqmHu-114MnOCsgA7LnJog-hr9CZbYtEOL4gj5EAw92o4taoiLLSRHZ8Uq9S_ciPL1k6oF5HTMIU8fIntzT2BoOMpMD1TZRhH6PnSt90Fo3CyZO3vENgVC8mIMgotErNu-oYmvz4YxUzqZTQK-A04VeyS6X2l58f00dkqa93JUEzm1OMPEUbkxDXO25QUK1_qevZ2A3aCNJ2O4Odw296K1FEWa-XtRTKoAgbKKyFZFQhE1JPULzJGgFPfL-reWbE3oZEMEnY7Kxjc8UEG9L5Q42sJQTfn6YfsDoW28Nl20IiQG03r_JiB3_lDDJkejWKtJE9-fIDfvuA8W0pgt6xK0SXcTFjuFeYLOVb1NrlYL11Zy2HK8CZDJN913s0x6VFVFlsp0jt3riKRevZ0PYYXTQGgAaNvGF_kayqpxflbN_C2_ixwYNFifgfz95rltjkTSe6_tOAXyynmsLEdggyRjXMTHV6E_Xs35jz_9IXvnivJlQ.emQbUSfPo2i7D_gKDcVoAylMe4drMYyhMFPiCESn2oA&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c70a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzAwIn0.Ddu77qe51CeDRt09vlV-VdH3xYV8GTbPnTvT10fpDaWwXA1fXEEaqYrepqX5GV2vF5lSSOP1QAVOj2vXCWyhrNg1vXnrlyXLc4TklpsDwBu5XAKGH3U26EesxBH69pyPIFZtzhcq3a_GjcSm-UwHUIb2CRuE7fk4Nsk9-K12Hn9iypNzASBkgEAaFQInbNCKidzZFlpnDUs2YcUEh7bVG9qEDEqCg-eyKxoq0dTVlklXwmIaerqcWTHoLcBK0TWnUdSBUwEzjJx5YK8aLwp10m0gbJpQUg5BVnh2vvA7D8TURbyyww6K5-unEqjyypXfPAyOZg1getF9m1iDGglpxakoD0jBHXp_gs0XH8jx1VMEFwgnPLDPPIQbjxZXMVECNpgArOqYyJhg2OiFxcUuAdeG2F3-sbKd6-QAoWUCoMiFF11wwzxz0oM_cgQb4R5oXRtGYZ1Nu2bGxLaGnMQNKq8lA9SCCWvfleMKMUutlHcenY82Bo04OBKXrHz_rGTZiOyapPqOzNspQjjWueLbpg.o51zIqVoA3HNgYMDeqkmdvyksUArv4QeIlQwmFfVjM4&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c30a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzAyIn0.Y4zcOZwjfwZcTAgZFbumkFMYneqCgFMJw16xykWELjYzFlO4KN8hTISzgFB3Oeq6QcIjiVad_xU7mfx42SXURk7n5PLaw6hHtBQPnjpcK4lXDCnqiSVSd1DetuRkL4x14cmhv34ZpSW1zbzYTfyL3vMgaQX6UgiB7gv2rKYIhji5MieFz4UR3XlJKX6ceJ_rIaBB4Y5i_rruTqAXLB_oZM24qaZm4AeE_jjPy42QNNGkHgYCdGaLLW0Qbg4VR8rciQD6Kxy3QyYDfsF7ISaCgFCzMchfqcYlN-zMf5Hl9fKKULsc3f8sSjuhGORT6TdIexJOvBKLDJogkINT2sxsNq3B_XFa8SjFNIFB2kJuILD7sK7iDdShx1OWCf3Nd740YOMEiljvFVV2qj-aphIazD5a0-sWyClnxRtgfQFfqGYdNQZfuB5UfgGlvmB1gAXt_qRGOm1AJhiePdfLOEJVMaeTBkLJq1-UI2KkGrczr3YAfjVRQu4mOKLDe7fJF0jc5HUZzUFbW2drciW10-N4JA.YakTzEAnZ8bHpsIFWcxvlIVFdneTOPFnk2XZBz50b8I&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c50a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzA0In0.FdCLU_BbCGpWfrZdVXDfcgGOAPayPC4NXaXDVMzxAwqBtTdfJDbubE-Bom86As6J0PeTekdscFwu9Q4bPWgcqZgsMCa6q7-YKR4jg2jpkTpBvM8nQgRUchE3_65h8bHy3FHjbOBCNmj11GPl5B3FboOPt5U1D78AvDz1TCIxCL5kF_oqvw9rHpRljEi2hG8D1GZLNMS42Zy-u_Jw_fgAvuugcKy-nQlkMSxejgps7AicX71o7q2SftMChWjinJb6OsZHUYmwpJ6DWntXCHXi_fa4HDk_m5Q4R6cRnrEDwjbm-xuTSrvDB1ljy0EANVEi4XWXlDx6vHHx7dBc5MzaIJfyHdSoYCWhL8K0ZP8tmILVk4ENOiwxWjQFWT8CfKcgw0z6nrwIWSXa_SRdkw6Df6UzuVh6tOVZsgsoYShkEEehg_gjHd04esZFo31Sh382F9Y31Oep4SPLG1sHJconYARKxwDNBSokxUbU74w9RuSoXntJYfSiZ_BaD-VYltW2bGGhDOMLnYZP8ZwR3cJtnA.3i2tM2HVuV8QbtumypS8unL9vRWeCB968qeh4TMDulo&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c20a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzA3In0.3uzmesxQE0xUIDK2eBJpiMRLjO7cEgxEOMZ7luyvvhh4CtyG77O_NyYIpFlcc_ho6ZpFLPx9q1xrnntubV-C6Jx5I8wezN8022Zbd25azAcpnkg6OBh8aqv8WBXDHtE_lpS9cjQuZQUSriK_roRvVc0jehqY-B8A9aAMjhEM_E_oJreorY1k_MdsfRzOZH7QJNUXfp21-b913-Gr17O0_zCc113D9bJ2b1IGaIzIXJeiPdiuVl0xc39ZI7uqZDDQAAMFFwNDmSJ18XHgWra-8HfjvlYO4qcntntl_6f7ooVcix4pVigNFIVs4jBElOwpXS2SU4_nP14jpdkixVQpMdxZP4ngE1OGiJZDEIDXjaHCIp1o6yHbzMPRt6QWIcKacMqLSKIp3R-tyiPmFPY5iwi4NfDWy9G1hRB-j_K4lD2D8zz5yfYZiFfiDAGX5g17T75hyTBLz6oqDBkzZ7rnbIUxZERlJnKkG1iTXeaNC1XalJDzOfI0yyVwtyVQpM8BFIpABat6aHuQBmDSva_Mlw.-DViofQa_ei1WX8tppMQWZZqvqZp41OEg-QYBaaEhT4&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c40a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzEwIn0.3zweUnhb0ll9br0zfFYMxAcKvs1ZBXmJ5ZSlQmtCJEmBXld3eynHJ45e7pGotRmBPHupun_FZjJv8vWis96OJeT769BfDZtz5QBD2jY68bBfCwkvRp25UmMRfaQ_AMvIPjNaTadgy6p_S1wfDnI9Vkmt34NT5sIRrNBu7HcFr34nHxKwlYXxgjWDw2Qc7SUCnEoehrpJC9a2Hb3OxsN_rwWckp6hGS-z0bPWMoAzujj2U2sUEwA-DwA6ij11NHvx4TknVsXTBZhxEG8TljGtJRX5FhUb_Yyu7TERZipC9NTRnsbUBESyEEhMxNxU9arMNvc_2cTT0pa_WSh1DZvYT_dFXtag49d99nEJfyeHxsSJeBFLDSymAfeX1CVOTXDmc5pupk_HcMJCdU1nEPou86vC9dJRr3VikkpGRQsbs-7DHDQCoyjvdiuwPI7S-VpO_yV2p4rzqTOLnnYZAW0RVSbTllkDAj6u9Kcp6SjSkhsHrMwzIczRhVF_wwa382YbfEYL1pqTo575jlZYcsthVg.1AJFww9LB1Uq9lfw88T63-prO-beQbcOLpNVAJ7m4sk&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-fb030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzEyIn0.5SgGKuXpUqWi9osmAZJbbGrrdLHAQSi-IEcQOWDnOsAlhdGWSpbJJrQzgG_ig-ugXKyB9A79QZYPXQf5den1MnZHHHa_T0HHLJ8xo7KVqVUWWVIf0SLEdkpHCbVxjuJnd08sYSqqBvpLtC-DavGP9XaPPNz33j6n5vz6_EnhkYL8Nk2uaGsAQW_VB-aA0NQCtteiOJTR7rSY-bc2j14HiulnqCIYjul4khCfI0YZZzvfD8rJ4ENxnJjvBBbKYVyQ7OWH1zWsRDJ4_ifqNAuuUDC6wqbI0DcZxbPNc0i1OWOG9Jz7vqCuFfVcI5Am-uywFHS5mr9l8WHxDlty1ZMtGnxy2FvqDT2OPx8YJnMi_lVRvcQ-t-2TvYZZr22blZ6gPxOfDZ2MRbhQ_wN-wyKQz7FlIqrim375OZOF8uWTT5TCwoar0lRNHxCftTvA-crOs75P3dRfyc94sMaN280n5epYq5OiERGzLEdh4qlVxJ_oHGDZGlvlUdLb1j1hXnGchZG2w6ompHt44DaxPRJqtQ.RI2ZngiXRfwWNMDa8F2cXoQbqN1DjrA2Ooto592CNX0&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-fc030a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzE0In0.0x_Ex4KBWGHPKvgochaodXqWQQSnQr_XlS9IynhpcnNeIYJ_ilDsSH8FNT9hu-pJRvhsg6ssT4CQZoBHAVl28QIn_1ttwE0CX0JCSos9gLqglJehMGE-UyxpayFiur5--2aMS9uJg3R_r5mVFIMSpdIX1L0g1ykP9ve4PnWZGap8n7pWUrpQTcKtHKDszN2VNLm7GZ5mylaJ06sOq8Qrtsg9uUGfeQKnql1Njr1P64-qBFsH1SpR5Y2IkcRTXMCj6NoV3eU1Y_-Al2GTqL4B_yQo3lbnFgZsz7vPp2w5mMOIZtOjQdIGYvLHgzpDv5WIfm9s2gieFJvHQvTqf7o9-ZMFnCu8HHFONion0bx9IouYAd6y9GVLzyR8LIexpBxf9NFgrDep8GvEbpLOSvB966FX4XGLlItdYnLSWgrbFpBl3Q4nq-wwg4B3RzAAaw3RhhdhlzAvJ-pFRbb3QTE5qn7jiCJCU04RtJW8na7d4Pog6SaYS_tE--TPJFJlMUcfVuCU1nbNf3YnBtMfyU-cXA.wB-Nc4HhkUDoaha_S9fH-8uQb0K4Dpvmu1OiH7SGKRw&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c80a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzE2In0.a9070DhKwhdamavS-_88sdI_BrSHbsoilJ2tE1iIlIabhq7T4H1_Uajibt090jDzcJwKTY54udxxUmTEH6A-2eYxbYekqXRF2LxnKZavCG6z-Q4byekVQBPYK2uXKVjHzBK22bh8d2EKvlKsKc1RJ8JP5A9B0ve120yBFgyCHzm10S7pIdqh3c9WEp15jVKDtCmE5TNa_Tkmh7cJZVJvdEbki9yalsRLIq8hyF4OQMrE_nsOas43exDk8mygkJwb41Q_Rfi-YkW6MQE28qHG28qbrtSSfFU1ELwtA8WKH4O8OC8d_3SlnWkSlo8lMa9Q5P7r37EC_61OCm622UJIl-08CTr3KvD_Vv3OxnbObbQUgLawEBKT5ICcNPctPnfzl-h5A1rW33hYAAVBmiw80qZ9yNmH-znnlXdi43ivUAK9Yzin-3hugdR1i8CX_AsufsZBaJfZ6yHv4XPZlE-DdmG48EqtCiXtJrd4bBU60TqoI1rtf2p2GtMnDdNAvkbIIUf7nG3_raZvULx6WLxx6Q.cPRPtpDcTScrML6JhOztdT-qKhWaB2beP4AjfJa-f5w&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-4d060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzE5In0.DxXpVstDnCB0Z19IdkLxAFVWoE764ANsOJYfFBdgcSENuf3etyZ06kDBTF7X59_Fo6j8MS4VzVguH69NFztKuQhfj1u3c1pW_kVTKN1qPE9YaSQmTlxCDi_SgpCag4KQusADdSJDOUQxW4UdlAsmibPXni05p1zOtFLU9iGwV3lFK2P7qfJ_JPKVYOKsx6nxOLKPh5225s-xfJQcf_2bijzaA1R-mh5PCG0hmPT5M4ZRiMxlc-HeQ9SSKXBfBqJ5FaF1X_MAy-wWMMmr48QX0MzViMqDwcfUbR7ka6F3-rbiRk23ZyaNKOSt9xg--8mRJgAkHRoAlPQwEJ1VBwyBr8to1iVvXjMMw-KZK1hfgTX8DdOgCOxMEBdDDZVtL069GOUzJxCbg98kwhLZD5RrUk40XI-5hQwFfxoQBYPB4MODwFHNJHhDwZYzV5UwvmtisonSQ0h6I19GZZKkNPOBUXFpx0i3E-Zy9fRn1fD5vXeZFBIRdYbTIxwEWPpMkR8andOi1t2K36Qn_7o1ZDbuEw.mYq7AD4WCO00WPYhK73g1QQn_0RfZAgX5gttCjXEZh8&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cb0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzIyIn0.tCfXU9mqJCaGRwimB_ukS2LABIoZzY8zxhiwVRbDtWvxOFwTr6hhoJVFh_2LpKNm0HTico7N-ir3sMrXkyzouuyhhRMnHbDhgGSCdYarnxgDZzYF24J-TNRJeYzyZb-3zc4yvgx0bkJcns7sDpomiUqLEjii1ZoPguSG40kprJ89U18e76fQrXVdX0BLqz3izaaCWwk0gsNFFZfqOjdJav9J4xfa6HoZPi9mo26f-Yp6XkE9a5y3LxQe9QOpeNvQ5LMqOiIQYEhE4EGg5X9lyjQOibXt5CL-kqJlVFTvbwMPCzgCZlc1onSijJhERLE5aHBS0W-dJocPBItMw2QsV3FYyCvw5C01JfdMSwFJJe-a3L8z2EJfaBsYPjNgl_dh-pTZQqrJpcrxFziR5_SPaGtu99bBxriHkEZGL6E9iuM0NSvTjR55FPYxwLwR3CarHkcZMatVLwbfrHlB_dgGObquaX-zWA4-bepepVveCvvlPFFIqSnvDeI4dUAJxppNJPSrd_b2ggZyWiIRbiX5VA.1K61QIe8loQV4gTCooauTsJzxN0f9sgNlBfbTTrPVB8&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cc0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzI1In0.1obmUxaRgD8on-wlvUF5GaRP8ZZ8JFwBU96Cqj_1zzGRm_MEPXsl_pwpr7G3HDrO6Q7w6UgtgzEIRa115papwB4SvxvUetTPvtDdER3sD1ZT2qObGl9_sPXC98G2CycmVMHHIjJbs5UJXJe-8hHQwoN5J-CkM7MxFh2uL49vIdfWLvZ_4wlJqHrHPJKDPEgmK2Rg1DYvAO7I_1ULVakdhN7vMPeaGPm4qpeYzytkNlrcDFpb86HZ_hER_dthnw7b8du_5A3E2lJNApHdPXAMNyU1kl7ypi3tAe5I--V6WUyARb5j9nAcpa59WFdqwfcRrJbbZ93_PZMuDTEd8qmElYl2oykjpuxMj2xfJ1yuga9CmkDldEukiS40HfEZPCOGbEz9YEVIRqKa7UVVzfZGhBhP9_BYC9EbJS-oKd5asGuD4L_tgjdlQs7rgXAqW2IsR3cOi4_nJ-BdYtoHoXXUF6XANQE7CIw7pWf2hjzmY5QmjwN3fnmUGkqap9nS-1JmoDc_rfD6C8ydRCraYYEMcA.ly4XN1Fh8d3isBvTixi7-gSItO4y1ckU9rkaTgCMC_Y&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cd0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzI3In0.Q0bEFCbN5fG5k19vQ-jPtZ74nZ3NKKnswIB46qJUFhO3FUt_BN4_IZGSgrkkRIhfBo5riFu9VrPk6uYf3Eef7UjBqQZSgCqmuQ4I8eIY0QpcfdbEHniKmPmz_QqazEDX89dNvz798UZkByZT6fKxHxJewieBvcnmVIVYk2KadU1bt7dEmw6graJFcltFrsgK-FUYmrXde3MkagYpqGFKQ-mQ89GI_IWDZzNwRO6cpQkVg5oiCPeXlY8IRunBCZqLMzHlgQR4ZqLNITEgj9lM9Z1JJfmmspzgytA5056cVf77-lVUda-pJNgoeo63409IzOU4BkUpE-oViXLo-Y4AhUyH4taJq5WbDedPPhvtqeBk6236DBIrXTbkDWHfwZjtDfnvvCYMka2hLx9xyNBfZK2pUoIJryv3dEF1D8ijT9Vh456zZjHRufQy-8roIcOs_I1v1ippI8Lz7rknCAGBAfhJGJ5LafcK3EWhvW8Ripeta5XjjoYS4aULiZjDT5klL1PEFHWYG8SzFUFMLqZ2Dw.FcnZAFgy1MaApyJMJEh1pOCNdinCASaGIkGGdMU-rIg&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-ce0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzMwIn0.L6fSCN04ViN5Cp_o0lKc91Rk9Nj-uGEtM1M6NkOurCcFgB46HQT9MAJYKzSQnn9iACRGwYIUjs5VUsJjYk7K1h_0YqCnklkI5RUizgiQRV1lajm9ZBqdZcYqoixh4_7RJS-d8TIGvLK8vm5EvmgCD-qiqiDPtSUv2jN9hNACAWk77c2s5UelZ-PWt6HfDUL0GgvRDXdVYxGVELw6gSCaQDLx7cIjJyZQov8KzQV-58_mmvgva0EfAMiWCoSkHm67r1k-LRoOWCsOwwclQ-VNHJtdsYCORB9LBGN4w7ta4IZeye6j0AlOxkk-Fhw0lSy5aMePDgnZ0X93ZO404TeXadHBrVS8XSQRkSln2e1sevQMMDQEgGw9jwVtcBh8vQ46sU311b-2jRsrutZsxpAV0zMVLmGp2w362grqJez9uQe5RhNSxoI1vo0I2_2mVv8hI0H6mkCQq-cJv86eA9_1bDHeSfbB5XiKZMSoUAYatC3NWlk5s0IOfQaHJafcPXLnxQYPn6r2LRhZ3xg8PCsVHQ.FmBAOUudIWGk6EjuZ6c2TMfE3agTZ70_0O5VBeSJC1A&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-cf0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzMyIn0.UM8Mxo8z5LRWZb7kMgy5YH5w4qWtd6KCwg7wPsnNe9iEFQ_XASoONbqQA6WPpXUMF-bGVCJxo3reYpRGrR2epwJ8yVDDlFictm7oEsUzerg8xDmtwsnx58pUx8PV2zwWgkPFKUVNtVy737OJJObFUE_2607wn9LONDsizchOQVsqHet4GsYsyiCwpgRieds85656ftEUGZuAfsztyUF3gRXieOZ9_8qi2oN_KaR7Wc4TP5HpTXK5MUnE0zZZ08o7Eu1WhKWEoQSP7hgcAL7UGWMFH60XVoqh7hpKwjA31EsEHn4bOG8JyFAURM21ztTrneY5JVFhjoXD5luh83uaOALeCHx_ZIK60mTZMpUi16CFGq-0uKuWql-qnAkA63J9WI0Ztz22n3fmWt_1b_9wMT4eUApkPOaRiK1Hpv-A_t8r6YfuIxCnG6gCru8T0QGQosxnGDdlrWZ-Nv9BiJI_7Zl5L1YO0x4xon4rHaGMI1QOLvpyOBrCTRxicn-OkEtu2zBOIUYAmbnKmLxaBsmhyA.w2D-dcLbCVOb_WeJfF-POiM-AJYAz1KHJCR6Y0T-v68&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d00d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzM1In0.kAW7D2IoHm2EHNr_ebiE9sR66JOCA7LiXpxgiI-XUaoVP8lLtialoUQEiTwCbkxIU3hdpH6Qz_KAxYs8wp3pvMwTbNaD9L3kQUbuEIWkv0ZR8N-oTh-_JoE8_IjDtO79IS-R7jMkzsRpOxZpvLgJQHM98RCHcyJpQ0hJgjbWPNWF61B_nzcbaj5DHNoDucqqlVRAuKBKfnAC4eSbLfbkxsttLIo8j5iDMhxwNeHzO_pCtZgPzvom_0t2QSj6FOkb0-CV4Bcen9Cijnd219e9ZPWkK2_8zIC56rr-M2-6Gw8YdkILj-awsve7CLx7KqkrrjlSAufl2mvy5QDuVtZzkgMuFUFES2dH3bH1-1WGcM6AQzX0dSxiHkJ-71Zrd0jEQNVXe5hK-MbbqC_q5c57_HjbLhM055IsXYTjA5mI5z8fZ1SmruiRlyiMugc3h1JInliWUS7QH1wZlhy5j0K74-LxstJFNefjkP7LmH8T5O4TXtEvks1k5sCCIRWRqKNFeNkNFodR7dUiNPizJidmFA.N5lkVLZPCor1ZsjOMzw-aPkt5b3hYWRzWS-b5F5w65E&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d50d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzM3In0.bwrEpRQRyeeJbAwu9ja4R5Y40tYkkQyv-hIVv_o2LZxY9IWbIfxtuSlmm0EuNtvoN_mwG-zm6wU2ief9Xp9OXGpbyp8EC6BX6fz3Wt7wsAwx5wMTVRzCz2WU7vT-UVl_cvwJzWl1qtSjHwj--PcaXNdN6lIpLFIoF5sn889k-l6X8iHKELdOaYcWZgfIAR52m91nPXgQ6ktC4BVepiPWC9hK5lyXicCflyiteUiCj2-ZUrl5qXKT8dFDTNNi7P01d2P18-ERvBg09jAysOVQcFIdDDDS1R-DN0H5yeRWXqbE661q34154KuMmTdTRDb-5f_Budl4Pe0gvDd9aertgaeqKdRRo-8SKP-pPkriqKKiwjG3hEDK_1N6T00Rv4ZkG5QlpAG8CQ7uusIy1QnpkK0aJV1Mon2t64wPgOPxuOcUmaeRit7AsGzmTXCuqd1UBnXwhf9pMeF3vs6s3hatTxhASG-HTzu-Z8JckrjcjhZkLCgHHuKeppI8myQ9P_mcBADHaFI05D97Ly6AYLIUMQ.zNYGuGBokqxn4GsC-MCgjDIiV7aq4JKK1Q7SQVhCN4U&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d80d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzQwIn0.PqIQGxQ4bWKoVoPnCZI-Hv8fL6Dq72xM0kUuV1gMpI7-3HkXt_JLBthV_Zi9PPPLgX0QRFNwMmkRoq2VKaBQO6Ut5cFY4pbCiab965CPrq0lw0N79gQIzKD6f4neMC72z4zuTrWJHigVpf5P_hUE9mm9gHK5eEz1W74wMj4MO86yRaJ6gvsRoHzfGn07o1MBWWcIm9P1J-ifwv4DDxVZc4oY8O9yd0t1SyPACc0iMbdQHyyA7SOO6OrffbqWTzp_a9ZKpSfPz_OH8J8GFA8ONbXUOlrMVax9GFOoJK-3J4oo_tP5ZnJkk2IzNzFeUqFap7eu6n5R3_6IP66reowMoySPAKW0OwZxpye3fuwUW5AiVZ0v2kOxfuHY4DCrnjQ6IlOeMB1XrcYfZmUb7womnu-Uv7UaQCezX0Ap6AkJKLhjH4zlOHxzdZcSjoeOIFTrO-jxpoT_aHMhYM5Q-G1whKYe0uXAmEjLAVSK9HzKENRPtiM3iJ_EyY68OymEj0D23NL_loTos_0mZkAjgr2tWQ.48D5Vt7xRJFrNY79CKctFO6uLoHMGWHMyfctVmtk1Ro&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d70d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzQyIn0.qDOATQlEDZjyIbd_uyCKyoKnHTtGNbcBqY469_Wt6hLVGChoYcgrENktfIuwC7Fcc4SjYSJBoalx4BsPcUGR0UKOwWr0Ls_zYIwSEiNAa9MPurZV9Ix5Gkt_Q1Rra5Q5PnCN42bMbsWNQeR40SBtI40UWC7GqSdH3_3LBF2SQHy5-hJqnF0SEytRwdaSA054uUNsDs4HS2EsZ7etVWTausNHmY7RVeZIuQercXcvfoQgAWMcTsobVlTAmptlz-QGQHArtSG2lUL6xWHVIhoRe_lJc7SwF7uPFDN2_W55t6uEpAQLlm-Sb00XDFMt1M5hxxFqszA12DaE0aYkwMorLUveyqG4p7vNourm5WgGDPGi-iuF9fLQcSRnRPjZ-AnXOra03tOFnJLzrpOdug4QhXj5KBKv45jbbKCMVf7KNHbdnP-qccwQ4vx-jpdThoqroEQ-0UkXSwBb2NyW26iaJ_6UOz7CUePjqPxLzH65x-mF0VejYYDES5yuX8jyiWdR-L-f6fK9CaSvCpCqXMuqjw.IjV0SK8zBYCxa0IfYI9nQ2pGCwv4orM9jXdGoQYf89g&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d60d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzQ1In0.EVwdI04Z3ePQ8Fq3gUaf_lnSYX0NimsBh0dZheLvRANNVRns_bIZnVJvuiQz6ImiXbyj9tKFTzKaOXy16K7EGi2vviuzr_hzKPq8nzKif7NwCEAVYgOsILipao8a_zevhYsjfU6fB-TN1xkwfBy-ermLLjlq_J_3m444Rnk7ViiQle9jgb6ljaOL6iA7DHyMfUPerS2MHWWamZfL8SvBPbEmF6uMR38lJa39CxbGQl3o_bcIS46XU8Y46Pe6OnuEcJGQA_U4HRQyuPAG5hXkvzJZssVT4HbYbxgKwUZjXB-7CXnFYr6pHub2aa9T4n4YN_j4JBT9UYT1aBNfvRdj7o3ZNk2xBFhoio1zOKcVhwIjzoLRp7YtzvU_rKa16PunfjPnVnrb1feMeppSJ06WeCVAyVcUSOWBOtatQUqt_uzsewlg9ReAvo0dJOLv8c91xnvnwmbBBkp8F7W1wbXRKmP1NtTjZqzlPe0OylOh9JWtF_fAPJ8sJ_sHH6-Hs2V3EiQABK2CCNhojiL7ei-S-Q.RnWIiSeWD4JFsaX4clmAWURK-b60wXb6JWQNVnWVm5Q&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-da0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzQ3In0.gFqASIy-WiU34UdIDDG1KGud3g1qc6Ox9y7qvfVUQ-KPLosHS3tqYoaM5-C0qtr74mM29wNQfuBCU-HucxH3u696BJQP7HO8SSZr4i-LLJfhSf8Q1do15wP8W4nlu9qAc8RI7yS8AENIUK4LjDjuen0hmhFcwOrjSlLLTDrlmSSaPl67SxbmUWShOFyi6fseEV5ik5JK0e1-faHUeV36ule5KnPycD_M7Wu7P42NP-PWMdGYtlXxp7_CKdT8f4jJiGwJgcdrih9T3ekkOItVPBDiEF2HhVO20hvJQK4Ny_yiGx22maAIXSwenQLzWzMoi-kS1DualwYGAqeHbpVl-N_GfKf9b_UuNHFrOsRdEtSSfMxpdKrMHO8lm9rj1y339yAeq07d5tBCH1eMX9nzcJf8ht-A3HqCqisCF4DDHGYt20O1tdUJd_Ip_xa2u4j79_p5yVsWwOIlg2NyUFHrFP1ANrs-RA7R4vEia8-1m17AT7qnrO0mI4aALengaW_oc93RLDx5Yb18nzoxpNVrhw.AjBJSFD3raERnH49Ka-o4PphWtX-JvTAfphOSViGH40&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d90d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzUwIn0.IABVEdFZXXrAWRZG4LCtfHUNJK6p00bWUThQGTvSImcxjYdwixrP0Qjn9BUiygqd7Mc8FQDGb6rX06j_tarlUZP5X9MNpnNI34QOCJ7p7l9KPGIL66c6kmte8f52RjHA78VLJ3invkctv3GjqQSMI5KW21Wco88pUqLn0B8LaY04a-opEgIhg0mc6sJ4J4Ho9Apb8rUuf6_f89AkXwtmgLOBYZ0sfgljUiCE6LtSYYwzufhLoY3CcR64V5pdxgjSt-uyrBS2ZFPGgACAls-iaQ5lFGYOqNB4iWa9yU85S70I2BQ9Jd_80OZpBSaopQ9nCaGL-cykHotdhXRPzhgBu-iXaehYZpiDJ6F2FuO96cTlSI2FtX6aPcfb72txreVmc9Mopyr8c7a5oaDVeOOkuuLHB__Hqi0eeQCS-UbkVmyhLfrsASFsUs1R0q5DKfaFR_eIM2JRVx532ch8v71BhrM6eab-D1N3W6wbZiB7HTT_gnUmRMpr1V_piVb6MKYRrrrgiyV2VEeBW7TEoGf91Q.pCuahJ4gatNMPBavIrfHX8YQjsH0m0oTa1sF9zMJMGc&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-db0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzUyIn0.7zgPrsNK3twc857Bd4BB3Wsf5vTG75-jdiIiQgB48Zwtum3pnfOx_Upu9kMT0VlWraIYmp_Ye7nsSVNWcjX7tuYN9TmmyrOcyaO6vhaB0Gq-Flevoy5PcLRe0vF0ZTrfBz9Fstrq8LFWjgffPZ8y7cN7pPgEOOY3xOHsVhkfb09rFeDeuVfJZrkcsMm3oLWBZeV8FBb_F7hFgYry2ZTdv3CJu_YiHq2UabBl60-BF2odiL3saHa70pVrbItk0glFrVue9r5RnJRnQsf5cjDIe2-NtIQcpbI9FoV8w5ykxUngH-DxdwDO1sFfT1LUaQL6hVr6CZCb0n_a6VNK_cfzSKKzbyFKvgmZSWfFZXTu1O_tnaCfVee5oQlynXcZB5TQppJ0fgUP6znpeCVuT9r3-reJcSatO1-js2aJAamEy-4mlbX7w_Nri8ajlcYD6fOqSpZtdqtNjrB3nMzaPUZOKjClrFT4wSLWLOf47HvU6NjaijaK2vhbU82bNEKsob_NuwjpNwROvLKSO0WmITu_GQ.SPbMEtjzbd2IBm32VQeakrryqjNLyb3BCFv59YLddec&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-dc0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzU1In0.A8dlp8I9HZTHClnPIGzB7-PLbvJpLGb817gtVpoXXJDDfKPUFMcUjjwxafulmREI3bv-qnrTZcoH4KAvypOPWP4dk20vCNNhsn2RbnnUZphqrnrviaDYqn2QPg_ogqMdSzAzAQbWeHTuGK4J2GkkvnkqRXiFhjGtWgOKaV0JVucg6j2FA61QksimQZhhEguCtiTydQ172GcGyeEAqKRu8mMlMVcMy8ebBX90_iyIhSF3oSUF157lJUlTtuNIIcr_y8CcWAP5oXek5aJJIq79c0nTKjAaFhYUGfrC67t1igJXnBCQMsTwPLYEUYkBhdC85eBdbwMVA3yJjyMgoSxvYY-bw4Dtsmnc4wp0u42NiJG-lyWghA0S1JPbyZ6bcz8FtjZceb9VZXZUKA19Fzc6T7ZoeaBe2aOaa4cePGgAH-ksx4dE6ZCB5jdzHtXn7JeYH8Dn5nOi5b04bJUH_mjK0_doW1m8V4AH51evwCtowvbfjkXA9WBEIVAFPm2_aihF0Ne5fbaBa0fyPGbfVPQP3w.1nEhdhRi4IU8xaGqyHbu3cH1AssL0O8FCevZuOTK2gM&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-dd0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzU3In0.zfByrrtQr7PD8kGRVHWn391qDREIehYLh6hw545dCB427Wz-i0BM-aGODLOdNyCEwrez5O3gSmb5LYpqRUF9uuhrbvBWNwDnRj_ICCUH8nz-jeSyvrJke1ffeZqKtWvBYQlFNI-f34D8jvY7oui9utum3mkQbASuDFuvVBTCbH35BDsTIfNZV0SlhWqgmkrfABLkGLff39NcD1XUYUiHlo19Z7g1EqCpK-EeKI9qozaH2RXk1hQ4GaTuf4rNZXNyLyHZFZiEFasTZxI6O5z-W_60Ra3s13xua0EL3QYFm7Lvxs6Yl5uXED9Rk1yS7uZ8VYkq6AvlHZvataEl-O5oElt4urBxjtghmbMzT5W_b3pEvyICGkZtQ09-uLrTEMyzMy8aV5mRePJjHpgnqUE1t8hnV6-ZzyBBOXWnG3DyYwbctsHDo8yMpQBja7FMEUkdvWaqfo0tAnKG0dkaLhDa1BKCi_ya6Kjnekj1Q5L26tiy4d3Z2GfV2U4HgZo3gP9_lcYa3S6y_yriDIQsdithRQ.-meQm31rv_C2XxyBoGWjKlXpRgUhq9L68M8kC5CpTdY&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-de0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzU5In0.T8KLv0DFH8QDdN5M26_2TsNH9Gp8gfjLCUreVbwtdUEHJF2x8MM5_3OD-VBaYEfRE4WdrxSuYg759qSPTHDujR7P8gH2IkgySNO7sW4verbIKZnXEeRRRqJwdZ3B2foPPao_b3IQtjbRspxGGLKXApfVeGP7p3Vhbu14mtSxvZjiGgEe4mRLXsnUxbcBjmiJlHq5Jo9XWwH-d31DnfHJNmVfm5PgG8d5JloHPRZA49HMh6ABmhz4ewMK42Q8H6e-_oj0FPMjG4HGBqAj1lTTTmkHA_COdeRTC-E1-ArscfaJ_bOxDrIMNSut9VFTidRfW2Lw3jM-9-dM8KdGnvvWoe-FK_2bU6QAHCZMol20KSKR8oVlFcH4YP0T4khDJ6JL956TsvMQJ0TNL4gs0Z9H0DUSG6ymtz32ZoSMfnIhqPvR51Zv0hg5igSdv1_yKZBQN0DJgsIJ9Ypt1sLUTM3XbacAhi5vC9yw_FH_AZ2-AqW_S9A6Al_sdTTENRNnw-DkNnSLuXXy6KXtEx0qtnYxGA.SrlIjT4RNg1g1omOWmuGFciULuz2jmjhhg-rR1O3xdA&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d10d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzYyIn0.ZGwVd63zbw0vvfV-rjl5PNcNN01DZyLgP_2Peu_qXRAmBpSadTZECOOEQSiree4TM7gMjGzT9OYCQOszyiVP3MHbqQdtWXNAxyJEHtWN_R6h40VZlSmQGEozpmkhITcb56gQLTOSFOFo7K_ZbqR7yzBi1GYIlozjoWfMCItANEPK4hVhY1RMzwShm2M-O-DyHzJS5FJOmhqCACdi6XjrTKz4A-YbYu03H2TvwPaX2NHuL1Vee1gx-9c8Ly8RRyy30CppuR0ai4haq_uGGTSyFQlygzPZLr5a-UF_KHt2ES-zluASKdDm7Z6om7PbIhoayQNhr-lQxgn3a54dac9V9pkQTQ4qA0Ez9k8YZyh8vl_94pd2ZwHDu1FyrSZS3N4UftJ8tWTod-bvfcPG8Thatz2pr9zGgBIv9UQGZL2vIaTkVdAR4lc3KSVlqVMuMjsWuIuAFguuH65bggTWsOjNg96FMVc7EKA30x5KA8zclffYKmA42cJr4A9RkddOYstBy8ZZsdLHsQ9lTrIzbUZ6Uw.BQ_3bkqETtzwn1UjFMH-GRlwJ_9hMb1lyUGTGmNF5To&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d20d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzY0In0.RCTsGQSOfkKGUtIMfYCPa5WUWUxKM0O81lXgLAuYcaA6trc6zCpSLiNTHJ3kIXhnaINx_BBxqGupIXrvxu5HjeBanqycqNE1I_3icK8R4NW8IUhS_aEANoNXHn4khCiBxPtD7ptx_11HgljVElKRuAi-CAcz8mOJFqzRUWZMF_yXJ3Yr-PgWD2pRHzt08n14yQ24yDHitdIUnejUjU6ZBtk7LSAM25R7SxVKjL5mmY2sPRgTrRdfXFlQjsW9mWIk2Wt675_Q2_x-hgCGZRkiwBL_ECuphsg13RomzytoW4kjJ7yRfNnq51FJ5Ix6XflydAw8BTAUkEGJeIW83m3EXw_NH3jYEgTejpx31i0RIoSnMeR44JXBOX8x9BAuYjTjBzjRrk-SEK3P1u5KC4bJK6alIBiRoLUmPS1bsqEZYDTRe9XxywkLrRmQVhAOYecF8gMbSShn9JsJ_Rhy7vRhLnGXRDIBHnoeDt8S8Vnfay_txGIpS5XcuqOZeVvf8N-fLlnpuxTHQJoGtGRZNM82SA.6heBhGZHL1Rtqrbp7KG784vJoG1pYY37kUKPAHi6s48&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d30d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzY2In0.w67X2Y9QBLUmgfJ0EdQ_RNyF0MmRJ9z99TjiGq8EVFYmk5y-Yira6w3GtxQlHF1Em86KOGOfOQujy1knYfHuQvwswh1TcQkOovbIBh7maVnvOwC1Vc-YiLtLsQDep2hbvWo01vX57d7QG4lKLbsFlqlBhvSvKZ8RZnC69Ex9pQSowG5YxqXiVaIvmVmC-VvtoZHIMVKFj6vRSMHJgyTMy-weQz3zY5jTOpAYwAOanwBjymmUIS4BcQvPtKpsPNYDpLtqB8HXGJs_uWZb1Dnzb96NAdxRWQSC4Aa9JJl8-iDhry32BOF0ZsyP8mGjnMz51uM41WDxBiGY9TvN3bhtt4bXMvxnvijuTc6OhlCovHFlhPf3ChiBcSyW4LZgfT53HkaTPrAgRc41EyCbef5RxdzGycK1pq7MBHbr360p_8UlzSFQ6z6nitsAB41oPXjTUFOBwL5bCsk_H46K4c69aTzNv10aYgkt4oUPNpG1I8NbrKigwPq4fPXYBoA7DF9x9NBZH6HbBM4Vf6Wwe2y6ig.jYdOjDtUcRmAq25NItYf-JWUUY2NpJi8unBCRfVjcwM&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-d40d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzY5In0.Q2TDGvbB0TqiPVuT2n2so7jX5hKIgdnH4czfg603EglWkDWFA-oQrd3kcBP3pG2-Gdq2JOYJSyQPVu1e5Dnhpe6bR0UXeX844ojFFwUhobuEPqdhj3gUPvDSWog7BCsfSIxzPaRLMUVNjdB0zRQt9ehwWlFOhksf2HQ6TtBwoPSusRhds6wlmF62NG8MdJDd70mzUjHUWALUzGtQeqINPTthE_rwoM0oDcgLd8LpIokxPWqjxMjoSfnx1n2VtW1Acqf8lW88jYKi0Kfc3NqRqTxOYIKmIh08UckWKymb0_I-Nn7bDVn7r4czYg-yJ3g_s8E-i9LdgDtJ2Jx-GFq-7KpsW1vB2IkdKKHffFqFmWohF1rCGGysHu-Z0_l6mgszFk2pVLXob5fRe8scKghvK3CGGM1ttPgSdKEnsX2UvFp6WInrk6rFhdgf7Rn-rBe09o8sW3zlqzKfM8Wg6D8veC5PPLWO0Rgia6Yn-FJY28Wrx9pJNFf7GHvJ6okduN3lP4NIVbe99pRHAC0QwNTs9Q.R0xcWdjUUznDbfZ1RNVhXcscJyfWJ2VRwxDriXYC-3k&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-0e040a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzcxIn0.kA5bP9L83ainqqocLNluOwi7NpZOSONH0OwJ_dOvK9DcSy3gAZndH5NDPX58wKgO3X-g47dp793h5RcxkiUUVNyHhbA9xmhd4lpnFBNrPSCq6fbo2ODvyO2cxgDFtTxumBPbuQMFoRyrf8JLuVBESPN4F9IDHqaGqjCMstUsyr_RHN8cvWmBwwvw-j22fPBOM_SE6PtYiKbRc7UwUSQ_TPkFa-tS_LEbnAI9LPHQs5m-mXDC0pdshMfOnuRRB0R96D3CCO1k5NyydIfGPncznVRneeQyRKxOtWVGUStU8eVP4Lgd_Hne8ZlEz8RKdj_oafPmc4f_0xD9u77skV2zv15h8OuVM9YFgwjxExYIhmSgm0a9OzPbRgDssJQsXzv6yGYCwFceDQQv9P7csoM4wOpjyUo1CNACWxyYLpzZC-VzaI6-Owx6LK4bAodMQnhS8uH6spuw8Gg19YsA8UtmE3mk8jPZbOT0IBSYCYRfP7zb8ko_hOmqR23hWUDRobjEZp4riNtrp9g4Ur1ZUP8iDA.qYbZVejtOAhWMZq3J3BPKDIMSp90fTbcpxHfx59sylM&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c1050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzc0In0.JoyDvsZza0sKdiF5WF0vFKu5ew5HvKjKqdh-A4K-DijU6-3hMLuGLtBBVzCQITmuZH0ZY1PBoRmVm5lqSjn5LQfv8C8eRNN2Z6s_jhIkcKG9vf4xcQ5Xcuny5lUD0gTDQObsemV4JMsx76-_YcrplDjN5nMQeZuvtuApel2rpxW0efmGEEQUPLgFuqcHkxX8lqccOaaLFT41GCHF48rxMv4RJjHKXI5Pu_RZFlnjGgPSVuqEsqhvX0DsOaqzafYGBlwg_DR6b6iKYhTomFLURk9G72CL0XjNi82c1GJRsgGMEjILNm5NgYUJOcume7JDc6nD--3B9FKXcYYhTOERh9mb0gUaPY8c-nGtNw0tuwbi2ej7rmbqT6FnGqeV0OTKvXwuB_7GdTHg4WAagcL_N0Hdn9PcCh67_CswhkiEC6PV9uti4ELA1FkLGgtscktdFu_KLdGJiotSxrmpxt9pR4Ykc5YVcbc0EwM87okmJkbOiDAuQvO1_FjogWPZzSiJiU_C28EOGRefuNcoWSteiQ.EBdB9XnZzAN42xohihWwYLQhuZSQc-kLU7SSOR9Df8k&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-be050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzc2In0.wghJi8KQ6qkgCgwYYeX2q7LJMVw4IuhwCWEMOuZVxz82XcFDkig3VxWvfq9R3ST9pYX1Gtcs5mZPAwYIKwwIssgSKZubDD9BcxiqubjfH5jP1943FNUXvmFdxUIfkODTF4J3PI2770JzltKdOlWW80EBzkuewrOsnZqwzLtOkKGKvbCiusD7Of7MqkEkuXVNqux5BRigKKXyYYEW95HHF0SefMOzhQu6_5Avs96IfXCBGwA2cergcKI_qpOjrPRUPpbBkxDgMRkLzaadRtZ5Vv_YzK3TLmrjX6K6axkRxeA9C9WzNb2EbeNnZMlCFLuhG4edhCGFs8n7skSAManM15Hj5_ovM7G3V_vXNmgayE5pRUXBff0vFtqq3JwYoUzRieM-hVUWGiGCl7UmVbpyd5zE-KcjZGje5jmK7omFNqMAE3XfJadw8g2xsI_xvE1_K3Nq5Uj2fqB_aErncO5Khvec6HjzqRBxWxHAhVrEgt50YdwX9mif9mIkUJ_CkqdM1aci37yDazjHV8wFGHHSdQ.C861gcVmRA9rMUvzvLZ7fFRrk-e-PUjHGfzsVLncIEQ&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c10a0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzc5In0.GhXsFW1-iOXVOtDCskZrLqhM9AhUEU_mn2h92XniON3CqBmN7wtxKuDwztjciMDzOpR08x_BnUs9dJDRqen7NlXvyELWT4XLJkNoaOaHLgl9bz5Nd0ZIVVwP8ZzP9oAZRjoUBo6r4rjPp9FPf5gxzX5uE0dEejHYFVtlpXtx_s2QV6sW7IDvyRMU8Tg5Cf63RwSnYtfWk6KFBuukkVJA-f6pGOCrypz2DH0XGqq9iWxS46ml-rRngplovAipAvrHNb_SggD5mOaDmM7A4Nqv0uR1jVjQ0aJJUjwRmuykl9c80o6WeRv3a5QPGjZIfyqCVU34_FmNf4DkJxaH9vj1dbJEPSxuFKk6NC-XOf70HnuvH6zIaHvO8PnRqTc3sKBOpMJ92SViMgee0nMDzrfB6-PXp9Xk_bhVEkRMonEGwHl0MelPQryJSDOUgWqVSQqyfziNDhWx2pXMyMCKE3qoEBqKw8YNoihW0w3gAKK6jrXIqeknjoHXX8_SfX7ZXbmUszZseZ1foVtLxubKAKBhjQ.SNqB7hZtBZ-p_kOa0cYz81gi8evlXYYNo0ljslllLWU&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-a5050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzgyIn0.3Om4ab53_uAIsx2rkTbgDT4aXs8p7_LF9L3BamdGCZqtAZX5J6SS_m6mXgOP77qSzSYSgOoGQhQzbmke4RlRXUy-5wxWJJAqNxTuDr_J865lyjyK1WVrojcGwzifRLVrgXMZKM7G81BhKhmWOeVfbDNhYbzePDnU9neM9NjJWunxFsPcv0dXuBkpBPZKSB_8BQHL54Em9krRBPxYugNBF9zPYXI2GXxVJ2SER5_4lQ8AjsUPQNGtawNw4-M1-93PRzimBeM6nQepcYFhEWp8gbxYzVqDfaYpdddhvIMnapVriu-lbEsLgtDFREN06wvvjwqGY2ZUtI6CkBfqEtC6f9JIN8uLMnW05VZrRw6_Vw5XNEImpv2TLkB3de4BldqvDJomMUD8y2eK2ix-7pCWHZ-inlA1x2rmCQ_AbWw1jYGLrz5JeuxAYBlcgd-s72lXXbPBHobECKbN52PktvrL4rF3zuuhXbmfgPQvx4elFCKkgZ6P8WkpXtY9FdqeOBZn2cqRSXl6VjuWKyCN3X6wzQ.6lvwOyie4XiqDEnr8z5BR2nkUk8-Fl_rDNubZe7GLew&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-c0050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzg0In0.MrQxA8BkjTSfBH7F397-wuJGJvjlFI4psy9v0QpIwM9rfoybVnxQ3cbHoMFSFo5M045Muaqv2PMRejc_1GB8roFjSbA5TA8SPnUV7dEklRFQVa2l1r_Zue93K_xRvmhifihD9avfEMQv3XKK0kid_6simEdiZ3JDb_DRWQS1q3ZAiuDBkLwSlM6lMf3rrUCq5GjjuCsiVX7C-Kp3EF9YuRshwai3yAznmi1ZHuGY2GIz1kjjeBj2SC2t8Z438VvbozXOX4QlsAzXTDbWqUghB1VPqTpTtf9LE-aGgnkMw3LHAJkcLtNFEyWaywy-wywD9znPaFqU0fj3AuozokLcVpD6BmuaIyzdyqhQjxQUSgL5MXk0D3ojlQAVYPJBUCSq_CNQKIjTLQw1ZOwGYrxdhXdcTS7pI7AHTj4a8xa5wHOxHgjjmlgWtGghdVgIouLiLEEJVj_ubvOilvi1j00orZ_XPJacu3L7KUzFK13y3wNZeNigR1E9NraB6S33nc6IpkBQ4HsJFrFmBSomODyl9g.JJu5cMcsO7dj9sPizeuBRfTwV3QesXWejXCifrRxkqE&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-bf050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzg2In0.egFrXFF3xFwiFCkKxV5toAFzxsncFQnb_ReGfrU9HyzwMUO-CtzdcSmoLXkXLcbJPgmHGZf9y4p1zuyBTJ9lNuNAz7oXkQ4dILjPbHJcoO-uP3AhAsI1z5NyZwiRzNReYZU6P0UsUz0oMebXzmDqiI3ypWIVxoH3mkMXp1nc5EjFjyrqNlAz9OliqP9mU3kZiwEf-5MIdcZrv4QP9FSO0e3TG2QIFgKjAR4AVtID7UK-DEM4w0-xhRvkmyyYy3OpoRqNRZWFUJeKezy8SnBpTyrUqMvOSJjnhEgJKyDYy_-P-VW6aXkD01hRycUaTRCiB_TMiaLsqe1NZ6z9vdo6i408iYVMlHTpOHclm9-UMhhi_zsatPsVWL1LhPBakowksRLxEtO4pNhcCz1o6G4C16yIlRrLmgtLzbED82sKWEUvScU3vJ5JrJ8T0urxNfipQg1L0Dcopee_xFd60scnWDbyVFnwXZlN_BetkaZYs_htvzfoTwuenxtL_D8SivqXB8GR0bYdL6WZfr1v4XEzNQ.wxHJ_OxqPs2DO-VQvhbLloFc0B2Kha_r0EHMGzlR5rs&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-4a070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzg4In0.-wUZNfIbS9jZ87upNTXX8I4sJd7RApdlJgliYU8AxZTKEKTyL8X_eQIiwxu_h9gsl_aoa8ekZBRCVnFxmFpbKoyVv4foWvH_PY1BoFCQYTbD6GRa7-PodXKZ7nvYcFO02FVOyuEji-6kDIFK4MQ1QZbFAczcerazOPbACGYOylwYg2gjPkQyEWIlUlWSBA3AdozQyyY2-V8-AI6MZ7_4RgA6M4O81cBMFUjE3zwFC7g2a6tITjYzauNCMS0jgwHM_6C3qjpikREsF7FqWRwNwHYeEffLXxdU-gyZfDimygglL9aPEnRCttQC0OhRtk-wSQBNu7_evk5RzRvCsalyyB8Ijr5bgoa47U_lCsNoDqv58R6uDdtDBRCpkKgb-E96N2v9WUw2CjGsnPGVooo8cBQK7yt0s8xQ29zVJCBu8S3ZRyTLbl97hTV6YkSNBeNaYw4YkOqovJwyQEMGuw_3-v2bGnJ4ZBXW-22PFh00X4LEno_eOwOvg6nWiKz_6l4wQYBi6FmYKKsnZRXMegoJyw.TlrJS5TNSMWpN5Iik--WE206K1admyoaPJqctBYUhVI&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-49070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzkxIn0.G_pkCoKfxmlDDim9XnBn6HvKEstRYZObE-GZE30dlwcErkq3tVYnSekoKsuAfeiT3UEu6fSgfE9vjqB8UILrY3iEjTdmE_rnhcXEOzpP5_O99u5grBJvHJM-ua_WSth4v6FR7owqg_iMcvckO7yXiX-Hp429aDOHv7o__oB3JSNhJl_VPViYyEutXASML-6QbBUAN9qGoyrs3MiqAoprEhwxpsI-Btl2XpE6A1acbD6ieCkIFsq9iHKB8g8HGjuoWYIOQgVe_7FtUEqfQequKHTyWzzqq0i2J_VHZCe9Z81e5LiXatPXiSCidvSVYOXFGYTf3XMb2AQXtU7Uhy1fPNo8WkTJotcjXyY7LcD1LXchqHMEZQh0_ukxnVCVITdb7vQTEXmvJ9F_7ob2oTsSiYXmBxxeEqagikk6pT_38njsYHfOQGNPWt9VNNv_UmZ1Rf4aHCNWMQcRA36PqNCtRUembkS1BJG-g_T3lTYwBDpHdw-Q2rxmp44ZhOpQLd1fk3_68Pu9v8KXqCFnmNC_cA.3yFGyhmn1e-HCjofl0wo3IbLODNU3-x9hvcn7Ct31VI&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-4b070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzk0In0.ezW_PRjTIFeiPJErOaU5Wvw6DIxBlhSeVeZey4VsCM7diExGgMBf_L70cEAsy_YwdZDIuihGItReyXxxmwScXmUtxkD3CDfKECv1oES7yEtN8dgQXkTtFD2UPpF-dzUzx1DF0iUTsdC9ckHvhBxRLLQc03vkIcmsSE_WWWYZdozPeo7ifYc9YoTaGtysPV7vUnVUGRP06hhDJfjGfnArlxxMCfrj2BygvnQmcEtsAuRI1pZhPzNmZ2kjkYMm4Q4f29lA-su08iRnCHlkXYSKgcY59_Toekzy3z2L8o1O-MYRKNAP3ihpkSzI0-oGLMRddEbfBCbeDkuwPXsKi6dOUyargR86wepxXPPPpq6fNsQ2OjIsXS-ywLJtpgxVy7S0fDYMUIfqH-NvhvCJiWnR6ID6QHw29tMucH5eEUM5sueS_wtFW9x2KIeJNLz20LGOK9W0uPpeg4C5Q3G5WUsXLtg6pKFcQyg12BJulofBmh2qkMaHc_jpGhgg0PWFgyOxSqPfYHfg-blfKhUJFBx_EQ.Mg9-8c6xZ0OTKEZJogB0gP3gAQPnREuWTGfEShw171k&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-4c070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzk2In0.S3raCemZ0t2KDCSbrm21DTbu7UjGrm_nBW5tt3Rm6vP64Id6PygHD8zd62XlucPVCXPsywyKDd2j8dFMGsjlHb32VPTY0fsddrdpFT4j-DLQOOwT4AXRwYuwQPKMhu21qm40PMn2bcP_mg3TOS2TjlBqwRsxAe52lTjrTE1wHwxM7q58nP8-lKblq3YWVTiDv1GEkwR7k_shFxir1gXqyqZFqbYjnDIx2HyV9dlg9px43CD9QJEAEAmhfiY5dkeU-6uIMCD_-Gp4SoDKhyenA2WmwmJUuPF6l_y2MRFTrpiKpncDsUXul99-fBgakHX270WzG8yPnW_2QAEYpL9wKsPIzOpo3xVmRfm8YoqoupXvJJmf2Ndw2UnxR5TLPrQJ3nMezbeHlGTtWtoXoOvOwH6HuJdarMZnWKcb01JhZYTShF08nlr1wvxxLxXRrdm82BsJ9JG1dA6kRAepxqzRCNOAwerG1Yyuu1C4K5d_SUsXCZfns_P6yt16rv1uquLj9z4gIh9dcjC3Pj5-Q5zoIw.dyIyAA8OJyZZiBprwC1V2sqoAd73Zsbe6SUxgMYxg9s&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-db050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxNzk5In0.VI_EeS9IBF5hnDNgc3CcaO3fC0UJ7KRWxBoK3e65_3Jk9U2WGwh9kbLnXCJ8KSNt0mfJSTeJWVe0A5i1T7xPIHHwo87zLELVFA7RcKhRcNvQuEvnFHSL3nSRxdQuHgP7muZhgLf6-OuRf8baJwC7oF3UvXpejzyHY2EbQj8DPH9HRpmRHK_9eydN6f2ZEQIIYZqAO3Cxwwb0wgTneNovbachlrq5OQfxxrz8aY8xzFMeoX89GjukX3tf7nKjOZqcDSETSy1_lb4VbX6IFvuqknKGYu-PVvaoGuvbnVtVdhC2AM8tP4BZik_5kl4-gXh7njRJmzN4DIXztnDnICdYXjMkgdj1GRiStpW_16jPKIKfhh22PjnFmjOAb7NEqP2YgVVYgmK2uZouScAL4orhXBEIV_lcK95AmKCjP-yb5ha0nYlbctpz0jPUZu8Rq9Ws3yPvC0LmgNpWv_gBY0GdpELtPavE93qApRUepy3ssKcXAE3jCNldbPedjTH7uzp3O7-UjNJwBqWrF0SuXskfvw.IB04KFjZJb1oj9cAe4iV__CeslLGjswecIIF_W2VJY8&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-dc050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODAxIn0.mZumLh6iiNLy6yM6rdCSEnVRv1-1DmT_Wdf2AuIXr2V5Gv3AEl62nlovtHeDnGr5WU9emHPJuT_61kbtLkCIMOT_WrklTKSf2heY8Lw_pei669pCXOkEhsFxBQ6IUlgYSgwoQXNmtruGeyQW_0eEecZVEGuOvKe5N7q6Uf8lBReEGUg7Ipwi8fP8en86OOZlbzNivK7FKzWo3LFzGQw8YwLp0BuFUj4Fy3mpqDa-jUjtQHJWHoHUlK9el1lVCMYlrJ607Kd7D6mwa0dPo36kKLMcsvzd-ti_EzwleRY5bTWWgt6YIpfyIkq_LAPeCrVngQ8mTfHwl537p0reaTcyKL79G9V2An-oOyIMWBv1UEv1L_oAXtqnbJMRNnqoz747U0glHiDDYIRogybqakAS1ku5YcLgZ5fFmAzBvgh4r9vuKSLOrx_2NlmrLjxofpaSRFQyCBQ2oVEi8nhhMFvDHc6LzwfavkmY7I84aWh2dMjhPOdcIQMP9BbYH-p_A8rO-M5its6PXJqAWYe2i3m_Xw.1IluleC8apEt1AP9mPWB3GXbJ4FjqiXZmg8P3tjESc0&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-de050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODAzIn0.7BRt7i5R5255cYjEUxLlCF9Xwpptx3DMJ6LzuFQ7ZYIHktiryx29XJ5fOnm1WKiiyIuaCyDX9DrRRr_RWB5cjIcdaZSUL1Kubta-yp1VhsjgCWazLiXdlQlkxEjQSblBz4EMswZl2qaonOg-yLXBcDT3EfE9j35o4vzgbQS6SVYydYEnnnlBL4FcLbJWYGNSY_UbT8fOvhaZf0H_jpHJzcx7DSJ07Y9E-p0FW20CoojTDs2ex53Aj0-8ySZlW2YbRaMhYWudEatb43O5ieIh06eVcP4oA_Csd2PpViRZvw_h-SHOr5NhzOul_VYIXdyWys2lNJ_P3ogX5yQlWmeAHdO1bi3XUj1aQq7gHH6sGyz0R8jCN3clLRIPyMh4Jrxn6YJnXjdhmAr18GzskMNuAeDnFRKKWmXB3u5-zPw3vR0XvGF7CYD3hsbNyIQYOUJ-rAr1PXeK4lc9Dufp63ENWqt3gdBO2dB53qaMPAJ9SsxKfkVsq42--FKOVYvrBM-w-mTSlZ5wi_DwfTxnc1qvWg.SBArBP8pAUS97qERcpsygr3T2EHl_rhh9oB5KqHM0hQ&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-dd050a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODA2In0.cYxRktaWnXy-OFsGdTnBI4ljBfmkAsW4UQWG6kWkLhVluBXZoK_4KjuEzhDi5ON1GjX6lgIdNcYQ-kwEOnD6Da_4pk6hP368Nlo6Idv_YzHTVd1X6sVuaP5-XymlpMI5sYKUdxcA4QVad88IASmCRIuN_EQARRzVMCfgyod73o3q0ASN8YkQ-uXgyeZJWqGdMq6NqeC4NEbvHh_j3rhU-8_LjJMNINhQIULGw-IuCAygQysalacIgE95X50x7DGmBaLMifk5OVxDW32VqmpErd_vepdjDOZwfWpA_698aTVOTy_Oo9iCwAC8HX4PHH-vJNCIwGnKEsOEOMlALTQFKtqrft9Gh6HF2GvvWDpsBTQQflQBPUcCRdEo6T8iyaQIy7b6Mk3Jo86hxwrMHIjpS-LrrTGxpym3y0b0JBujaWTHAhI8_AdHvxXVSnb37eg91Ur1dxn3HEXwYcJQ-xTlTnkWztABAZd1l3Cpmj47aTTqaTTSFSrxFcEx2MGYs16oH2M1Zu0YMf21Ea7XCaEzaA.yyUKp63L9sop6druwgVLkQoAFtRUbU1VceQ5ar1YTeQ&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-ca0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODA4In0.u6BQl2_i0UazlEm-vsbBmDH9HYpfiiGEXVWtKNKtURCQYNP93ucCdCN62XnDXY0UITUq54Rvj7NFHyx3-NGgUUTaVaNlMZEF_g6R334H8kfF2z0MzPA4038qWb4IUWT4ueKzr1_iGI-IC8ZGCPwopOxbfyg2u9WjNA8wmJfowOJZMHIiiTOLWZphCsmpIhYbDU3MCPsvMZyn3OQAKXID3JdUHA9jPpsPL8tavSZ4J_pu6c8SB3OWaH2yHxtFpBMLqO6DdgWeFcYNiczC6WtD0mYtssY5HBWJZFgldlvL8xPR2dHT8NfOAwbyd2hY-h8JONn44dGA8gYsXs4Kzs7mCyKh4_G8tGxdBGOamV6qRxUdxcCdjfQG7R4Uq7Vs8tU8YnVbHo0S6XVuzjnubFBnBnjR8bcX_wcG1qKkjHV6pG6KXTODdpqHoDkSUFtUQnM3MU6v9CybfqUcAB8shLkILIkz91sn9fQ_XXETh1m_KaTeX-PgeYWHTB7ACb9A2_BoimqulwS9aitobz4QUmnDOw.g-p0xYSzYKLmabC2ooUuttn1Hu-cauGa_CrRhkWYzE8&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-4a060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODExIn0.xEoR67qywKGleR9UEj-VZzUf3OoBbt8ewF3EwZjhpV3va5hAkrddz0rRSRwqNilNysVJkAaSC7VjL2k1Emypfrjx5oUnQQzQ61W770rAq2tslbm7U0fketQrezpZeWqq5s0W-2XgPX1WYFgEhWmeGmMMAxHbz3un3FbhEqmCnViIm5g0lIIH3ZG8gRiaf2YWDSED8hgrCPgB4wBkmn9deNunt0RTzTz2Kn6vXq1P9nPog1Sq9G2kf5WO3s6rYfQ79jgjTTUM7V6iuJx3RkpDIR4hYo8zT9n2SmhfFXZTSayKj3qBP9uK1OZNR2bG1ebSjNl9axWYhNduA22nhBdFeDg2hHAryvr-gE0pSvCuTT7e4oj1kYbjH74XBxmL-fZ83xUya-fGwLXXayCx-B8TYnHeMOZ8zwmbhoZRQUwMC2UlX-Fpcpb-hIjovUm8KzawmRJTQvumEorhtLu7F_cVq92EUYPScSvbdcCb1AotpK4t9s_lA_PKI6ofHxIjPlRRIWdYMP-ThfBjV9nfmzqupQ.U35wbSkVtC4DdMFtZtOjoKDaEDNA51XRyrPkDJaahgc&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-4b060a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODEzIn0.jx9D8TjQ4OXHQrsWEUzpjv6uqFx2kBM4Wwdc7MYJCFq6Sc1ql5dpTV9asMBn94Ftsh0Xu_8QttvB3DAv7boplJ2416Jv0akW49uhDBZy-Yadut3_gSIcCjLtJoqWaP5dbsalUoV90zmF3REzkkFRCRgY4nEWHiUaeXmxaruQdSSfKvpJcXVgh37pW1MHs-xbjl0zeN6zUbcc1BC01DVLUlIr-51sSSTXtzswusuNkPJQ9-IpzqWPNJbaialq3Nw2r205bLKVUfgI3HOgYLq_kD73vYDMcaNA76qe_-sWTyyDXzX7928oQxX7K_UiDR5btQD0VTg0IvxMRC31Eebx1Twfb86y6ebl9b7X-CskG_on70OXuLTcE9CyShZp-23oIPbGPOq7bIjCp5cD2riOIjGCiRvyIOX0GqD2ZAVEcK-IAS3cZvRsKe3Z6wTaqm82GN5QGllug8crcDiUKHSblfHrV2230YqpU7A6P80UAWJBMj-kcajQztPHbaBBCNWxuTlh5vZY-_ywDtKkHzrfew.uFhFalqF25Kbt-17uwOIGt5C7PRjCjNiVGYAwbx3FIM&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-41070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODE2In0.KKkoiKVV5qXxssaD3x-0cXw-YZHasb8mq31li5-3TaTTpgFhqdASpygl-sHwik811j36o8TELCMJxUAs0fdpxkIx0KS3HfI4CsPfhMyj3x8t5Jff-G_5Igpqk3Aug0Ks7yDWmg_HM9Dfkk2aCrcUHdDT1uTg0oXDMxSGL7xlgDcr01EuR5Tw9ElqQ2sN-VFdXeCy5VVLwwQ-96EKRkYxqlFo5zH29I8JfLFvsNkDMt2KZbwjrN8BfbVRzo47ldnJpIW2qivKYSATCbUFomM26OnYYsfY45U6IHto_W2W1xEK2Hwtvx2ptRoTV6qfYYx2rx35LVDiSlRnPt_rtKmJ9z-huKdf0nuL0HGP5GxwsDYTxzBQ4bOHlslq-5Q3fA2tgUo2lIa_acrNW6I8S27Uu8UGQlpYPBBFo9zk6BokqeNuKm3sKxB0lmspNaCMyjYvsZzXINAyePXtcuhF7PzDYdX0hW8wINFa_CJLfdIKZrDds16PP7KBYyUMEWRQV_gQwH6xyXeuKhdTkojyjQSpag.m8Fe0jpO1wjmQFHTWHhCcCzpBfPAq6IcneobtOa2_sU&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-42070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODE5In0.TUGPdgun72hWG42SRAXlh7pIdDOq5u4Q6_1hCrOxaMFhWbrM_Vq_ypTo08FezNWg3eXLBZrvxpJ7wvMg01s5v7Zw5Q_fet_zcTThrL9PLfSFZ-1p1xpfu_u6QVFh7BWGkhZsjqoghTQUF-BDAaND2kpOgmxPQSLB4dxHQhMKzTsRZOYnYMJRX_xiLzhFUwXA9W4IPaIpDwMR9jifwUWybGChF30im5HpVLg0DCwQ5ALNdV2cayM6ziK9aaQnsvGRcS78YM_OqlW1pz9Vq4qfEofiI2n1Mq0mAy_2Fs_kTayThGyYm6Y2gvP6doPNV52cfrI8TkqdxO_Lai-dLHz0ydK5GAhOzXCuwZGTsGgIyog_iohi6Yj0hPAoLz4ZuzDK6Llxza5a8O_7S6hqYFH7LlzWH5sMn6M321RcEAIxE54zzSgWeGJLeuvv7dHEB3-6RrvbFxJadYYYc0yb69pLW2jTX18EZbxAsqSV_sr9z9j4GtdfgCbCAUZW9dGGr5S9wOya-BnWXhlqmOvdluZ38Q.02gsUzrc-IpBBc3X8qSj7toXRnDqVpsRUnIlFhqTi3c&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-45070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODIxIn0.9NOykQ8QBafzO__WQLl0kHzwigHl4m7gevcP16puVkZVOWTDTfn5zUpATr_UV3q-JrhJfkZsO79BMDEJ-6aWIMgBwGv9y5HZv4N6Uev3qkJi9rcg7-g4kokcoNsp-4zWaI5whchM5ly4CenDy0iFre7AWqid6whKrvNZoueylgfNfy9OVzUXe3Xyo2UnxBI90fUvmA_IyzqcWBIrxWqX3acuPLqvQI4xkhaT0HX4rTDsoSms1gE2-w6tlyK_yHOm16GoIVMehzDwTZQo_jXtQkz751hC4bWQY0ZhKjaZ2uIZeBJ4CtsIkUjEdo65Z3jrMSGDdRduzPLr5e0ucON24iMgM39yhzsPkx3-0q9GJ4QhXx3eRaz1nvvnVkaBVkFGJMVIIvDnOPLbtUt2WugkbXL4Fw3F2LXFOO5HRdJNeftXeBnrPzQaFbxhoqbN7AdSilvkDeGPhfEUbEgxdPibCqpXgJnXh4XH4365jyc6SNKKQyS1oaQWfHBkV8yZD4eUuq489JWbh-3ifebXl0M7fQ.hX2yWy7qloXrawSh8b862u10HOpUDVKdIpPk7MHY8wc&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-44070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODIzIn0.4RqlmsOT1UG-L-eoBhBGg9YozNdhTE4PeEzHJSm9LtbVqsgBJlQ9xrPWEQDq83psiN3ndBBrILOVXh0b7H1fxnd-fO2gD9XbOaX2HEjkAa518AFYte6jPOWCVF6uIiDobsc_Tc7fsl7JOvPn47HfOhYRfvMdJtg6xXjdKcMfqHwIQXpymE8doND7gIsjyX6Wk99rXokVCuUJk0NyWinkIe2UtVJrixMKKceDllXEPUmdajMWB5XJufOnUlcK597_PXj1ILEIRD1hKSo-jNY81WOVojqUbD1tfZvZ30Ie-aCndbmvQANindi1AXrmDFqFZ166hbrwQnZRY9gxnVKG9Svro96AnQ1iVHM8G3WTndEda3WUAu5fqes8ieLIayBoZSPfVQTMa-w1re4ndxJHlO3n5w-DLhs0C1pP98hnJK0HwLKgL81fEZNmp05odrKBEWzzLIwgZAMzfA8z4mhJN-c6l6EqQxPn2t5UbtkvqKlkm6cZ1eHb_Tl_p3RciIlutU3swl2yrm2AdGqacf8zUQ.vWGxFqGQWqCfwobnb91eW8t6UxHpZ92w6DDb5l0IOKc&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-690d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODI2In0.oBvnekAT6YWN7tMcyGii1dg5xlLlesLNqXdjKKl2gWSxOfG7WpmxxbUt08ST3rwKFw4wzD_qvB83jCeCNCIh3DeaUgrMeP6cy6dmzOccwnGucFPrcg2BnRKfUynVE8fyCM8eEO7WcnZrNW5LmKVtsBtBf6qY1iqrv1ejXAUgdaTIPTTK-wrxWYlUZKs8NTEKn8jRWawEVx9TBS12T-vdYZV6lq0XXyQ6Y8H1dRF93iPhG7kZKFLjBxce00wbtzf_qGo2efaaJpFFKIEL7NpOzd3UkYCDCargzE_1VYzRlWA1Cc8FzA_3w_z3nyrP_SQLFvo2Bh3NJwtQJzkiAZ2iDTp1hvKqModsBaPeBKI7Rf1pZ28sWGtL4hIKDDgMLef9PyMAbbht9_8v3wmVwWjJw0dQ_BAGeg5HOMF1alyiDQJmx5X9Mq7w9paMuWtE8uFlzRC--GluNSWZwyZzis-sSzW2--KmaXHWPkRkVhl9fOHgYRV_6-RfCWkJKaEyvhkrQdRCQ5UuwoTSY7VoGom-Ww.KyxK2REuLAlp600ODegW-9BorpfTvMHSb4vrOqMzBbs&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-46070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODI4In0.c47t1xX5Hh4GO8ADDJUtB-1X2KQEFHmS4xM_I4kchkHFM0h99UkcfSQmzGHvPmUjVquPAE8EvVIqL-ZqAk9_26z5sc-nsF7vke3wbEuC55He7Kt6rCcAD9hDk5vQ1NxY77HCQhYkATivdd6wa1iWeaa1dwrOqrj9uGLa8E-zF9DTOa1c3sr9B5CWLybQrSBqoheFg9CfjCs8X7IgeCKYBd9uoSZYj7rxv8BaG4M86ciBUdncFTBMHvYO7dja_W1MWybNjBDlFltjxTsLca3P8V_n04-PslBTLymPkVlYBUkXz0sSP18heE1S_V2-hjdw0bSr1MfzcpmW3EiThX0oUVkRXXTmohhCFR3EkuALhcZkokZbuYpF5NXj2Zwc39V8GWRsQFqbnNFn-XfyXZL2iV_2Vk73HH2DbMwZ8NWVLcogk-PyriS6n-VjwaiyMkqx1pD5puc2KDaFHSkbvztb8QswkCyl0r01bmXhmINXofflhaoQuJCKVWPasvuKXZ1ay5ViZP-eqX9rW4oi-tHDwA.M_SZX3xc2ozlVklEjc-LkEvhFXU-_P3VeGL00P1pxhw&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-47070a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODMwIn0.eMc3R_aEsnBwIL8RtMBBm7eKMSzYuw_44RoNemY7PsuKsIOP3RxgOtwFwpAE_vx3iplQ_ZzLd03adXgkTdqpm5JqAkcsRtapwT_hzXDG4mMMaBS2L542ZosldKrdY8wd4IT2OZ_w5dwmio8N9jCtGa63yVDEyQsrZzyw3_0wq0elbpJyRxcolhe7kcanfmFfiery3HamZYfP0Hh5CfE0AwLpsib1LcBBHnfpTCSHB5ObM74pZ9Z6i238pTgpCee_lg175bABUwkVfe3FvoujjeRmXaNqZ71_Sfh_DyR3NpVfDmPkoPZ9GVmobhi7Cvsj54-EAbecqODOzsu0qGLeqA1BRhP9PcTZlB5x-z5OJPU0D8nd7rfrfkVp3i4qepfAAHzJQ8HBTeF8fqInKBgQp63OHqUbwod7v70hV1QHS2hK_fZ2RRqKkX7xNzyeitj2b3100NSe2TwBgZ_haDwLwsrB8IWQoaWUbUQFUZyhauE4z1waqeerIIfZPGw1_Cjdjb1AddS0zUyllFQm8DGKHw.ueqQonEfTb-jYZw1r8Qqi9fQVNVW5nhQTbyaij1gxac&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-680d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODMyIn0.QBEGAgf3C_sheUO9SWvv22B2lzLKWUHTa2bAOFRrgcgDY9A3qPAaxCnVOKa9BiYTC3-UWJTkw2NlFsJg5vjFzZVoVqf2sok8gkO9YekejWLcfvv_TwXTo-gReK310E5zlkdUNr67fAcLzHZRufJjbXHfpKnbLVInFSsogdTHRRQj5ZSi8-_nPydSAEFdrvNuBUmhhdSNRwtKhyoE-o2NK6RZh77-U9oi-kAJyYurlgZe2uqolhg-yI3jPEqccmssl8hDpzXgB-MqyNXms5-K1hjRxCOYeEUZGAMyiSlFybjyL1fjthNBZmqyCzDkGSHiFoPsMw4j-z7ypEgFRZTV6YBCvgtJ8v_E932vVxCy_I9VWw9M24cR1JOkvCKrhKz9fkdpMmf72r4szeKJqfxaYbk0F49vD9UeK388zM-GXGMD1bpp2QmbvkJ7iWQCGcRD0Ze3n3OiEpYGUPvynYx1vNP0Yv-zflaR3sfzknynlEJgbEWjJAcpKwAefTdf6rJU3oqczOacbwPKU5W_ONDCmA.9F6CCdjlTBKcinXhZxzcv6-l7HBPxGQO3UsQ2r6SUlI&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-6c0d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODM0In0.E7-SRXdJ9hvYR8YP0jB2rq6Ggdeo3ftUYLemkKsrb5luEK7pUNX4BAe6guzCEG_aB0Rw_1vyCXRCc0BQ5oigPitHDlPm5ZWryBb-KTB5HbXhAVjChkqi040kIqOqbhRpmyf0iTt-tXli2Ndm5o27S6_XRkj8fxpWi5WsLURjPYNVTMzF_15urpWjzqa35kd_D7NYB2mCEmphbjo4oBCgD4Ydl6Rot3IZ8kZo938aJRlpWO3Bfe122d9MynF0GWr7t-NIdQOjiO7SfzdICDKmL1mtBtSZoFVEpuRYDOgvVPor9dXwAoe8W0pnGYv56zHn7_Z9QOKtWEUvJfeTsaoHJMoToNSfpCKqySaTLfsXtsByp0OQwUoape_c6P2Nrscs4dqE_dBsx5oK_oV6o4J5q4JxYDmGNn-2aDK18eeHWkmAlkUsiJTqT77SQrIAba8_Uq0m_Szx1JA2CANDHMF0n8vb-zRFnJD27j9ylUnWBMnlNheIYeyMunpSGBjWNfx0uLV_qZk3qyAw0qJ0otDA6A.ydhmZDdsS46sPg5gYsL82OIQvWBwr2dwE-wQ0X6SJrs&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-640d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODM3In0.PuYu1Q_IGiSlrlH1bgd3r6CRpQXvFB9YkkurTkxC0Wtm5yGpO5MEKrCrnaP0Drw-FcvM94GNLegmIDX91HglIUvRBmkKHZTDnJ6Qe4ySaBAQle-Qq9OqF6tcJsrx_BNEA5eshXeL6EEnDrNgd9FH9DBt2lmWULSxdZNeZsuvl8YXQa6_tv1atc1P0-YnAHdAlabmTqW3UeR-QomvRDwNN-qrP3i4ajxrmh9WDRHQzLRMxOAHnV4RJ3BAIyf6Vg04szKFTXWpGEhFpnOhhtRUOMe5TXfTN1m3xpav1Rl3n1G_q12v1hD4ns1P0Nttc3BPuwo0_ENIHgmEgyKiHtcy1SawQnycTkrS_sOoJppq-nhxeYoPBEh4bYQvRvVgyiIcH8aDE-xUkMJEA_vmSd4_1BLJeEQPIi2DSWhR8yzebTFo_8n4UEbxaIkUJTCzIKbj67s5TW8Ik7gl3lTLn0kxgesFzMxJsDSfdZ7bdtS5NnSBWil94S37osLNYuSHCBZBMVfoZagH1BJ0rfVArAxaPA.YiLQxCMgvB_mUHqQIQ3OZ1D9Ny1Aad4FhYArWSk1juQ&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-620d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODM5In0.FNAe_oMgjXxeYCqs2_HPeG3nzKeyCMl_Z3uIvkUlTq8Kzp0OBZp_357qfZlGpSM8tHZj6ps9BIPJA6SiWZ9OzU9YB9dPfIZShMTp0zm0dbf6D-Wprj4y1CASy1xUq4-HmfddkpLAH_bDxDJD5HVwWlzrBkFmFRWYQnvjU-LPQqw0Xgii1hc42fUGWgsvZ6rDBysZo5_1X6qxiBhXg99xklFRSsYHe9G1MdK-Asi5Tsh4GkOii0N57fgehpvfWn9TNyaUNKG0RMtCT9LqPFlKlFrsTmgLiFA7XxhzfhXjY4J9UN7MmhqlHXKHSDd_jyrn78J-VXP3WrPsmOWJCwdCLboS-UOOTNd9vCl0QBY8ryFXsS9U-l6qTwrhjbQ9sovItHH8jCzVTouyit9fq-HaLi72VqW6pzm_hoMWMXLc_A0MOFyzJpblIc-W5417B9tD6cOKl2E2mtrAoYKY3Dzr9jCY4cEeO1Ert0RCxW42geB1gVdohIcq7dG9RUVybFF8vsKixY0YsHUoPlynLiixjg.WA02sbIlY1QddZB84mEv14vRiJwIvC2cXagwXq__YDM&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-670d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODQxIn0.WyA4xAiVzyhFkcdzAqWNdyTgCpu2KOnyH9rlg1Xuqz1BHCuFmy3DrnkVGggsIfuLDolwAwbUgkWej6bpILU5mEXVhEuxuBPAx8q7WCGFk0q6CoTgOlV-YZ4Wz4jRPRHJ0Xd8kJbCyMJwi3ZkliE3O19upXbUbsAPS0GJUjOzOJz3EfwhWOwyaa2EceUYfjHE-YGetJ4as-ST9J88fc7nbWC1cMVvG_ZvbfEwA37t05UGrSRKxMNrakmSBJ401DIMgAz3LVEq8tzyow1rUNP65ZB32unrOFeFWsmO_PJq03FREhNFwN4VRljwxttB_9u75cvYbOVrYw5NGWQ86ZS8Z661Wl0t77-OMpXtVGFkEJb8dcTFWdeAddymEMKP2hzYHvOkKXNTIPz9kbfnecBNNmg_iOs326sLqq08T7G2yUos3NJ_XIMIqLhbK8va0dR7eJ5Yubh5lJJCdF85KmC_0wt6tOkk6Jto2vSOJV3g0k-A6dYFhvIhoGNBPbc1tvEY4LJqRz_5RMEV-9JoygvRJg.2MD-GazTXjojeUYlU25czQ3EENRdThkiXr-FeqWThH8&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-660d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODQ0In0.pwyp0hmTzVNcw44jeXyl0F-_gx445l1WJ31pWpPSrX6z_qud2j58ED7-e-MsEZaj0gPGd82L1nKWtjaXLitEendds7WhVrX1F_LrlL2Y6T11H_J9S_NXl0aYV7LvrZ1ZH1-q-LBE-gXsX_QcDVv6uueYkhPV5XOOfD9Z3AXcIGX7jcN33XHOlULLOR7yUckPveiSOfzTCzlS5bf-yZ3KVhiQj4gBZJz1G5HfmDAlLeifdq7Yhqzxl3nTXeFUBuesJzmOang-Li2uQtLv-Y91vnlbfaSv1APy3rmnu1fnKL6V4H4PxehbUD6Q2vmz6Fqb75ZyS61AqTUoMnDmkXS22bA6kjGUKX5LqMz83Kwb5wl_Pby8zFvJbolWo6NahYbaUKxWnnS8fuwu-gPblg6DMeP92SM9Ct90h2ybuOkHX2CiXDYnoUixwl1TOSnR3rnUJa82olw_OzxW7ul8yxy6i2T8TevAOoH4XNJZPcbkk_YwXfqYb_LVcDfi-m2odqJ4BA8Bbh3ZDVKCBunmOdtnPQ.deu6l807c7m94rvvJse3g39qAdiJKixnpexssPvyqFw&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-630d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODQ2In0.mha6eugHfRvlHqBhGQudMgLeTxQqXfF_Ezc4VksIc3d5RBMDA-x3SROg9-0S_dhxFDPtzWvssTY_taJyVsc2gElTCQ-BZvwaj1Het9O8OkYgQS3HU2XZaGvEB7bBbgtdZdmqXkPVPIBiJTv4EQc3R7SuzuRdVwCvRyT02i6PKrgxrkByjP3fspIUguxUSyY5k-Gm2JoSa9kTzD9ulYl2wiG0e7YotHt3hl6f33hENcQMcTYvTEFhmB9cdQ4HL8b4KHah1WbTkc93aZhOi5X3VwNFTeMtbYDopJ8RIUshfWeYxZ68OQ64Hk7I4e94JHdIYkZiHxpvzpNscMYe5kbvl1fcqxxx0IXVv6G2Fu_RvIFYc5fXGu2PQiVx8rkeJs0JohjIbqTyw8PNwhS40uyUDWerlAGj0yvOGisuXE9qyF61ZGufQG390OVS5nK04Rz-pEat-nLYZhaALTPU4EkZnnSfnG-ttQz0au_nqOqXDrC0c_bk8sKOR3UDjBADgSO0FQ7SIcwrskDgGhyZ5wMY_A.GVWW0cJLnsTv33OLEVe4sJ8bZCG_65LGxW9bTqwd9BI&amp;ApiVersion=2.0</t>
+  </si>
+  <si>
+    <t>https://my.microsoftpersonalcontent.com/personal/91277b806043e344/_layouts/15/download.aspx?UniqueId=6043e344-7b80-2027-8091-650d0a000000&amp;Translate=false&amp;tempauth=v1e.eyJzaXRlaWQiOiIyYzNlM2Y4Ny1kNjUzLTRlN2YtODA3MS05MjViZDJmNjcwMTMiLCJhdWQiOiIwMDAwMDAwMy0wMDAwLTBmZjEtY2UwMC0wMDAwMDAwMDAwMDAvbXkubWljcm9zb2Z0cGVyc29uYWxjb250ZW50LmNvbUA5MTg4MDQwZC02YzY3LTRjNWItYjExMi0zNmEzMDRiNjZkYWQiLCJleHAiOiIxNzQ5NjYxODQ4In0.sNnr4ozFV_heY_GzZXayzJNPAPq_N0hX0hdWoU0mQiLlmVQfW-dF8IZPVw21aBU2NYmZKwBJOwlxfVKe7hsMAfiDRLYPlxLX_5YGTrEhomaYT0cWUu9fOh8w4Xu7B4rje3vkCFyTv-ulbatbGa47jcJaZWqGHuHp2FKKIHkrjchrSJXiv18C2SysyNiUIbeVltiyXtUjuq66qDWrNR_lwea9W-5MZKZOGsyJDul4G77hY93gHvt-gHPwS_6rSnWWtrgj6lcaiSHLM9CheCgoReAS0H-u5XjiK8TID1tOCgtK6Ti-DJzLEbWaoAj-COCe1BOwFzlAt_Pndlm_mvT7CKfiCRjwzngM2MnZn4IICSMeV0P4psrfWTfHRXFJ5T-v_mSNOm5hKHBKsw1opR_fM1oLGrWm97zOjpMLhyrzJ_aiaO_zFwz81nwYSKmoZy3k1_ge9eB6mLkOmHP0nFxwvIR2N8AOUr4yVt4aWnwaglMUoxE5lKoUbOCO6KpztoAnUmyWMQhRkSvA1Y6J5Mr-iw.JZ3iRQG_JSs1743um_68FVvFViJuzxtML4YQwz9Cdlg&amp;ApiVersion=2.0</t>
   </si>
   <si>
     <t>https://1drv.ms/u/c/91277b806043e344/IQRE40NggHsnIICRCAUKAAAAAZNbH628P76s0OexbhJ30kQ</t>
@@ -1013,9 +1013,6 @@
   </si>
   <si>
     <t>https://1drv.ms/u/c/91277b806043e344/IQRE40NggHsnIICR1QUKAAAAAeXZZGT5-JBRvsPfmejwC-4</t>
-  </si>
-  <si>
-    <t>https://1drv.ms/u/c/91277b806043e344/IQRE40NggHsnIICR1AUKAAAAAQ2lh7w5vpurz8uYvVv2x-0</t>
   </si>
   <si>
     <t>https://1drv.ms/u/c/91277b806043e344/IQRE40NggHsnIICRegQKAAAAAdYtHPD-A4tFSZVuahRmG4U</t>
@@ -2341,16 +2338,16 @@
         <v>274</v>
       </c>
       <c r="G2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="J2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -2394,16 +2391,16 @@
         <v>275</v>
       </c>
       <c r="G3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -2447,16 +2444,16 @@
         <v>276</v>
       </c>
       <c r="G4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -2503,16 +2500,16 @@
         <v>277</v>
       </c>
       <c r="G5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I5" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -2559,16 +2556,16 @@
         <v>278</v>
       </c>
       <c r="G6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -2615,16 +2612,16 @@
         <v>279</v>
       </c>
       <c r="G7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -2671,16 +2668,16 @@
         <v>280</v>
       </c>
       <c r="G8" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H8" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I8" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J8" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -2727,16 +2724,16 @@
         <v>281</v>
       </c>
       <c r="G9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H9" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J9" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -2783,16 +2780,16 @@
         <v>282</v>
       </c>
       <c r="G10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H10" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2839,16 +2836,16 @@
         <v>283</v>
       </c>
       <c r="G11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H11" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I11" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J11" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -2895,16 +2892,16 @@
         <v>284</v>
       </c>
       <c r="G12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H12" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I12" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -2951,16 +2948,16 @@
         <v>285</v>
       </c>
       <c r="G13" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H13" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I13" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J13" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -3007,16 +3004,16 @@
         <v>286</v>
       </c>
       <c r="G14" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H14" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I14" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J14" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -3060,16 +3057,16 @@
         <v>287</v>
       </c>
       <c r="G15" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I15" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="J15" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -3113,16 +3110,16 @@
         <v>288</v>
       </c>
       <c r="G16" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H16" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I16" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="J16" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -3166,16 +3163,16 @@
         <v>132</v>
       </c>
       <c r="G17" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H17" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I17" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J17" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -3219,16 +3216,16 @@
         <v>133</v>
       </c>
       <c r="G18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H18" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I18" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="J18" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -3272,16 +3269,16 @@
         <v>134</v>
       </c>
       <c r="G19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H19" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J19" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -3325,16 +3322,16 @@
         <v>135</v>
       </c>
       <c r="G20" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H20" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I20" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J20" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -3378,16 +3375,16 @@
         <v>136</v>
       </c>
       <c r="G21" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H21" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I21" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J21" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -3428,16 +3425,16 @@
         <v>137</v>
       </c>
       <c r="G22" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H22" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I22" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J22" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -3481,16 +3478,16 @@
         <v>289</v>
       </c>
       <c r="G23" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H23" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I23" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="J23" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3534,16 +3531,16 @@
         <v>139</v>
       </c>
       <c r="G24" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H24" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I24" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J24" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3587,16 +3584,16 @@
         <v>140</v>
       </c>
       <c r="G25" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H25" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I25" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -3640,16 +3637,16 @@
         <v>141</v>
       </c>
       <c r="G26" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H26" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I26" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J26" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -3693,16 +3690,16 @@
         <v>142</v>
       </c>
       <c r="G27" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H27" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I27" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="J27" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -3746,16 +3743,16 @@
         <v>290</v>
       </c>
       <c r="G28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H28" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I28" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J28" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -3799,16 +3796,16 @@
         <v>291</v>
       </c>
       <c r="G29" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H29" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I29" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J29" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -3852,16 +3849,16 @@
         <v>292</v>
       </c>
       <c r="G30" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H30" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I30" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J30" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -3905,16 +3902,16 @@
         <v>293</v>
       </c>
       <c r="G31" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H31" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I31" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J31" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -3961,16 +3958,16 @@
         <v>294</v>
       </c>
       <c r="G32" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H32" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I32" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J32" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -4017,16 +4014,16 @@
         <v>295</v>
       </c>
       <c r="G33" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H33" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I33" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J33" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -4073,16 +4070,16 @@
         <v>296</v>
       </c>
       <c r="G34" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H34" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I34" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J34" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -4129,16 +4126,16 @@
         <v>297</v>
       </c>
       <c r="G35" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H35" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I35" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J35" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -4185,16 +4182,16 @@
         <v>298</v>
       </c>
       <c r="G36" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H36" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I36" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J36" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -4241,16 +4238,16 @@
         <v>299</v>
       </c>
       <c r="G37" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H37" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I37" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J37" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -4297,16 +4294,16 @@
         <v>300</v>
       </c>
       <c r="G38" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H38" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I38" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J38" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -4353,16 +4350,16 @@
         <v>301</v>
       </c>
       <c r="G39" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H39" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I39" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J39" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -4409,16 +4406,16 @@
         <v>302</v>
       </c>
       <c r="G40" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H40" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I40" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J40" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -4465,16 +4462,16 @@
         <v>303</v>
       </c>
       <c r="G41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H41" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I41" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J41" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -4521,16 +4518,16 @@
         <v>304</v>
       </c>
       <c r="G42" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H42" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I42" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J42" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -4577,16 +4574,16 @@
         <v>305</v>
       </c>
       <c r="G43" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H43" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I43" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J43" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -4633,16 +4630,16 @@
         <v>306</v>
       </c>
       <c r="G44" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H44" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I44" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J44" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -4689,16 +4686,16 @@
         <v>307</v>
       </c>
       <c r="G45" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H45" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I45" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J45" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -4745,16 +4742,16 @@
         <v>308</v>
       </c>
       <c r="G46" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H46" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I46" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J46" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -4801,16 +4798,16 @@
         <v>309</v>
       </c>
       <c r="G47" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H47" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I47" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J47" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -4857,16 +4854,16 @@
         <v>310</v>
       </c>
       <c r="G48" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H48" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I48" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J48" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -4913,16 +4910,16 @@
         <v>311</v>
       </c>
       <c r="G49" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H49" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I49" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J49" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -4969,16 +4966,16 @@
         <v>312</v>
       </c>
       <c r="G50" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H50" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I50" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J50" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -5025,16 +5022,16 @@
         <v>313</v>
       </c>
       <c r="G51" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H51" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I51" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J51" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -5081,16 +5078,16 @@
         <v>314</v>
       </c>
       <c r="G52" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H52" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I52" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J52" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -5137,16 +5134,16 @@
         <v>315</v>
       </c>
       <c r="G53" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H53" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I53" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J53" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K53">
         <v>0</v>
@@ -5193,16 +5190,16 @@
         <v>316</v>
       </c>
       <c r="G54" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H54" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I54" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J54" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K54">
         <v>0</v>
@@ -5249,16 +5246,16 @@
         <v>317</v>
       </c>
       <c r="G55" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H55" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I55" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J55" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K55">
         <v>0</v>
@@ -5305,16 +5302,16 @@
         <v>318</v>
       </c>
       <c r="G56" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H56" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I56" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J56" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -5361,16 +5358,16 @@
         <v>319</v>
       </c>
       <c r="G57" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H57" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I57" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J57" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K57">
         <v>0</v>
@@ -5417,16 +5414,16 @@
         <v>320</v>
       </c>
       <c r="G58" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H58" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I58" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J58" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -5473,16 +5470,16 @@
         <v>321</v>
       </c>
       <c r="G59" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H59" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I59" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J59" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -5526,16 +5523,16 @@
         <v>175</v>
       </c>
       <c r="G60" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H60" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I60" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J60" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L60">
         <v>1</v>
@@ -5561,16 +5558,16 @@
         <v>176</v>
       </c>
       <c r="G61" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H61" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I61" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="J61" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L61">
         <v>1</v>
@@ -5596,16 +5593,16 @@
         <v>177</v>
       </c>
       <c r="G62" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H62" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I62" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="J62" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L62">
         <v>1</v>
@@ -5634,16 +5631,16 @@
         <v>178</v>
       </c>
       <c r="G63" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H63" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I63" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="J63" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L63">
         <v>1</v>
@@ -5669,16 +5666,16 @@
         <v>179</v>
       </c>
       <c r="G64" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H64" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I64" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J64" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L64">
         <v>1</v>
@@ -5704,16 +5701,16 @@
         <v>180</v>
       </c>
       <c r="G65" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H65" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I65" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="J65" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -5739,16 +5736,16 @@
         <v>181</v>
       </c>
       <c r="G66" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H66" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I66" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="J66" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L66">
         <v>1</v>
@@ -5774,16 +5771,16 @@
         <v>182</v>
       </c>
       <c r="G67" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H67" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I67" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J67" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L67">
         <v>1</v>
@@ -5809,16 +5806,16 @@
         <v>183</v>
       </c>
       <c r="G68" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H68" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I68" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J68" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L68">
         <v>1</v>
@@ -5844,16 +5841,16 @@
         <v>184</v>
       </c>
       <c r="G69" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H69" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I69" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J69" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L69">
         <v>1</v>
@@ -5879,16 +5876,16 @@
         <v>185</v>
       </c>
       <c r="G70" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H70" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I70" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="J70" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L70">
         <v>1</v>
@@ -5914,16 +5911,16 @@
         <v>186</v>
       </c>
       <c r="G71" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H71" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I71" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J71" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L71">
         <v>1</v>
@@ -5949,16 +5946,16 @@
         <v>187</v>
       </c>
       <c r="G72" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H72" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I72" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J72" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -5984,16 +5981,16 @@
         <v>188</v>
       </c>
       <c r="G73" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H73" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I73" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J73" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L73">
         <v>1</v>
@@ -6019,16 +6016,16 @@
         <v>189</v>
       </c>
       <c r="G74" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H74" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I74" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J74" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L74">
         <v>1</v>
@@ -6054,16 +6051,16 @@
         <v>190</v>
       </c>
       <c r="G75" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H75" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I75" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J75" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -6089,16 +6086,16 @@
         <v>191</v>
       </c>
       <c r="G76" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H76" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I76" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J76" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K76">
         <v>0</v>
@@ -6145,16 +6142,16 @@
         <v>322</v>
       </c>
       <c r="G77" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H77" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I77" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J77" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K77">
         <v>0</v>
@@ -6201,16 +6198,16 @@
         <v>323</v>
       </c>
       <c r="G78" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H78" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I78" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J78" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K78">
         <v>0</v>
@@ -6257,16 +6254,16 @@
         <v>324</v>
       </c>
       <c r="G79" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H79" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I79" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J79" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K79">
         <v>0</v>
@@ -6313,16 +6310,16 @@
         <v>325</v>
       </c>
       <c r="G80" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H80" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I80" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J80" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K80">
         <v>0</v>
@@ -6369,16 +6366,16 @@
         <v>326</v>
       </c>
       <c r="G81" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H81" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I81" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J81" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K81">
         <v>0</v>
@@ -6425,16 +6422,16 @@
         <v>327</v>
       </c>
       <c r="G82" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H82" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I82" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J82" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K82">
         <v>0</v>
@@ -6481,16 +6478,16 @@
         <v>328</v>
       </c>
       <c r="G83" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H83" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I83" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J83" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K83">
         <v>0</v>
@@ -6531,16 +6528,16 @@
         <v>71</v>
       </c>
       <c r="G84" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H84" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I84" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J84" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K84">
         <v>0</v>
@@ -6587,16 +6584,16 @@
         <v>329</v>
       </c>
       <c r="G85" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H85" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I85" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J85" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K85">
         <v>0</v>
@@ -6643,16 +6640,16 @@
         <v>330</v>
       </c>
       <c r="G86" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H86" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I86" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J86" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K86">
         <v>0</v>
@@ -6699,16 +6696,16 @@
         <v>331</v>
       </c>
       <c r="G87" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H87" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I87" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J87" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K87">
         <v>0</v>
@@ -6755,16 +6752,16 @@
         <v>332</v>
       </c>
       <c r="G88" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H88" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I88" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J88" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K88">
         <v>0</v>
@@ -6808,19 +6805,19 @@
         <v>203</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>333</v>
+        <v>203</v>
       </c>
       <c r="G89" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H89" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I89" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J89" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K89">
         <v>0</v>
@@ -6861,19 +6858,19 @@
         <v>204</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G90" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H90" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="I90" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J90" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K90">
         <v>0</v>
@@ -6914,19 +6911,19 @@
         <v>205</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G91" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H91" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="I91" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J91" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K91">
         <v>0</v>
@@ -6967,19 +6964,19 @@
         <v>206</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G92" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H92" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="I92" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J92" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K92">
         <v>0</v>
@@ -7020,19 +7017,19 @@
         <v>207</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G93" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H93" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I93" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J93" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K93">
         <v>0</v>
@@ -7070,19 +7067,19 @@
         <v>208</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G94" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H94" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I94" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J94" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K94">
         <v>0</v>
@@ -7123,19 +7120,19 @@
         <v>209</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G95" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H95" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I95" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J95" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K95">
         <v>0</v>
@@ -7173,19 +7170,19 @@
         <v>210</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G96" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H96" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I96" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J96" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K96">
         <v>0</v>
@@ -7226,19 +7223,19 @@
         <v>211</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G97" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H97" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I97" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="J97" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K97">
         <v>0</v>
@@ -7276,19 +7273,19 @@
         <v>212</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G98" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H98" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I98" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="J98" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K98">
         <v>0</v>
@@ -7329,19 +7326,19 @@
         <v>213</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G99" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H99" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I99" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="J99" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K99">
         <v>0</v>
@@ -7379,19 +7376,19 @@
         <v>214</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G100" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H100" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I100" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="J100" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K100">
         <v>0</v>
@@ -7432,19 +7429,19 @@
         <v>215</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G101" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H101" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I101" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="J101" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K101">
         <v>0</v>
@@ -7482,19 +7479,19 @@
         <v>216</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G102" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H102" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I102" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J102" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K102">
         <v>0</v>
@@ -7535,19 +7532,19 @@
         <v>217</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G103" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H103" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I103" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J103" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K103">
         <v>0</v>
@@ -7585,19 +7582,19 @@
         <v>218</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G104" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H104" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I104" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J104" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K104">
         <v>0</v>
@@ -7638,19 +7635,19 @@
         <v>219</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G105" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H105" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I105" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J105" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K105">
         <v>0</v>
@@ -7688,19 +7685,19 @@
         <v>220</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G106" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H106" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I106" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J106" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K106">
         <v>0</v>
@@ -7741,19 +7738,19 @@
         <v>221</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G107" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H107" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I107" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J107" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L107">
         <v>1</v>
@@ -7773,19 +7770,19 @@
         <v>222</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G108" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H108" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I108" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J108" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -7808,19 +7805,19 @@
         <v>223</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G109" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H109" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I109" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J109" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L109">
         <v>1</v>
@@ -7840,19 +7837,19 @@
         <v>224</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G110" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H110" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I110" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J110" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L110">
         <v>1</v>
@@ -7875,19 +7872,19 @@
         <v>225</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G111" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H111" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I111" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J111" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L111">
         <v>1</v>
@@ -7907,19 +7904,19 @@
         <v>226</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G112" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H112" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I112" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J112" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L112">
         <v>1</v>
@@ -7942,19 +7939,19 @@
         <v>227</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G113" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H113" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I113" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J113" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L113">
         <v>1</v>
@@ -7974,19 +7971,19 @@
         <v>228</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G114" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H114" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I114" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J114" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L114">
         <v>1</v>
@@ -8009,19 +8006,19 @@
         <v>229</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G115" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H115" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I115" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J115" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L115">
         <v>1</v>
@@ -8041,19 +8038,19 @@
         <v>230</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G116" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H116" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I116" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J116" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L116">
         <v>1</v>
@@ -8076,19 +8073,19 @@
         <v>231</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G117" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H117" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I117" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J117" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L117">
         <v>1</v>
@@ -8111,19 +8108,19 @@
         <v>232</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G118" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H118" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I118" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J118" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -8146,19 +8143,19 @@
         <v>233</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G119" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H119" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I119" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J119" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L119">
         <v>1</v>
@@ -8178,19 +8175,19 @@
         <v>234</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G120" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H120" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I120" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J120" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L120">
         <v>1</v>
@@ -8213,19 +8210,19 @@
         <v>235</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G121" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H121" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I121" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J121" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L121">
         <v>1</v>
@@ -8245,19 +8242,19 @@
         <v>236</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G122" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H122" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I122" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J122" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L122">
         <v>1</v>
@@ -8280,19 +8277,19 @@
         <v>237</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G123" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H123" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I123" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J123" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L123">
         <v>1</v>
@@ -8312,19 +8309,19 @@
         <v>238</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G124" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H124" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I124" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J124" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L124">
         <v>1</v>
@@ -8347,19 +8344,19 @@
         <v>239</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G125" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H125" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I125" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J125" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L125">
         <v>1</v>
@@ -8379,19 +8376,19 @@
         <v>240</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G126" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H126" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="I126" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J126" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L126">
         <v>1</v>
@@ -8414,19 +8411,19 @@
         <v>241</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G127" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H127" t="s">
         <v>27</v>
       </c>
       <c r="I127" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J127" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K127">
         <v>0</v>
@@ -8467,19 +8464,19 @@
         <v>242</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G128" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H128" t="s">
         <v>27</v>
       </c>
       <c r="I128" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J128" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K128">
         <v>0</v>
@@ -8520,19 +8517,19 @@
         <v>243</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G129" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H129" t="s">
         <v>27</v>
       </c>
       <c r="I129" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J129" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K129">
         <v>0</v>
@@ -8573,19 +8570,19 @@
         <v>244</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G130" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H130" t="s">
         <v>27</v>
       </c>
       <c r="I130" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="J130" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K130">
         <v>0</v>
@@ -8626,19 +8623,19 @@
         <v>245</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G131" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H131" t="s">
         <v>27</v>
       </c>
       <c r="I131" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J131" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -8679,19 +8676,19 @@
         <v>246</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G132" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H132" t="s">
         <v>27</v>
       </c>
       <c r="I132" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J132" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -8732,19 +8729,19 @@
         <v>247</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G133" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H133" t="s">
         <v>27</v>
       </c>
       <c r="I133" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J133" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K133">
         <v>0</v>
@@ -8788,19 +8785,19 @@
         <v>248</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G134" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H134" t="s">
         <v>27</v>
       </c>
       <c r="I134" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J134" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K134">
         <v>0</v>
@@ -8844,19 +8841,19 @@
         <v>249</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G135" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H135" t="s">
         <v>27</v>
       </c>
       <c r="I135" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J135" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K135">
         <v>0</v>
@@ -8900,19 +8897,19 @@
         <v>250</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G136" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H136" t="s">
         <v>27</v>
       </c>
       <c r="I136" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J136" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K136">
         <v>0</v>
@@ -8956,19 +8953,19 @@
         <v>251</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G137" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H137" t="s">
         <v>27</v>
       </c>
       <c r="I137" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J137" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K137">
         <v>0</v>
@@ -9009,19 +9006,19 @@
         <v>252</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G138" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H138" t="s">
         <v>27</v>
       </c>
       <c r="I138" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J138" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K138">
         <v>0</v>
@@ -9062,19 +9059,19 @@
         <v>253</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G139" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H139" t="s">
         <v>27</v>
       </c>
       <c r="I139" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J139" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K139">
         <v>0</v>
@@ -9115,19 +9112,19 @@
         <v>254</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G140" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H140" t="s">
         <v>27</v>
       </c>
       <c r="I140" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J140" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K140">
         <v>0</v>
@@ -9168,19 +9165,19 @@
         <v>255</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G141" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H141" t="s">
         <v>27</v>
       </c>
       <c r="I141" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J141" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K141">
         <v>0</v>
@@ -9221,19 +9218,19 @@
         <v>256</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G142" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H142" t="s">
         <v>27</v>
       </c>
       <c r="I142" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J142" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L142">
         <v>1</v>
@@ -9259,19 +9256,19 @@
         <v>257</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G143" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H143" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I143" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J143" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K143">
         <v>0</v>
@@ -9312,16 +9309,16 @@
         <v>95</v>
       </c>
       <c r="G144" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H144" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I144" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J144" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K144">
         <v>0</v>
@@ -9362,16 +9359,16 @@
         <v>96</v>
       </c>
       <c r="G145" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H145" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I145" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J145" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K145">
         <v>0</v>
@@ -9412,16 +9409,16 @@
         <v>97</v>
       </c>
       <c r="G146" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H146" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I146" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J146" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K146">
         <v>0</v>
@@ -9465,19 +9462,19 @@
         <v>258</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G147" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H147" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I147" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J147" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K147">
         <v>0</v>
@@ -9518,16 +9515,16 @@
         <v>99</v>
       </c>
       <c r="G148" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H148" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I148" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J148" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K148">
         <v>0</v>
@@ -9568,16 +9565,16 @@
         <v>100</v>
       </c>
       <c r="G149" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H149" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I149" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J149" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K149">
         <v>0</v>
@@ -9618,16 +9615,16 @@
         <v>101</v>
       </c>
       <c r="G150" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H150" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I150" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J150" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K150">
         <v>0</v>
@@ -9668,19 +9665,19 @@
         <v>259</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G151" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H151" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I151" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="J151" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K151">
         <v>0</v>
@@ -9721,19 +9718,19 @@
         <v>260</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G152" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H152" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I152" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J152" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K152">
         <v>0</v>
@@ -9774,19 +9771,19 @@
         <v>261</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G153" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H153" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I153" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J153" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K153">
         <v>0</v>
@@ -9827,19 +9824,19 @@
         <v>262</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G154" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H154" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I154" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J154" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K154">
         <v>0</v>
@@ -9880,19 +9877,19 @@
         <v>263</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G155" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H155" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I155" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J155" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K155">
         <v>0</v>
@@ -9933,19 +9930,19 @@
         <v>264</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G156" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H156" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I156" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J156" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K156">
         <v>0</v>
@@ -9986,19 +9983,19 @@
         <v>265</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G157" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H157" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I157" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="J157" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K157">
         <v>0</v>
@@ -10036,19 +10033,19 @@
         <v>266</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G158" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H158" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I158" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J158" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="M158">
         <v>1</v>
@@ -10068,19 +10065,19 @@
         <v>267</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G159" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H159" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I159" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J159" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="M159">
         <v>1</v>
@@ -10097,19 +10094,19 @@
         <v>268</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G160" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H160" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I160" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J160" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="M160">
         <v>1</v>
@@ -10126,19 +10123,19 @@
         <v>269</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G161" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H161" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I161" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="J161" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="M161">
         <v>1</v>
@@ -10155,19 +10152,19 @@
         <v>270</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G162" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H162" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I162" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J162" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="M162">
         <v>1</v>
@@ -10184,19 +10181,19 @@
         <v>271</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G163" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H163" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I163" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J163" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="M163">
         <v>1</v>
@@ -10213,19 +10210,19 @@
         <v>272</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G164" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H164" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I164" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J164" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="M164">
         <v>1</v>
@@ -10242,19 +10239,19 @@
         <v>273</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G165" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H165" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I165" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J165" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="M165">
         <v>1</v>
